--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -2785,32 +2785,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129094196</v>
+        <v>129093188</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421526</v>
+        <v>421407</v>
       </c>
       <c r="R21" t="n">
-        <v>6788587</v>
+        <v>6788409</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129093188</v>
+        <v>129093043</v>
       </c>
       <c r="B22" t="n">
         <v>79034</v>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421407</v>
+        <v>421355</v>
       </c>
       <c r="R22" t="n">
-        <v>6788409</v>
+        <v>6788265</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2999,32 +2999,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129093043</v>
+        <v>129094196</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421355</v>
+        <v>421526</v>
       </c>
       <c r="R23" t="n">
-        <v>6788265</v>
+        <v>6788587</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -12280,10 +12280,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129124158</v>
+        <v>129124053</v>
       </c>
       <c r="B109" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12291,21 +12291,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>421383</v>
+        <v>421421</v>
       </c>
       <c r="R109" t="n">
-        <v>6788546</v>
+        <v>6788216</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12387,50 +12387,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129124117</v>
+        <v>129124063</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>79653</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>421611</v>
+        <v>421442</v>
       </c>
       <c r="R110" t="n">
-        <v>6788482</v>
+        <v>6788613</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12462,7 +12457,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12472,7 +12467,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12499,10 +12494,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129124139</v>
+        <v>129124158</v>
       </c>
       <c r="B111" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12510,21 +12505,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12534,10 +12529,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>421354</v>
+        <v>421383</v>
       </c>
       <c r="R111" t="n">
-        <v>6788463</v>
+        <v>6788546</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12569,7 +12564,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12579,7 +12574,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12606,45 +12601,50 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124181</v>
+        <v>129124117</v>
       </c>
       <c r="B112" t="n">
-        <v>78700</v>
+        <v>8450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421537</v>
+        <v>421611</v>
       </c>
       <c r="R112" t="n">
-        <v>6788706</v>
+        <v>6788482</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12676,7 +12676,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12713,10 +12713,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129124052</v>
+        <v>129124139</v>
       </c>
       <c r="B113" t="n">
-        <v>79653</v>
+        <v>78791</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12724,21 +12724,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421391</v>
+        <v>421354</v>
       </c>
       <c r="R113" t="n">
-        <v>6788209</v>
+        <v>6788463</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12820,10 +12820,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129124159</v>
+        <v>129124181</v>
       </c>
       <c r="B114" t="n">
-        <v>79034</v>
+        <v>78700</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12831,21 +12831,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12855,10 +12855,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>421612</v>
+        <v>421537</v>
       </c>
       <c r="R114" t="n">
-        <v>6788488</v>
+        <v>6788706</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12927,50 +12927,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129124116</v>
+        <v>129124052</v>
       </c>
       <c r="B115" t="n">
-        <v>8450</v>
+        <v>79653</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>421615</v>
+        <v>421391</v>
       </c>
       <c r="R115" t="n">
-        <v>6788580</v>
+        <v>6788209</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13002,7 +12997,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13012,7 +13007,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13039,50 +13034,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129124111</v>
+        <v>129124159</v>
       </c>
       <c r="B116" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>421315</v>
+        <v>421612</v>
       </c>
       <c r="R116" t="n">
-        <v>6788532</v>
+        <v>6788488</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13114,7 +13104,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13124,7 +13114,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13151,45 +13141,50 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129124175</v>
+        <v>129124116</v>
       </c>
       <c r="B117" t="n">
-        <v>78700</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>421343</v>
+        <v>421615</v>
       </c>
       <c r="R117" t="n">
-        <v>6788400</v>
+        <v>6788580</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13221,7 +13216,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13231,7 +13226,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13258,45 +13253,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129124080</v>
+        <v>129124111</v>
       </c>
       <c r="B118" t="n">
-        <v>79624</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>421633</v>
+        <v>421315</v>
       </c>
       <c r="R118" t="n">
-        <v>6787841</v>
+        <v>6788532</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13365,10 +13365,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129124053</v>
+        <v>129124175</v>
       </c>
       <c r="B119" t="n">
-        <v>79653</v>
+        <v>78700</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13376,21 +13376,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13400,10 +13400,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>421421</v>
+        <v>421343</v>
       </c>
       <c r="R119" t="n">
-        <v>6788216</v>
+        <v>6788400</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13472,10 +13472,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129124063</v>
+        <v>129124080</v>
       </c>
       <c r="B120" t="n">
-        <v>79653</v>
+        <v>79624</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13483,21 +13483,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13507,10 +13507,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>421442</v>
+        <v>421633</v>
       </c>
       <c r="R120" t="n">
-        <v>6788613</v>
+        <v>6787841</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15208,50 +15208,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129124088</v>
+        <v>129124057</v>
       </c>
       <c r="B136" t="n">
-        <v>56913</v>
+        <v>79653</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>421296</v>
+        <v>421312</v>
       </c>
       <c r="R136" t="n">
-        <v>6788608</v>
+        <v>6788393</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15283,7 +15278,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15293,7 +15288,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15320,10 +15315,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129124077</v>
+        <v>129124163</v>
       </c>
       <c r="B137" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15331,21 +15326,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15355,10 +15350,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>421633</v>
+        <v>421454</v>
       </c>
       <c r="R137" t="n">
-        <v>6788617</v>
+        <v>6788422</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15390,7 +15385,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15400,7 +15395,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15427,45 +15422,50 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129124057</v>
+        <v>129124088</v>
       </c>
       <c r="B138" t="n">
-        <v>79653</v>
+        <v>56913</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>421312</v>
+        <v>421296</v>
       </c>
       <c r="R138" t="n">
-        <v>6788393</v>
+        <v>6788608</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15534,10 +15534,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129124163</v>
+        <v>129124077</v>
       </c>
       <c r="B139" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15545,21 +15545,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15569,10 +15569,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>421454</v>
+        <v>421633</v>
       </c>
       <c r="R139" t="n">
-        <v>6788422</v>
+        <v>6788617</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16181,50 +16181,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124120</v>
+        <v>129124144</v>
       </c>
       <c r="B145" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421520</v>
+        <v>421602</v>
       </c>
       <c r="R145" t="n">
-        <v>6788366</v>
+        <v>6787829</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16256,7 +16251,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16266,7 +16261,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16293,10 +16288,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124144</v>
+        <v>129124170</v>
       </c>
       <c r="B146" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16304,21 +16299,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16328,10 +16323,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421602</v>
+        <v>421604</v>
       </c>
       <c r="R146" t="n">
-        <v>6787829</v>
+        <v>6787823</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16363,7 +16358,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16373,7 +16368,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16400,10 +16395,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129124170</v>
+        <v>129124133</v>
       </c>
       <c r="B147" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16411,21 +16406,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16435,10 +16430,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>421604</v>
+        <v>421633</v>
       </c>
       <c r="R147" t="n">
-        <v>6787823</v>
+        <v>6787841</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16470,7 +16465,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16480,7 +16475,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16507,45 +16502,50 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129124133</v>
+        <v>129124106</v>
       </c>
       <c r="B148" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421633</v>
+        <v>421574</v>
       </c>
       <c r="R148" t="n">
-        <v>6787841</v>
+        <v>6788374</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16614,7 +16614,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124106</v>
+        <v>129124122</v>
       </c>
       <c r="B149" t="n">
         <v>8450</v>
@@ -16645,7 +16645,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -16654,10 +16654,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421574</v>
+        <v>421477</v>
       </c>
       <c r="R149" t="n">
-        <v>6788374</v>
+        <v>6788422</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16689,7 +16689,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16699,7 +16699,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16726,50 +16726,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124122</v>
+        <v>129124078</v>
       </c>
       <c r="B150" t="n">
-        <v>8450</v>
+        <v>79624</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421477</v>
+        <v>421640</v>
       </c>
       <c r="R150" t="n">
-        <v>6788422</v>
+        <v>6788394</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16801,7 +16796,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16811,7 +16806,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16838,10 +16833,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124078</v>
+        <v>129124087</v>
       </c>
       <c r="B151" t="n">
-        <v>79624</v>
+        <v>79129</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16849,21 +16844,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16873,10 +16868,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421640</v>
+        <v>421601</v>
       </c>
       <c r="R151" t="n">
-        <v>6788394</v>
+        <v>6787830</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16908,7 +16903,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16918,7 +16913,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16945,45 +16940,50 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129124087</v>
+        <v>129124120</v>
       </c>
       <c r="B152" t="n">
-        <v>79129</v>
+        <v>8450</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>967</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>421601</v>
+        <v>421520</v>
       </c>
       <c r="R152" t="n">
-        <v>6787830</v>
+        <v>6788366</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD152" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129124171</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129124183</v>
+        <v>129124161</v>
       </c>
       <c r="B9" t="n">
-        <v>78700</v>
+        <v>79034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421744</v>
+        <v>421701</v>
       </c>
       <c r="R9" t="n">
-        <v>6788480</v>
+        <v>6788470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129124161</v>
+        <v>129124183</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>78700</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421701</v>
+        <v>421744</v>
       </c>
       <c r="R10" t="n">
-        <v>6788470</v>
+        <v>6788480</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129093027</v>
+        <v>129094871</v>
       </c>
       <c r="B14" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,34 +2042,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421341</v>
+        <v>421534</v>
       </c>
       <c r="R14" t="n">
-        <v>6788261</v>
+        <v>6788452</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,10 +2143,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129094012</v>
+        <v>129093027</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2149,21 +2154,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2173,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421379</v>
+        <v>421341</v>
       </c>
       <c r="R15" t="n">
-        <v>6788540</v>
+        <v>6788261</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2250,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129093983</v>
+        <v>129094012</v>
       </c>
       <c r="B16" t="n">
         <v>79034</v>
@@ -2280,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421400</v>
+        <v>421379</v>
       </c>
       <c r="R16" t="n">
-        <v>6788524</v>
+        <v>6788540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,7 +2357,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129095317</v>
+        <v>129093983</v>
       </c>
       <c r="B17" t="n">
         <v>79034</v>
@@ -2387,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421398</v>
+        <v>421400</v>
       </c>
       <c r="R17" t="n">
-        <v>6788372</v>
+        <v>6788524</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2459,10 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129094871</v>
+        <v>129095317</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2470,39 +2475,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421534</v>
+        <v>421398</v>
       </c>
       <c r="R18" t="n">
-        <v>6788452</v>
+        <v>6788372</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129093598</v>
+        <v>129093952</v>
       </c>
       <c r="B19" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421371</v>
+        <v>421399</v>
       </c>
       <c r="R19" t="n">
-        <v>6788472</v>
+        <v>6788487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129093952</v>
+        <v>129093598</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421399</v>
+        <v>421371</v>
       </c>
       <c r="R20" t="n">
-        <v>6788487</v>
+        <v>6788472</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,32 +2785,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129093188</v>
+        <v>129094196</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421407</v>
+        <v>421526</v>
       </c>
       <c r="R21" t="n">
-        <v>6788409</v>
+        <v>6788587</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129093043</v>
+        <v>129093188</v>
       </c>
       <c r="B22" t="n">
         <v>79034</v>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421355</v>
+        <v>421407</v>
       </c>
       <c r="R22" t="n">
-        <v>6788265</v>
+        <v>6788409</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2999,32 +2999,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129094196</v>
+        <v>129093043</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421526</v>
+        <v>421355</v>
       </c>
       <c r="R23" t="n">
-        <v>6788587</v>
+        <v>6788265</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129094076</v>
+        <v>129093167</v>
       </c>
       <c r="B24" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421379</v>
+        <v>421391</v>
       </c>
       <c r="R24" t="n">
-        <v>6788540</v>
+        <v>6788314</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129093167</v>
+        <v>129094076</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,21 +3224,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421391</v>
+        <v>421379</v>
       </c>
       <c r="R25" t="n">
-        <v>6788314</v>
+        <v>6788540</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4925,10 +4925,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129095090</v>
+        <v>129094242</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>57720</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4936,16 +4936,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4956,7 +4956,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4965,10 +4965,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>421500</v>
+        <v>421564</v>
       </c>
       <c r="R41" t="n">
-        <v>6788425</v>
+        <v>6788544</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5037,10 +5037,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129093226</v>
+        <v>129094162</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5048,34 +5048,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>421395</v>
+        <v>421499</v>
       </c>
       <c r="R42" t="n">
-        <v>6788438</v>
+        <v>6788592</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5144,10 +5149,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129094242</v>
+        <v>129093226</v>
       </c>
       <c r="B43" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5155,39 +5160,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>421564</v>
+        <v>421395</v>
       </c>
       <c r="R43" t="n">
-        <v>6788544</v>
+        <v>6788438</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5256,10 +5256,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129094162</v>
+        <v>129095090</v>
       </c>
       <c r="B44" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5267,16 +5267,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5287,7 +5287,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>421499</v>
+        <v>421500</v>
       </c>
       <c r="R44" t="n">
-        <v>6788592</v>
+        <v>6788425</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6229,10 +6229,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129124130</v>
+        <v>129124182</v>
       </c>
       <c r="B53" t="n">
-        <v>78792</v>
+        <v>78700</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6240,21 +6240,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>421354</v>
+        <v>421622</v>
       </c>
       <c r="R53" t="n">
-        <v>6788463</v>
+        <v>6788520</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6336,10 +6336,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129124160</v>
+        <v>129124179</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>78700</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>421611</v>
+        <v>421487</v>
       </c>
       <c r="R54" t="n">
-        <v>6788481</v>
+        <v>6788638</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6443,10 +6443,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129124070</v>
+        <v>129124176</v>
       </c>
       <c r="B55" t="n">
-        <v>79653</v>
+        <v>78700</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6454,21 +6454,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>421616</v>
+        <v>421338</v>
       </c>
       <c r="R55" t="n">
-        <v>6787882</v>
+        <v>6788476</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124182</v>
+        <v>129124070</v>
       </c>
       <c r="B56" t="n">
-        <v>78700</v>
+        <v>79653</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,21 +6561,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421622</v>
+        <v>421616</v>
       </c>
       <c r="R56" t="n">
-        <v>6788520</v>
+        <v>6787882</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6764,10 +6764,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129124179</v>
+        <v>129124160</v>
       </c>
       <c r="B58" t="n">
-        <v>78700</v>
+        <v>79034</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6775,21 +6775,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>421487</v>
+        <v>421611</v>
       </c>
       <c r="R58" t="n">
-        <v>6788638</v>
+        <v>6788481</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129124176</v>
+        <v>129124130</v>
       </c>
       <c r="B59" t="n">
-        <v>78700</v>
+        <v>78792</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,21 +6882,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>421338</v>
+        <v>421354</v>
       </c>
       <c r="R59" t="n">
-        <v>6788476</v>
+        <v>6788463</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6978,50 +6978,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129124124</v>
+        <v>129124061</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79653</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>421440</v>
+        <v>421238</v>
       </c>
       <c r="R60" t="n">
-        <v>6788409</v>
+        <v>6788555</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7053,7 +7048,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7063,7 +7058,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7090,10 +7085,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129124061</v>
+        <v>129124142</v>
       </c>
       <c r="B61" t="n">
-        <v>79653</v>
+        <v>78791</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7101,21 +7096,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7125,10 +7120,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>421238</v>
+        <v>421594</v>
       </c>
       <c r="R61" t="n">
-        <v>6788555</v>
+        <v>6787870</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7160,7 +7155,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7170,7 +7165,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7304,10 +7299,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129124142</v>
+        <v>129124151</v>
       </c>
       <c r="B63" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7315,21 +7310,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7339,10 +7334,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>421594</v>
+        <v>421275</v>
       </c>
       <c r="R63" t="n">
-        <v>6787870</v>
+        <v>6788430</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7374,7 +7369,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7384,7 +7379,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7411,10 +7406,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129124151</v>
+        <v>129124131</v>
       </c>
       <c r="B64" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7422,21 +7417,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7446,10 +7441,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>421275</v>
+        <v>421659</v>
       </c>
       <c r="R64" t="n">
-        <v>6788430</v>
+        <v>6787750</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7481,7 +7476,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7491,7 +7486,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7518,45 +7513,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129124131</v>
+        <v>129124124</v>
       </c>
       <c r="B65" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>421659</v>
+        <v>421440</v>
       </c>
       <c r="R65" t="n">
-        <v>6787750</v>
+        <v>6788409</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7625,32 +7625,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129124058</v>
+        <v>129124173</v>
       </c>
       <c r="B66" t="n">
-        <v>79653</v>
+        <v>92816</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>421246</v>
+        <v>421621</v>
       </c>
       <c r="R66" t="n">
-        <v>6788416</v>
+        <v>6787838</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7732,7 +7732,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129124059</v>
+        <v>129124058</v>
       </c>
       <c r="B67" t="n">
         <v>79653</v>
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>421354</v>
+        <v>421246</v>
       </c>
       <c r="R67" t="n">
-        <v>6788463</v>
+        <v>6788416</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7839,7 +7839,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129124051</v>
+        <v>129124059</v>
       </c>
       <c r="B68" t="n">
         <v>79653</v>
@@ -7874,10 +7874,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>421392</v>
+        <v>421354</v>
       </c>
       <c r="R68" t="n">
-        <v>6788226</v>
+        <v>6788463</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7946,10 +7946,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129124074</v>
+        <v>129124051</v>
       </c>
       <c r="B69" t="n">
-        <v>79624</v>
+        <v>79653</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7957,21 +7957,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>421236</v>
+        <v>421392</v>
       </c>
       <c r="R69" t="n">
-        <v>6788559</v>
+        <v>6788226</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8026,12 +8026,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På stubbe med 6 brandljud</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8058,50 +8053,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129124114</v>
+        <v>129124187</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>78437</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6437</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>421399</v>
+        <v>421639</v>
       </c>
       <c r="R70" t="n">
-        <v>6788567</v>
+        <v>6788393</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8133,7 +8123,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8143,7 +8133,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8170,32 +8160,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124173</v>
+        <v>129124074</v>
       </c>
       <c r="B71" t="n">
-        <v>92811</v>
+        <v>79624</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8205,10 +8195,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>421621</v>
+        <v>421236</v>
       </c>
       <c r="R71" t="n">
-        <v>6787838</v>
+        <v>6788559</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8240,7 +8230,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8250,7 +8240,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På stubbe med 6 brandljud</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8277,45 +8272,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124187</v>
+        <v>129124114</v>
       </c>
       <c r="B72" t="n">
-        <v>78437</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6437</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>421639</v>
+        <v>421399</v>
       </c>
       <c r="R72" t="n">
-        <v>6788393</v>
+        <v>6788567</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8603,10 +8603,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129124103</v>
+        <v>129124152</v>
       </c>
       <c r="B75" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8614,21 +8614,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>421618</v>
+        <v>421234</v>
       </c>
       <c r="R75" t="n">
-        <v>6787832</v>
+        <v>6788411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8710,32 +8710,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124177</v>
+        <v>129124146</v>
       </c>
       <c r="B76" t="n">
-        <v>78700</v>
+        <v>91684</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421318</v>
+        <v>421654</v>
       </c>
       <c r="R76" t="n">
-        <v>6788511</v>
+        <v>6788448</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8817,32 +8817,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124146</v>
+        <v>129124177</v>
       </c>
       <c r="B77" t="n">
-        <v>91681</v>
+        <v>78700</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421654</v>
+        <v>421318</v>
       </c>
       <c r="R77" t="n">
-        <v>6788448</v>
+        <v>6788511</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8924,10 +8924,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129124152</v>
+        <v>129124103</v>
       </c>
       <c r="B78" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8935,21 +8935,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>421234</v>
+        <v>421618</v>
       </c>
       <c r="R78" t="n">
-        <v>6788411</v>
+        <v>6787832</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9031,10 +9031,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129124090</v>
+        <v>129124143</v>
       </c>
       <c r="B79" t="n">
-        <v>91540</v>
+        <v>78791</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9042,21 +9042,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>421576</v>
+        <v>421596</v>
       </c>
       <c r="R79" t="n">
-        <v>6788373</v>
+        <v>6787835</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9111,12 +9111,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ej märkt med hänsyn</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9143,10 +9138,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129124143</v>
+        <v>129124090</v>
       </c>
       <c r="B80" t="n">
-        <v>78791</v>
+        <v>91543</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9154,21 +9149,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9178,10 +9173,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>421596</v>
+        <v>421576</v>
       </c>
       <c r="R80" t="n">
-        <v>6787835</v>
+        <v>6788373</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9213,7 +9208,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9223,7 +9218,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ej märkt med hänsyn</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9250,10 +9250,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129124134</v>
+        <v>129124167</v>
       </c>
       <c r="B81" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9261,21 +9261,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>421616</v>
+        <v>421342</v>
       </c>
       <c r="R81" t="n">
-        <v>6787882</v>
+        <v>6788261</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9357,7 +9357,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129124168</v>
+        <v>129124148</v>
       </c>
       <c r="B82" t="n">
         <v>79034</v>
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>421329</v>
+        <v>421395</v>
       </c>
       <c r="R82" t="n">
-        <v>6788222</v>
+        <v>6788374</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9464,7 +9464,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129124157</v>
+        <v>129124168</v>
       </c>
       <c r="B83" t="n">
         <v>79034</v>
@@ -9499,10 +9499,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>421271</v>
+        <v>421329</v>
       </c>
       <c r="R83" t="n">
-        <v>6788641</v>
+        <v>6788222</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9571,7 +9571,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129124167</v>
+        <v>129124157</v>
       </c>
       <c r="B84" t="n">
         <v>79034</v>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>421342</v>
+        <v>421271</v>
       </c>
       <c r="R84" t="n">
-        <v>6788261</v>
+        <v>6788641</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9678,7 +9678,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129124129</v>
+        <v>129124134</v>
       </c>
       <c r="B85" t="n">
         <v>78792</v>
@@ -9713,10 +9713,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>421292</v>
+        <v>421616</v>
       </c>
       <c r="R85" t="n">
-        <v>6788456</v>
+        <v>6787882</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9785,10 +9785,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129124083</v>
+        <v>129124129</v>
       </c>
       <c r="B86" t="n">
-        <v>79624</v>
+        <v>78792</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>421598</v>
+        <v>421292</v>
       </c>
       <c r="R86" t="n">
-        <v>6787829</v>
+        <v>6788456</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9892,10 +9892,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129124148</v>
+        <v>129124083</v>
       </c>
       <c r="B87" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9903,21 +9903,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>421395</v>
+        <v>421598</v>
       </c>
       <c r="R87" t="n">
-        <v>6788374</v>
+        <v>6787829</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9999,45 +9999,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129124150</v>
+        <v>129124123</v>
       </c>
       <c r="B88" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>421349</v>
+        <v>421446</v>
       </c>
       <c r="R88" t="n">
-        <v>6788397</v>
+        <v>6788421</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10069,7 +10074,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10079,7 +10084,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10106,50 +10111,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129124123</v>
+        <v>129124132</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>421446</v>
+        <v>421649</v>
       </c>
       <c r="R89" t="n">
-        <v>6788421</v>
+        <v>6787778</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10218,7 +10218,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129124132</v>
+        <v>129124136</v>
       </c>
       <c r="B90" t="n">
         <v>78792</v>
@@ -10253,10 +10253,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>421649</v>
+        <v>421598</v>
       </c>
       <c r="R90" t="n">
-        <v>6787778</v>
+        <v>6787834</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10325,10 +10325,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129124136</v>
+        <v>129124150</v>
       </c>
       <c r="B91" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10336,21 +10336,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10360,10 +10360,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>421598</v>
+        <v>421349</v>
       </c>
       <c r="R91" t="n">
-        <v>6787834</v>
+        <v>6788397</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10432,10 +10432,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129124135</v>
+        <v>129124102</v>
       </c>
       <c r="B92" t="n">
-        <v>78792</v>
+        <v>83005</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10443,21 +10443,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>310</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10467,10 +10467,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>421594</v>
+        <v>421694</v>
       </c>
       <c r="R92" t="n">
-        <v>6787870</v>
+        <v>6787682</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10539,10 +10539,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129124096</v>
+        <v>129124135</v>
       </c>
       <c r="B93" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10550,39 +10550,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>421596</v>
+        <v>421594</v>
       </c>
       <c r="R93" t="n">
-        <v>6787836</v>
+        <v>6787870</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10614,7 +10609,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10624,7 +10619,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10651,10 +10646,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129124102</v>
+        <v>129124128</v>
       </c>
       <c r="B94" t="n">
-        <v>83005</v>
+        <v>78792</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10662,21 +10657,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>310</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10686,10 +10681,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>421694</v>
+        <v>421391</v>
       </c>
       <c r="R94" t="n">
-        <v>6787682</v>
+        <v>6788209</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10721,7 +10716,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10731,7 +10726,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10758,10 +10753,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129124128</v>
+        <v>129124096</v>
       </c>
       <c r="B95" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10769,34 +10764,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>421391</v>
+        <v>421596</v>
       </c>
       <c r="R95" t="n">
-        <v>6788209</v>
+        <v>6787836</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10972,10 +10972,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129124153</v>
+        <v>129124072</v>
       </c>
       <c r="B97" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10983,21 +10983,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>421305</v>
+        <v>421591</v>
       </c>
       <c r="R97" t="n">
-        <v>6788474</v>
+        <v>6787819</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11079,10 +11079,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129124072</v>
+        <v>129124153</v>
       </c>
       <c r="B98" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11090,21 +11090,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11114,10 +11114,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>421591</v>
+        <v>421305</v>
       </c>
       <c r="R98" t="n">
-        <v>6787819</v>
+        <v>6788474</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11149,7 +11149,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11298,10 +11298,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129124104</v>
+        <v>129124154</v>
       </c>
       <c r="B100" t="n">
-        <v>92849</v>
+        <v>79034</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11309,43 +11309,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>421407</v>
+        <v>421303</v>
       </c>
       <c r="R100" t="n">
-        <v>6788349</v>
+        <v>6788456</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11377,7 +11368,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11387,7 +11378,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11414,7 +11405,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129124154</v>
+        <v>129124147</v>
       </c>
       <c r="B101" t="n">
         <v>79034</v>
@@ -11449,10 +11440,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>421303</v>
+        <v>421437</v>
       </c>
       <c r="R101" t="n">
-        <v>6788456</v>
+        <v>6788275</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11484,7 +11475,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11494,7 +11485,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11521,10 +11512,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129124147</v>
+        <v>129124104</v>
       </c>
       <c r="B102" t="n">
-        <v>79034</v>
+        <v>92854</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11532,34 +11523,43 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>421437</v>
+        <v>421407</v>
       </c>
       <c r="R102" t="n">
-        <v>6788275</v>
+        <v>6788349</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11591,7 +11591,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11740,10 +11740,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129124081</v>
+        <v>129124165</v>
       </c>
       <c r="B104" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11751,21 +11751,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11775,10 +11775,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>421592</v>
+        <v>421340</v>
       </c>
       <c r="R104" t="n">
-        <v>6787842</v>
+        <v>6788389</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11847,10 +11847,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129124165</v>
+        <v>129124071</v>
       </c>
       <c r="B105" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11858,21 +11858,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>421340</v>
+        <v>421598</v>
       </c>
       <c r="R105" t="n">
-        <v>6788389</v>
+        <v>6787863</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11954,10 +11954,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124071</v>
+        <v>129124141</v>
       </c>
       <c r="B106" t="n">
-        <v>79653</v>
+        <v>78791</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11965,21 +11965,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11989,10 +11989,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421598</v>
+        <v>421616</v>
       </c>
       <c r="R106" t="n">
-        <v>6787863</v>
+        <v>6787883</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12173,10 +12173,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129124141</v>
+        <v>129124081</v>
       </c>
       <c r="B108" t="n">
-        <v>78791</v>
+        <v>79624</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12184,21 +12184,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12208,10 +12208,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>421616</v>
+        <v>421592</v>
       </c>
       <c r="R108" t="n">
-        <v>6787883</v>
+        <v>6787842</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12601,50 +12601,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124117</v>
+        <v>129124139</v>
       </c>
       <c r="B112" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421611</v>
+        <v>421354</v>
       </c>
       <c r="R112" t="n">
-        <v>6788482</v>
+        <v>6788463</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12676,7 +12671,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12686,7 +12681,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12713,10 +12708,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129124139</v>
+        <v>129124052</v>
       </c>
       <c r="B113" t="n">
-        <v>78791</v>
+        <v>79653</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12724,21 +12719,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12748,10 +12743,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421354</v>
+        <v>421391</v>
       </c>
       <c r="R113" t="n">
-        <v>6788463</v>
+        <v>6788209</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12783,7 +12778,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12793,7 +12788,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12820,10 +12815,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129124181</v>
+        <v>129124159</v>
       </c>
       <c r="B114" t="n">
-        <v>78700</v>
+        <v>79034</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12831,21 +12826,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12855,10 +12850,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>421537</v>
+        <v>421612</v>
       </c>
       <c r="R114" t="n">
-        <v>6788706</v>
+        <v>6788488</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12890,7 +12885,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12900,7 +12895,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12927,45 +12922,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129124052</v>
+        <v>129124117</v>
       </c>
       <c r="B115" t="n">
-        <v>79653</v>
+        <v>8450</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>421391</v>
+        <v>421611</v>
       </c>
       <c r="R115" t="n">
-        <v>6788209</v>
+        <v>6788482</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13034,45 +13034,50 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129124159</v>
+        <v>129124116</v>
       </c>
       <c r="B116" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>421612</v>
+        <v>421615</v>
       </c>
       <c r="R116" t="n">
-        <v>6788488</v>
+        <v>6788580</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13104,7 +13109,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13114,7 +13119,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13141,7 +13146,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129124116</v>
+        <v>129124111</v>
       </c>
       <c r="B117" t="n">
         <v>8450</v>
@@ -13181,10 +13186,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>421615</v>
+        <v>421315</v>
       </c>
       <c r="R117" t="n">
-        <v>6788580</v>
+        <v>6788532</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13216,7 +13221,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13226,7 +13231,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13253,50 +13258,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129124111</v>
+        <v>129124080</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>79624</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>421315</v>
+        <v>421633</v>
       </c>
       <c r="R118" t="n">
-        <v>6788532</v>
+        <v>6787841</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13365,7 +13365,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129124175</v>
+        <v>129124181</v>
       </c>
       <c r="B119" t="n">
         <v>78700</v>
@@ -13400,10 +13400,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>421343</v>
+        <v>421537</v>
       </c>
       <c r="R119" t="n">
-        <v>6788400</v>
+        <v>6788706</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13472,10 +13472,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129124080</v>
+        <v>129124175</v>
       </c>
       <c r="B120" t="n">
-        <v>79624</v>
+        <v>78700</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13483,21 +13483,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13507,10 +13507,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>421633</v>
+        <v>421343</v>
       </c>
       <c r="R120" t="n">
-        <v>6787841</v>
+        <v>6788400</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13793,10 +13793,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129124164</v>
+        <v>129124062</v>
       </c>
       <c r="B123" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13804,21 +13804,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13828,10 +13828,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>421345</v>
+        <v>421395</v>
       </c>
       <c r="R123" t="n">
-        <v>6788394</v>
+        <v>6788610</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13900,10 +13900,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129124082</v>
+        <v>129124156</v>
       </c>
       <c r="B124" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13911,21 +13911,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13935,10 +13935,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>421601</v>
+        <v>421351</v>
       </c>
       <c r="R124" t="n">
-        <v>6787830</v>
+        <v>6788471</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14007,45 +14007,50 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129124062</v>
+        <v>129124121</v>
       </c>
       <c r="B125" t="n">
-        <v>79653</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>421395</v>
+        <v>421524</v>
       </c>
       <c r="R125" t="n">
-        <v>6788610</v>
+        <v>6788399</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14077,7 +14082,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14087,7 +14092,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14114,10 +14119,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129124156</v>
+        <v>129124082</v>
       </c>
       <c r="B126" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14125,21 +14130,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14149,10 +14154,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>421351</v>
+        <v>421601</v>
       </c>
       <c r="R126" t="n">
-        <v>6788471</v>
+        <v>6787830</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14184,7 +14189,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14194,7 +14199,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14221,10 +14226,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129124105</v>
+        <v>129124164</v>
       </c>
       <c r="B127" t="n">
-        <v>92849</v>
+        <v>79034</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14232,43 +14237,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421613</v>
+        <v>421345</v>
       </c>
       <c r="R127" t="n">
-        <v>6788634</v>
+        <v>6788394</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14300,7 +14296,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14310,7 +14306,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14337,38 +14333,42 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129124121</v>
+        <v>129124105</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>92854</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>421524</v>
+        <v>421613</v>
       </c>
       <c r="R128" t="n">
-        <v>6788399</v>
+        <v>6788634</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14449,45 +14449,50 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129124056</v>
+        <v>129124108</v>
       </c>
       <c r="B129" t="n">
-        <v>79653</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>421343</v>
+        <v>421362</v>
       </c>
       <c r="R129" t="n">
-        <v>6788400</v>
+        <v>6788387</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14519,7 +14524,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14529,7 +14534,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14556,50 +14561,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129124108</v>
+        <v>129124056</v>
       </c>
       <c r="B130" t="n">
-        <v>8450</v>
+        <v>79653</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>421362</v>
+        <v>421343</v>
       </c>
       <c r="R130" t="n">
-        <v>6788387</v>
+        <v>6788400</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14775,50 +14775,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129124112</v>
+        <v>129124180</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>78700</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>421293</v>
+        <v>421501</v>
       </c>
       <c r="R132" t="n">
-        <v>6788551</v>
+        <v>6788671</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14850,7 +14845,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14860,7 +14855,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15101,45 +15096,50 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129124180</v>
+        <v>129124112</v>
       </c>
       <c r="B135" t="n">
-        <v>78700</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>421501</v>
+        <v>421293</v>
       </c>
       <c r="R135" t="n">
-        <v>6788671</v>
+        <v>6788551</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15641,10 +15641,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129124140</v>
+        <v>129124169</v>
       </c>
       <c r="B140" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15652,21 +15652,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15676,10 +15676,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>421656</v>
+        <v>421618</v>
       </c>
       <c r="R140" t="n">
-        <v>6787791</v>
+        <v>6787872</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15748,10 +15748,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129124068</v>
+        <v>129124140</v>
       </c>
       <c r="B141" t="n">
-        <v>79653</v>
+        <v>78791</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15759,21 +15759,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15783,10 +15783,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>421675</v>
+        <v>421656</v>
       </c>
       <c r="R141" t="n">
-        <v>6787696</v>
+        <v>6787791</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15855,7 +15855,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129124065</v>
+        <v>129124068</v>
       </c>
       <c r="B142" t="n">
         <v>79653</v>
@@ -15890,10 +15890,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>421530</v>
+        <v>421675</v>
       </c>
       <c r="R142" t="n">
-        <v>6788679</v>
+        <v>6787696</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15925,7 +15925,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15962,50 +15962,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129124109</v>
+        <v>129124065</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>79653</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>421325</v>
+        <v>421530</v>
       </c>
       <c r="R143" t="n">
-        <v>6788393</v>
+        <v>6788679</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16037,7 +16032,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16047,7 +16042,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16074,45 +16069,50 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129124169</v>
+        <v>129124109</v>
       </c>
       <c r="B144" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>421618</v>
+        <v>421325</v>
       </c>
       <c r="R144" t="n">
-        <v>6787872</v>
+        <v>6788393</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16181,45 +16181,50 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124144</v>
+        <v>129124106</v>
       </c>
       <c r="B145" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421602</v>
+        <v>421574</v>
       </c>
       <c r="R145" t="n">
-        <v>6787829</v>
+        <v>6788374</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16251,7 +16256,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16261,7 +16266,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16288,45 +16293,50 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124170</v>
+        <v>129124122</v>
       </c>
       <c r="B146" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421604</v>
+        <v>421477</v>
       </c>
       <c r="R146" t="n">
-        <v>6787823</v>
+        <v>6788422</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16358,7 +16368,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16368,7 +16378,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16395,45 +16405,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129124133</v>
+        <v>129124120</v>
       </c>
       <c r="B147" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>421633</v>
+        <v>421520</v>
       </c>
       <c r="R147" t="n">
-        <v>6787841</v>
+        <v>6788366</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16465,7 +16480,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16475,7 +16490,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16502,50 +16517,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129124106</v>
+        <v>129124133</v>
       </c>
       <c r="B148" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421574</v>
+        <v>421633</v>
       </c>
       <c r="R148" t="n">
-        <v>6788374</v>
+        <v>6787841</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16577,7 +16587,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16587,7 +16597,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16614,50 +16624,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124122</v>
+        <v>129124078</v>
       </c>
       <c r="B149" t="n">
-        <v>8450</v>
+        <v>79624</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421477</v>
+        <v>421640</v>
       </c>
       <c r="R149" t="n">
-        <v>6788422</v>
+        <v>6788394</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16689,7 +16694,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16699,7 +16704,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16726,10 +16731,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124078</v>
+        <v>129124144</v>
       </c>
       <c r="B150" t="n">
-        <v>79624</v>
+        <v>78791</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16737,21 +16742,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16761,10 +16766,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421640</v>
+        <v>421602</v>
       </c>
       <c r="R150" t="n">
-        <v>6788394</v>
+        <v>6787829</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16796,7 +16801,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16806,7 +16811,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16833,10 +16838,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124087</v>
+        <v>129124170</v>
       </c>
       <c r="B151" t="n">
-        <v>79129</v>
+        <v>79034</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16844,21 +16849,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16868,10 +16873,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421601</v>
+        <v>421604</v>
       </c>
       <c r="R151" t="n">
-        <v>6787830</v>
+        <v>6787823</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16903,7 +16908,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16913,7 +16918,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16940,50 +16945,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129124120</v>
+        <v>129124138</v>
       </c>
       <c r="B152" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>421520</v>
+        <v>421292</v>
       </c>
       <c r="R152" t="n">
-        <v>6788366</v>
+        <v>6788456</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17052,10 +17052,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129124138</v>
+        <v>129124087</v>
       </c>
       <c r="B153" t="n">
-        <v>78791</v>
+        <v>79129</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17063,21 +17063,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17087,10 +17087,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>421292</v>
+        <v>421601</v>
       </c>
       <c r="R153" t="n">
-        <v>6788456</v>
+        <v>6787830</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD153" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129124066</v>
       </c>
       <c r="B2" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129124162</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129124171</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129124185</v>
       </c>
       <c r="B5" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129124184</v>
       </c>
       <c r="B6" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>129124067</v>
       </c>
       <c r="B8" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129124161</v>
+        <v>129124183</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>78701</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421701</v>
+        <v>421744</v>
       </c>
       <c r="R9" t="n">
-        <v>6788470</v>
+        <v>6788480</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129124183</v>
+        <v>129124161</v>
       </c>
       <c r="B10" t="n">
-        <v>78700</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421744</v>
+        <v>421701</v>
       </c>
       <c r="R10" t="n">
-        <v>6788480</v>
+        <v>6788470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129094871</v>
+        <v>129093983</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,39 +2042,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421534</v>
+        <v>421400</v>
       </c>
       <c r="R14" t="n">
-        <v>6788452</v>
+        <v>6788524</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2146,7 +2141,7 @@
         <v>129093027</v>
       </c>
       <c r="B15" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2248,7 @@
         <v>129094012</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129093983</v>
+        <v>129095317</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421400</v>
+        <v>421398</v>
       </c>
       <c r="R17" t="n">
-        <v>6788524</v>
+        <v>6788372</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,10 +2459,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129095317</v>
+        <v>129094871</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,34 +2470,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421398</v>
+        <v>421534</v>
       </c>
       <c r="R18" t="n">
-        <v>6788372</v>
+        <v>6788452</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
         <v>129093952</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>129093598</v>
       </c>
       <c r="B20" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,32 +2785,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129094196</v>
+        <v>129093202</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421526</v>
+        <v>421407</v>
       </c>
       <c r="R21" t="n">
-        <v>6788587</v>
+        <v>6788409</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,32 +2892,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129093188</v>
+        <v>129094196</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421407</v>
+        <v>421526</v>
       </c>
       <c r="R22" t="n">
-        <v>6788409</v>
+        <v>6788587</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
         <v>129093043</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129093167</v>
+        <v>129094076</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421391</v>
+        <v>421379</v>
       </c>
       <c r="R24" t="n">
-        <v>6788314</v>
+        <v>6788540</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129094076</v>
+        <v>129093167</v>
       </c>
       <c r="B25" t="n">
-        <v>79624</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,21 +3224,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421379</v>
+        <v>421391</v>
       </c>
       <c r="R25" t="n">
-        <v>6788540</v>
+        <v>6788314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
         <v>129093766</v>
       </c>
       <c r="B26" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>129094170</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3534,32 +3534,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129094800</v>
+        <v>129094249</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421501</v>
+        <v>421564</v>
       </c>
       <c r="R28" t="n">
-        <v>6788477</v>
+        <v>6788544</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,32 +3641,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129094249</v>
+        <v>129094800</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421564</v>
+        <v>421501</v>
       </c>
       <c r="R29" t="n">
-        <v>6788544</v>
+        <v>6788477</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3751,7 +3751,7 @@
         <v>129093086</v>
       </c>
       <c r="B30" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>129093018</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>129094179</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>129094072</v>
       </c>
       <c r="B34" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>129095256</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>129094091</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>129096050</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>129095002</v>
       </c>
       <c r="B38" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>129093008</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>129094542</v>
       </c>
       <c r="B40" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4925,10 +4925,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129094242</v>
+        <v>129093226</v>
       </c>
       <c r="B41" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4936,39 +4936,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>421564</v>
+        <v>421395</v>
       </c>
       <c r="R41" t="n">
-        <v>6788544</v>
+        <v>6788438</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5037,10 +5032,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129094162</v>
+        <v>129095090</v>
       </c>
       <c r="B42" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5048,16 +5043,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5068,7 +5063,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5077,10 +5072,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>421499</v>
+        <v>421500</v>
       </c>
       <c r="R42" t="n">
-        <v>6788592</v>
+        <v>6788425</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5149,32 +5144,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129093226</v>
+        <v>129093117</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5184,10 +5179,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>421395</v>
+        <v>421391</v>
       </c>
       <c r="R43" t="n">
-        <v>6788438</v>
+        <v>6788314</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5256,10 +5251,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129095090</v>
+        <v>129094242</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>57720</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5267,16 +5262,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5287,7 +5282,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5296,10 +5291,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>421500</v>
+        <v>421564</v>
       </c>
       <c r="R44" t="n">
-        <v>6788425</v>
+        <v>6788544</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5368,45 +5363,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129093117</v>
+        <v>129094162</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>421391</v>
+        <v>421499</v>
       </c>
       <c r="R45" t="n">
-        <v>6788314</v>
+        <v>6788592</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
         <v>129094551</v>
       </c>
       <c r="B46" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>129093174</v>
       </c>
       <c r="B47" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>129093173</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>129095392</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5903,45 +5903,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129094943</v>
+        <v>129095582</v>
       </c>
       <c r="B50" t="n">
-        <v>79624</v>
+        <v>58093</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>421534</v>
+        <v>421342</v>
       </c>
       <c r="R50" t="n">
-        <v>6788452</v>
+        <v>6788310</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6010,10 +6015,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129094103</v>
+        <v>129094943</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>79625</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6021,21 +6026,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6045,10 +6050,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>421421</v>
+        <v>421534</v>
       </c>
       <c r="R51" t="n">
-        <v>6788547</v>
+        <v>6788452</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6117,50 +6122,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129095582</v>
+        <v>129094103</v>
       </c>
       <c r="B52" t="n">
-        <v>58093</v>
+        <v>79035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>421342</v>
+        <v>421421</v>
       </c>
       <c r="R52" t="n">
-        <v>6788310</v>
+        <v>6788547</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6229,10 +6229,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129124182</v>
+        <v>129124070</v>
       </c>
       <c r="B53" t="n">
-        <v>78700</v>
+        <v>79654</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6240,21 +6240,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>421622</v>
+        <v>421616</v>
       </c>
       <c r="R53" t="n">
-        <v>6788520</v>
+        <v>6787882</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6336,10 +6336,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129124179</v>
+        <v>129124182</v>
       </c>
       <c r="B54" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>421487</v>
+        <v>421622</v>
       </c>
       <c r="R54" t="n">
-        <v>6788638</v>
+        <v>6788520</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6443,10 +6443,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129124176</v>
+        <v>129124179</v>
       </c>
       <c r="B55" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>421338</v>
+        <v>421487</v>
       </c>
       <c r="R55" t="n">
-        <v>6788476</v>
+        <v>6788638</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124070</v>
+        <v>129124176</v>
       </c>
       <c r="B56" t="n">
-        <v>79653</v>
+        <v>78701</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,21 +6561,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421616</v>
+        <v>421338</v>
       </c>
       <c r="R56" t="n">
-        <v>6787882</v>
+        <v>6788476</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6657,10 +6657,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129124166</v>
+        <v>129124130</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>78793</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,21 +6668,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>421316</v>
+        <v>421354</v>
       </c>
       <c r="R57" t="n">
-        <v>6788317</v>
+        <v>6788463</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6767,7 +6767,7 @@
         <v>129124160</v>
       </c>
       <c r="B58" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129124130</v>
+        <v>129124166</v>
       </c>
       <c r="B59" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,21 +6882,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>421354</v>
+        <v>421316</v>
       </c>
       <c r="R59" t="n">
-        <v>6788463</v>
+        <v>6788317</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6978,10 +6978,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129124061</v>
+        <v>129124149</v>
       </c>
       <c r="B60" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,21 +6989,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>421238</v>
+        <v>421376</v>
       </c>
       <c r="R60" t="n">
-        <v>6788555</v>
+        <v>6788380</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7085,10 +7085,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129124142</v>
+        <v>129124151</v>
       </c>
       <c r="B61" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7096,21 +7096,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>421594</v>
+        <v>421275</v>
       </c>
       <c r="R61" t="n">
-        <v>6787870</v>
+        <v>6788430</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7192,10 +7192,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129124149</v>
+        <v>129124061</v>
       </c>
       <c r="B62" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7203,21 +7203,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>421376</v>
+        <v>421238</v>
       </c>
       <c r="R62" t="n">
-        <v>6788380</v>
+        <v>6788555</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7299,10 +7299,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129124151</v>
+        <v>129124142</v>
       </c>
       <c r="B63" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7310,21 +7310,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>421275</v>
+        <v>421594</v>
       </c>
       <c r="R63" t="n">
-        <v>6788430</v>
+        <v>6787870</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7406,45 +7406,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129124131</v>
+        <v>129124124</v>
       </c>
       <c r="B64" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>421659</v>
+        <v>421440</v>
       </c>
       <c r="R64" t="n">
-        <v>6787750</v>
+        <v>6788409</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7476,7 +7481,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7486,7 +7491,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7513,50 +7518,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129124124</v>
+        <v>129124131</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>421440</v>
+        <v>421659</v>
       </c>
       <c r="R65" t="n">
-        <v>6788409</v>
+        <v>6787750</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7625,10 +7625,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129124173</v>
+        <v>129124114</v>
       </c>
       <c r="B66" t="n">
-        <v>92816</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7636,34 +7636,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>421621</v>
+        <v>421399</v>
       </c>
       <c r="R66" t="n">
-        <v>6787838</v>
+        <v>6788567</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7695,7 +7700,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7705,7 +7710,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7732,45 +7737,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129124058</v>
+        <v>129124115</v>
       </c>
       <c r="B67" t="n">
-        <v>79653</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>421246</v>
+        <v>421608</v>
       </c>
       <c r="R67" t="n">
-        <v>6788416</v>
+        <v>6788661</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7802,7 +7812,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7812,7 +7822,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7839,10 +7849,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129124059</v>
+        <v>129124058</v>
       </c>
       <c r="B68" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7874,10 +7884,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>421354</v>
+        <v>421246</v>
       </c>
       <c r="R68" t="n">
-        <v>6788463</v>
+        <v>6788416</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7909,7 +7919,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7919,7 +7929,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7946,10 +7956,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129124051</v>
+        <v>129124059</v>
       </c>
       <c r="B69" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7981,10 +7991,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>421392</v>
+        <v>421354</v>
       </c>
       <c r="R69" t="n">
-        <v>6788226</v>
+        <v>6788463</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8016,7 +8026,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8026,7 +8036,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8053,10 +8063,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129124187</v>
+        <v>129124051</v>
       </c>
       <c r="B70" t="n">
-        <v>78437</v>
+        <v>79654</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8064,21 +8074,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8088,10 +8098,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>421639</v>
+        <v>421392</v>
       </c>
       <c r="R70" t="n">
-        <v>6788393</v>
+        <v>6788226</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8123,7 +8133,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8133,7 +8143,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8160,10 +8170,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124074</v>
+        <v>129124187</v>
       </c>
       <c r="B71" t="n">
-        <v>79624</v>
+        <v>78438</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8171,21 +8181,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8195,10 +8205,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>421236</v>
+        <v>421639</v>
       </c>
       <c r="R71" t="n">
-        <v>6788559</v>
+        <v>6788393</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8230,7 +8240,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8240,12 +8250,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På stubbe med 6 brandljud</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8272,10 +8277,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124114</v>
+        <v>129124173</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>92819</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8283,39 +8288,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>421399</v>
+        <v>421621</v>
       </c>
       <c r="R72" t="n">
-        <v>6788567</v>
+        <v>6787838</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8384,50 +8384,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129124115</v>
+        <v>129124074</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>79625</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>421608</v>
+        <v>421236</v>
       </c>
       <c r="R73" t="n">
-        <v>6788661</v>
+        <v>6788559</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8459,7 +8454,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8469,7 +8464,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På stubbe med 6 brandljud</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8499,7 +8499,7 @@
         <v>129124145</v>
       </c>
       <c r="B74" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>129124152</v>
       </c>
       <c r="B75" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8710,32 +8710,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124146</v>
+        <v>129124177</v>
       </c>
       <c r="B76" t="n">
-        <v>91684</v>
+        <v>78701</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421654</v>
+        <v>421318</v>
       </c>
       <c r="R76" t="n">
-        <v>6788448</v>
+        <v>6788511</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8817,32 +8817,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124177</v>
+        <v>129124146</v>
       </c>
       <c r="B77" t="n">
-        <v>78700</v>
+        <v>91687</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421318</v>
+        <v>421654</v>
       </c>
       <c r="R77" t="n">
-        <v>6788511</v>
+        <v>6788448</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8927,7 +8927,7 @@
         <v>129124103</v>
       </c>
       <c r="B78" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9031,10 +9031,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129124143</v>
+        <v>129124090</v>
       </c>
       <c r="B79" t="n">
-        <v>78791</v>
+        <v>91546</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9042,21 +9042,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>421596</v>
+        <v>421576</v>
       </c>
       <c r="R79" t="n">
-        <v>6787835</v>
+        <v>6788373</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9111,7 +9111,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ej märkt med hänsyn</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9138,10 +9143,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129124090</v>
+        <v>129124143</v>
       </c>
       <c r="B80" t="n">
-        <v>91543</v>
+        <v>78792</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9149,21 +9154,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9173,10 +9178,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>421576</v>
+        <v>421596</v>
       </c>
       <c r="R80" t="n">
-        <v>6788373</v>
+        <v>6787835</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9208,7 +9213,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9218,12 +9223,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ej märkt med hänsyn</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9250,10 +9250,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129124167</v>
+        <v>129124134</v>
       </c>
       <c r="B81" t="n">
-        <v>79034</v>
+        <v>78793</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9261,21 +9261,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>421342</v>
+        <v>421616</v>
       </c>
       <c r="R81" t="n">
-        <v>6788261</v>
+        <v>6787882</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9357,10 +9357,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129124148</v>
+        <v>129124129</v>
       </c>
       <c r="B82" t="n">
-        <v>79034</v>
+        <v>78793</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9368,21 +9368,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>421395</v>
+        <v>421292</v>
       </c>
       <c r="R82" t="n">
-        <v>6788374</v>
+        <v>6788456</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9464,10 +9464,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129124168</v>
+        <v>129124083</v>
       </c>
       <c r="B83" t="n">
-        <v>79034</v>
+        <v>79625</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9475,21 +9475,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9499,10 +9499,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>421329</v>
+        <v>421598</v>
       </c>
       <c r="R83" t="n">
-        <v>6788222</v>
+        <v>6787829</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9571,10 +9571,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129124157</v>
+        <v>129124168</v>
       </c>
       <c r="B84" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>421271</v>
+        <v>421329</v>
       </c>
       <c r="R84" t="n">
-        <v>6788641</v>
+        <v>6788222</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9678,10 +9678,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129124134</v>
+        <v>129124157</v>
       </c>
       <c r="B85" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9689,21 +9689,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9713,10 +9713,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>421616</v>
+        <v>421271</v>
       </c>
       <c r="R85" t="n">
-        <v>6787882</v>
+        <v>6788641</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9785,10 +9785,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129124129</v>
+        <v>129124167</v>
       </c>
       <c r="B86" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>421292</v>
+        <v>421342</v>
       </c>
       <c r="R86" t="n">
-        <v>6788456</v>
+        <v>6788261</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9892,10 +9892,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129124083</v>
+        <v>129124148</v>
       </c>
       <c r="B87" t="n">
-        <v>79624</v>
+        <v>79035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9903,21 +9903,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>421598</v>
+        <v>421395</v>
       </c>
       <c r="R87" t="n">
-        <v>6787829</v>
+        <v>6788374</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9999,50 +9999,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129124123</v>
+        <v>129124150</v>
       </c>
       <c r="B88" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>421446</v>
+        <v>421349</v>
       </c>
       <c r="R88" t="n">
-        <v>6788421</v>
+        <v>6788397</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10074,7 +10069,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10084,7 +10079,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10111,45 +10106,50 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129124132</v>
+        <v>129124123</v>
       </c>
       <c r="B89" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>421649</v>
+        <v>421446</v>
       </c>
       <c r="R89" t="n">
-        <v>6787778</v>
+        <v>6788421</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10218,10 +10218,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129124136</v>
+        <v>129124132</v>
       </c>
       <c r="B90" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10253,10 +10253,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>421598</v>
+        <v>421649</v>
       </c>
       <c r="R90" t="n">
-        <v>6787834</v>
+        <v>6787778</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10325,10 +10325,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129124150</v>
+        <v>129124136</v>
       </c>
       <c r="B91" t="n">
-        <v>79034</v>
+        <v>78793</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10336,21 +10336,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10360,10 +10360,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>421349</v>
+        <v>421598</v>
       </c>
       <c r="R91" t="n">
-        <v>6788397</v>
+        <v>6787834</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10435,7 +10435,7 @@
         <v>129124102</v>
       </c>
       <c r="B92" t="n">
-        <v>83005</v>
+        <v>83006</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>129124135</v>
       </c>
       <c r="B93" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>129124128</v>
       </c>
       <c r="B94" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>129124060</v>
       </c>
       <c r="B96" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>129124072</v>
       </c>
       <c r="B97" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>129124153</v>
       </c>
       <c r="B98" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11298,45 +11298,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129124154</v>
+        <v>129124110</v>
       </c>
       <c r="B100" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>421303</v>
+        <v>421271</v>
       </c>
       <c r="R100" t="n">
-        <v>6788456</v>
+        <v>6788430</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11368,7 +11373,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11378,7 +11383,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11405,10 +11410,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129124147</v>
+        <v>129124104</v>
       </c>
       <c r="B101" t="n">
-        <v>79034</v>
+        <v>92857</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11416,34 +11421,43 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>421437</v>
+        <v>421407</v>
       </c>
       <c r="R101" t="n">
-        <v>6788275</v>
+        <v>6788349</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11475,7 +11489,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11485,7 +11499,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11512,10 +11526,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129124104</v>
+        <v>129124154</v>
       </c>
       <c r="B102" t="n">
-        <v>92854</v>
+        <v>79035</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11523,43 +11537,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>421407</v>
+        <v>421303</v>
       </c>
       <c r="R102" t="n">
-        <v>6788349</v>
+        <v>6788456</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11591,7 +11596,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11601,7 +11606,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11628,50 +11633,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129124110</v>
+        <v>129124147</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>421271</v>
+        <v>421437</v>
       </c>
       <c r="R103" t="n">
-        <v>6788430</v>
+        <v>6788275</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11740,10 +11740,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129124165</v>
+        <v>129124071</v>
       </c>
       <c r="B104" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11751,21 +11751,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11775,10 +11775,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>421340</v>
+        <v>421598</v>
       </c>
       <c r="R104" t="n">
-        <v>6788389</v>
+        <v>6787863</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11847,10 +11847,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129124071</v>
+        <v>129124141</v>
       </c>
       <c r="B105" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11858,21 +11858,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>421598</v>
+        <v>421616</v>
       </c>
       <c r="R105" t="n">
-        <v>6787863</v>
+        <v>6787883</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11954,10 +11954,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124141</v>
+        <v>129124165</v>
       </c>
       <c r="B106" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11965,21 +11965,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11989,10 +11989,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421616</v>
+        <v>421340</v>
       </c>
       <c r="R106" t="n">
-        <v>6787883</v>
+        <v>6788389</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12061,50 +12061,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129124127</v>
+        <v>129124081</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>79625</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>421630</v>
+        <v>421592</v>
       </c>
       <c r="R107" t="n">
-        <v>6787815</v>
+        <v>6787842</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12136,7 +12131,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12146,7 +12141,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12173,45 +12168,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129124081</v>
+        <v>129124127</v>
       </c>
       <c r="B108" t="n">
-        <v>79624</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>421592</v>
+        <v>421630</v>
       </c>
       <c r="R108" t="n">
-        <v>6787842</v>
+        <v>6787815</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12280,10 +12280,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129124053</v>
+        <v>129124080</v>
       </c>
       <c r="B109" t="n">
-        <v>79653</v>
+        <v>79625</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12291,21 +12291,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>421421</v>
+        <v>421633</v>
       </c>
       <c r="R109" t="n">
-        <v>6788216</v>
+        <v>6787841</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12387,10 +12387,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129124063</v>
+        <v>129124181</v>
       </c>
       <c r="B110" t="n">
-        <v>79653</v>
+        <v>78701</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12398,21 +12398,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12422,10 +12422,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>421442</v>
+        <v>421537</v>
       </c>
       <c r="R110" t="n">
-        <v>6788613</v>
+        <v>6788706</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12494,10 +12494,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129124158</v>
+        <v>129124175</v>
       </c>
       <c r="B111" t="n">
-        <v>79034</v>
+        <v>78701</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>421383</v>
+        <v>421343</v>
       </c>
       <c r="R111" t="n">
-        <v>6788546</v>
+        <v>6788400</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12601,10 +12601,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124139</v>
+        <v>129124053</v>
       </c>
       <c r="B112" t="n">
-        <v>78791</v>
+        <v>79654</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12612,21 +12612,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421354</v>
+        <v>421421</v>
       </c>
       <c r="R112" t="n">
-        <v>6788463</v>
+        <v>6788216</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12708,10 +12708,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129124052</v>
+        <v>129124063</v>
       </c>
       <c r="B113" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12743,10 +12743,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421391</v>
+        <v>421442</v>
       </c>
       <c r="R113" t="n">
-        <v>6788209</v>
+        <v>6788613</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12815,10 +12815,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129124159</v>
+        <v>129124139</v>
       </c>
       <c r="B114" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12826,21 +12826,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>421612</v>
+        <v>421354</v>
       </c>
       <c r="R114" t="n">
-        <v>6788488</v>
+        <v>6788463</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12922,50 +12922,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129124117</v>
+        <v>129124052</v>
       </c>
       <c r="B115" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>421611</v>
+        <v>421391</v>
       </c>
       <c r="R115" t="n">
-        <v>6788482</v>
+        <v>6788209</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12997,7 +12992,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13007,7 +13002,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13034,50 +13029,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129124116</v>
+        <v>129124158</v>
       </c>
       <c r="B116" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>421615</v>
+        <v>421383</v>
       </c>
       <c r="R116" t="n">
-        <v>6788580</v>
+        <v>6788546</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13109,7 +13099,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13119,7 +13109,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13146,50 +13136,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129124111</v>
+        <v>129124159</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>421315</v>
+        <v>421612</v>
       </c>
       <c r="R117" t="n">
-        <v>6788532</v>
+        <v>6788488</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13221,7 +13206,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13231,7 +13216,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13258,45 +13243,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129124080</v>
+        <v>129124117</v>
       </c>
       <c r="B118" t="n">
-        <v>79624</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>421633</v>
+        <v>421611</v>
       </c>
       <c r="R118" t="n">
-        <v>6787841</v>
+        <v>6788482</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13328,7 +13318,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13338,7 +13328,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13365,45 +13355,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129124181</v>
+        <v>129124116</v>
       </c>
       <c r="B119" t="n">
-        <v>78700</v>
+        <v>8450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>421537</v>
+        <v>421615</v>
       </c>
       <c r="R119" t="n">
-        <v>6788706</v>
+        <v>6788580</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13435,7 +13430,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13445,7 +13440,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13472,45 +13467,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129124175</v>
+        <v>129124111</v>
       </c>
       <c r="B120" t="n">
-        <v>78700</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>421343</v>
+        <v>421315</v>
       </c>
       <c r="R120" t="n">
-        <v>6788400</v>
+        <v>6788532</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13582,7 +13582,7 @@
         <v>129124069</v>
       </c>
       <c r="B121" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>129124054</v>
       </c>
       <c r="B122" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>129124062</v>
       </c>
       <c r="B123" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13900,10 +13900,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129124156</v>
+        <v>129124164</v>
       </c>
       <c r="B124" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13935,10 +13935,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>421351</v>
+        <v>421345</v>
       </c>
       <c r="R124" t="n">
-        <v>6788471</v>
+        <v>6788394</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14007,50 +14007,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129124121</v>
+        <v>129124156</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>421524</v>
+        <v>421351</v>
       </c>
       <c r="R125" t="n">
-        <v>6788399</v>
+        <v>6788471</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14082,7 +14077,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14092,7 +14087,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14119,10 +14114,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129124082</v>
+        <v>129124105</v>
       </c>
       <c r="B126" t="n">
-        <v>79624</v>
+        <v>92857</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14130,34 +14125,43 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>5966</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>421601</v>
+        <v>421613</v>
       </c>
       <c r="R126" t="n">
-        <v>6787830</v>
+        <v>6788634</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14189,7 +14193,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14199,7 +14203,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14226,45 +14230,50 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129124164</v>
+        <v>129124121</v>
       </c>
       <c r="B127" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421345</v>
+        <v>421524</v>
       </c>
       <c r="R127" t="n">
-        <v>6788394</v>
+        <v>6788399</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14296,7 +14305,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14306,7 +14315,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14333,10 +14342,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129124105</v>
+        <v>129124082</v>
       </c>
       <c r="B128" t="n">
-        <v>92854</v>
+        <v>79625</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14344,43 +14353,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5966</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>421613</v>
+        <v>421601</v>
       </c>
       <c r="R128" t="n">
-        <v>6788634</v>
+        <v>6787830</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14449,50 +14449,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129124108</v>
+        <v>129124056</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>421362</v>
+        <v>421343</v>
       </c>
       <c r="R129" t="n">
-        <v>6788387</v>
+        <v>6788400</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14524,7 +14519,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14534,7 +14529,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14561,45 +14556,50 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129124056</v>
+        <v>129124108</v>
       </c>
       <c r="B130" t="n">
-        <v>79653</v>
+        <v>8450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>421343</v>
+        <v>421362</v>
       </c>
       <c r="R130" t="n">
-        <v>6788400</v>
+        <v>6788387</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14668,10 +14668,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129124155</v>
+        <v>129124178</v>
       </c>
       <c r="B131" t="n">
-        <v>79034</v>
+        <v>78701</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14679,21 +14679,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14703,10 +14703,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>421354</v>
+        <v>421235</v>
       </c>
       <c r="R131" t="n">
-        <v>6788463</v>
+        <v>6788559</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14778,7 +14778,7 @@
         <v>129124180</v>
       </c>
       <c r="B132" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14882,10 +14882,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129124073</v>
+        <v>129124155</v>
       </c>
       <c r="B133" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>421595</v>
+        <v>421354</v>
       </c>
       <c r="R133" t="n">
-        <v>6787823</v>
+        <v>6788463</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14989,45 +14989,50 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129124178</v>
+        <v>129124112</v>
       </c>
       <c r="B134" t="n">
-        <v>78700</v>
+        <v>8450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>421235</v>
+        <v>421293</v>
       </c>
       <c r="R134" t="n">
-        <v>6788559</v>
+        <v>6788551</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15059,7 +15064,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15069,7 +15074,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15096,50 +15101,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129124112</v>
+        <v>129124073</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>421293</v>
+        <v>421595</v>
       </c>
       <c r="R135" t="n">
-        <v>6788551</v>
+        <v>6787823</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15211,7 +15211,7 @@
         <v>129124057</v>
       </c>
       <c r="B136" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>129124163</v>
       </c>
       <c r="B137" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>129124077</v>
       </c>
       <c r="B139" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15641,45 +15641,50 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129124169</v>
+        <v>129124109</v>
       </c>
       <c r="B140" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>421618</v>
+        <v>421325</v>
       </c>
       <c r="R140" t="n">
-        <v>6787872</v>
+        <v>6788393</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15711,7 +15716,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15721,7 +15726,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15751,7 +15756,7 @@
         <v>129124140</v>
       </c>
       <c r="B141" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15858,7 +15863,7 @@
         <v>129124068</v>
       </c>
       <c r="B142" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15965,7 +15970,7 @@
         <v>129124065</v>
       </c>
       <c r="B143" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16069,50 +16074,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129124109</v>
+        <v>129124169</v>
       </c>
       <c r="B144" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>421325</v>
+        <v>421618</v>
       </c>
       <c r="R144" t="n">
-        <v>6788393</v>
+        <v>6787872</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16181,50 +16181,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124106</v>
+        <v>129124170</v>
       </c>
       <c r="B145" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421574</v>
+        <v>421604</v>
       </c>
       <c r="R145" t="n">
-        <v>6788374</v>
+        <v>6787823</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16256,7 +16251,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16266,7 +16261,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16293,50 +16288,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124122</v>
+        <v>129124087</v>
       </c>
       <c r="B146" t="n">
-        <v>8450</v>
+        <v>79130</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>967</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421477</v>
+        <v>421601</v>
       </c>
       <c r="R146" t="n">
-        <v>6788422</v>
+        <v>6787830</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16368,7 +16358,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16378,7 +16368,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16405,50 +16395,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129124120</v>
+        <v>129124144</v>
       </c>
       <c r="B147" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>421520</v>
+        <v>421602</v>
       </c>
       <c r="R147" t="n">
-        <v>6788366</v>
+        <v>6787829</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16480,7 +16465,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16490,7 +16475,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16517,7 +16502,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129124133</v>
+        <v>129124138</v>
       </c>
       <c r="B148" t="n">
         <v>78792</v>
@@ -16528,21 +16513,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16552,10 +16537,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421633</v>
+        <v>421292</v>
       </c>
       <c r="R148" t="n">
-        <v>6787841</v>
+        <v>6788456</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16587,7 +16572,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16597,7 +16582,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16624,45 +16609,50 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124078</v>
+        <v>129124106</v>
       </c>
       <c r="B149" t="n">
-        <v>79624</v>
+        <v>8450</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421640</v>
+        <v>421574</v>
       </c>
       <c r="R149" t="n">
-        <v>6788394</v>
+        <v>6788374</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16694,7 +16684,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16704,7 +16694,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16731,45 +16721,50 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124144</v>
+        <v>129124122</v>
       </c>
       <c r="B150" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421602</v>
+        <v>421477</v>
       </c>
       <c r="R150" t="n">
-        <v>6787829</v>
+        <v>6788422</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16801,7 +16796,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16811,7 +16806,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16838,45 +16833,50 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124170</v>
+        <v>129124120</v>
       </c>
       <c r="B151" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421604</v>
+        <v>421520</v>
       </c>
       <c r="R151" t="n">
-        <v>6787823</v>
+        <v>6788366</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16945,10 +16945,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129124138</v>
+        <v>129124133</v>
       </c>
       <c r="B152" t="n">
-        <v>78791</v>
+        <v>78793</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16956,21 +16956,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16980,10 +16980,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>421292</v>
+        <v>421633</v>
       </c>
       <c r="R152" t="n">
-        <v>6788456</v>
+        <v>6787841</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17052,10 +17052,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129124087</v>
+        <v>129124078</v>
       </c>
       <c r="B153" t="n">
-        <v>79129</v>
+        <v>79625</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17063,21 +17063,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17087,10 +17087,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>421601</v>
+        <v>421640</v>
       </c>
       <c r="R153" t="n">
-        <v>6787830</v>
+        <v>6788394</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17159,10 +17159,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129124064</v>
+        <v>129124186</v>
       </c>
       <c r="B154" t="n">
-        <v>79653</v>
+        <v>78701</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17170,21 +17170,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17194,10 +17194,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>421501</v>
+        <v>421626</v>
       </c>
       <c r="R154" t="n">
-        <v>6788671</v>
+        <v>6787877</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17266,10 +17266,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129124137</v>
+        <v>129124064</v>
       </c>
       <c r="B155" t="n">
-        <v>78791</v>
+        <v>79654</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17277,21 +17277,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17301,10 +17301,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>421312</v>
+        <v>421501</v>
       </c>
       <c r="R155" t="n">
-        <v>6788393</v>
+        <v>6788671</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17346,7 +17346,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17373,10 +17373,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129124186</v>
+        <v>129124137</v>
       </c>
       <c r="B156" t="n">
-        <v>78700</v>
+        <v>78792</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17384,21 +17384,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17408,10 +17408,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>421626</v>
+        <v>421312</v>
       </c>
       <c r="R156" t="n">
-        <v>6787877</v>
+        <v>6788393</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17443,7 +17443,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17453,7 +17453,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17595,7 +17595,7 @@
         <v>129124076</v>
       </c>
       <c r="B158" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>129124084</v>
       </c>
       <c r="B159" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129124183</v>
+        <v>129124161</v>
       </c>
       <c r="B9" t="n">
-        <v>78701</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421744</v>
+        <v>421701</v>
       </c>
       <c r="R9" t="n">
-        <v>6788480</v>
+        <v>6788470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129124161</v>
+        <v>129124183</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>78701</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421701</v>
+        <v>421744</v>
       </c>
       <c r="R10" t="n">
-        <v>6788470</v>
+        <v>6788480</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129093983</v>
+        <v>129093027</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,21 +2042,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421400</v>
+        <v>421341</v>
       </c>
       <c r="R14" t="n">
-        <v>6788524</v>
+        <v>6788261</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129093027</v>
+        <v>129094012</v>
       </c>
       <c r="B15" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2149,21 +2149,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421341</v>
+        <v>421379</v>
       </c>
       <c r="R15" t="n">
-        <v>6788261</v>
+        <v>6788540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2245,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129094012</v>
+        <v>129093983</v>
       </c>
       <c r="B16" t="n">
         <v>79035</v>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421379</v>
+        <v>421400</v>
       </c>
       <c r="R16" t="n">
-        <v>6788540</v>
+        <v>6788524</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129093202</v>
+        <v>129093188</v>
       </c>
       <c r="B21" t="n">
         <v>79035</v>
@@ -2892,32 +2892,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129094196</v>
+        <v>129093043</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421526</v>
+        <v>421355</v>
       </c>
       <c r="R22" t="n">
-        <v>6788587</v>
+        <v>6788265</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2999,32 +2999,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129093043</v>
+        <v>129094196</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421355</v>
+        <v>421526</v>
       </c>
       <c r="R23" t="n">
-        <v>6788265</v>
+        <v>6788587</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3534,32 +3534,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129094249</v>
+        <v>129094800</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421564</v>
+        <v>421501</v>
       </c>
       <c r="R28" t="n">
-        <v>6788544</v>
+        <v>6788477</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,32 +3641,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129094800</v>
+        <v>129094249</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421501</v>
+        <v>421564</v>
       </c>
       <c r="R29" t="n">
-        <v>6788477</v>
+        <v>6788544</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -5032,50 +5032,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129095090</v>
+        <v>129093117</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>421500</v>
+        <v>421391</v>
       </c>
       <c r="R42" t="n">
-        <v>6788425</v>
+        <v>6788314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5144,45 +5139,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129093117</v>
+        <v>129094242</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>421391</v>
+        <v>421564</v>
       </c>
       <c r="R43" t="n">
-        <v>6788314</v>
+        <v>6788544</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5251,7 +5251,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129094242</v>
+        <v>129094162</v>
       </c>
       <c r="B44" t="n">
         <v>57720</v>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>421564</v>
+        <v>421499</v>
       </c>
       <c r="R44" t="n">
-        <v>6788544</v>
+        <v>6788592</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,10 +5363,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129094162</v>
+        <v>129095090</v>
       </c>
       <c r="B45" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5374,16 +5374,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5394,7 +5394,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>421499</v>
+        <v>421500</v>
       </c>
       <c r="R45" t="n">
-        <v>6788592</v>
+        <v>6788425</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5903,50 +5903,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129095582</v>
+        <v>129094103</v>
       </c>
       <c r="B50" t="n">
-        <v>58093</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>421342</v>
+        <v>421421</v>
       </c>
       <c r="R50" t="n">
-        <v>6788310</v>
+        <v>6788547</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6015,45 +6010,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129094943</v>
+        <v>129095582</v>
       </c>
       <c r="B51" t="n">
-        <v>79625</v>
+        <v>58093</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>421534</v>
+        <v>421342</v>
       </c>
       <c r="R51" t="n">
-        <v>6788452</v>
+        <v>6788310</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6122,10 +6122,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129094103</v>
+        <v>129094943</v>
       </c>
       <c r="B52" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6133,21 +6133,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>421421</v>
+        <v>421534</v>
       </c>
       <c r="R52" t="n">
-        <v>6788547</v>
+        <v>6788452</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6229,10 +6229,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129124070</v>
+        <v>129124182</v>
       </c>
       <c r="B53" t="n">
-        <v>79654</v>
+        <v>78701</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6240,21 +6240,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>421616</v>
+        <v>421622</v>
       </c>
       <c r="R53" t="n">
-        <v>6787882</v>
+        <v>6788520</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6336,7 +6336,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129124182</v>
+        <v>129124179</v>
       </c>
       <c r="B54" t="n">
         <v>78701</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>421622</v>
+        <v>421487</v>
       </c>
       <c r="R54" t="n">
-        <v>6788520</v>
+        <v>6788638</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6443,7 +6443,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129124179</v>
+        <v>129124176</v>
       </c>
       <c r="B55" t="n">
         <v>78701</v>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>421487</v>
+        <v>421338</v>
       </c>
       <c r="R55" t="n">
-        <v>6788638</v>
+        <v>6788476</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124176</v>
+        <v>129124160</v>
       </c>
       <c r="B56" t="n">
-        <v>78701</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,21 +6561,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421338</v>
+        <v>421611</v>
       </c>
       <c r="R56" t="n">
-        <v>6788476</v>
+        <v>6788481</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6657,10 +6657,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129124130</v>
+        <v>129124070</v>
       </c>
       <c r="B57" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,21 +6668,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>421354</v>
+        <v>421616</v>
       </c>
       <c r="R57" t="n">
-        <v>6788463</v>
+        <v>6787882</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6764,7 +6764,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129124160</v>
+        <v>129124166</v>
       </c>
       <c r="B58" t="n">
         <v>79035</v>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>421611</v>
+        <v>421316</v>
       </c>
       <c r="R58" t="n">
-        <v>6788481</v>
+        <v>6788317</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129124166</v>
+        <v>129124130</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,21 +6882,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>421316</v>
+        <v>421354</v>
       </c>
       <c r="R59" t="n">
-        <v>6788317</v>
+        <v>6788463</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6978,10 +6978,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129124149</v>
+        <v>129124061</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,21 +6989,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>421376</v>
+        <v>421238</v>
       </c>
       <c r="R60" t="n">
-        <v>6788380</v>
+        <v>6788555</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7085,7 +7085,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129124151</v>
+        <v>129124149</v>
       </c>
       <c r="B61" t="n">
         <v>79035</v>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>421275</v>
+        <v>421376</v>
       </c>
       <c r="R61" t="n">
-        <v>6788430</v>
+        <v>6788380</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7192,10 +7192,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129124061</v>
+        <v>129124142</v>
       </c>
       <c r="B62" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7203,21 +7203,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>421238</v>
+        <v>421594</v>
       </c>
       <c r="R62" t="n">
-        <v>6788555</v>
+        <v>6787870</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7299,10 +7299,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129124142</v>
+        <v>129124151</v>
       </c>
       <c r="B63" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7310,21 +7310,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>421594</v>
+        <v>421275</v>
       </c>
       <c r="R63" t="n">
-        <v>6787870</v>
+        <v>6788430</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7625,10 +7625,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129124114</v>
+        <v>129124173</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>92819</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7636,39 +7636,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>421399</v>
+        <v>421621</v>
       </c>
       <c r="R66" t="n">
-        <v>6788567</v>
+        <v>6787838</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7700,7 +7695,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7710,7 +7705,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7737,50 +7732,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129124115</v>
+        <v>129124058</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>421608</v>
+        <v>421246</v>
       </c>
       <c r="R67" t="n">
-        <v>6788661</v>
+        <v>6788416</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7812,7 +7802,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7822,7 +7812,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7849,7 +7839,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129124058</v>
+        <v>129124059</v>
       </c>
       <c r="B68" t="n">
         <v>79654</v>
@@ -7884,10 +7874,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>421246</v>
+        <v>421354</v>
       </c>
       <c r="R68" t="n">
-        <v>6788416</v>
+        <v>6788463</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7919,7 +7909,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7929,7 +7919,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7956,7 +7946,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129124059</v>
+        <v>129124051</v>
       </c>
       <c r="B69" t="n">
         <v>79654</v>
@@ -7991,10 +7981,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>421354</v>
+        <v>421392</v>
       </c>
       <c r="R69" t="n">
-        <v>6788463</v>
+        <v>6788226</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8026,7 +8016,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8036,7 +8026,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8063,10 +8053,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129124051</v>
+        <v>129124187</v>
       </c>
       <c r="B70" t="n">
-        <v>79654</v>
+        <v>78438</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8074,21 +8064,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8098,10 +8088,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>421392</v>
+        <v>421639</v>
       </c>
       <c r="R70" t="n">
-        <v>6788226</v>
+        <v>6788393</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8133,7 +8123,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8143,7 +8133,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8170,45 +8160,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124187</v>
+        <v>129124114</v>
       </c>
       <c r="B71" t="n">
-        <v>78438</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>421639</v>
+        <v>421399</v>
       </c>
       <c r="R71" t="n">
-        <v>6788393</v>
+        <v>6788567</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8240,7 +8235,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8250,7 +8245,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8277,10 +8272,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124173</v>
+        <v>129124115</v>
       </c>
       <c r="B72" t="n">
-        <v>92819</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8288,34 +8283,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>421621</v>
+        <v>421608</v>
       </c>
       <c r="R72" t="n">
-        <v>6787838</v>
+        <v>6788661</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8496,32 +8496,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129124145</v>
+        <v>129124146</v>
       </c>
       <c r="B74" t="n">
-        <v>78792</v>
+        <v>91687</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>421591</v>
+        <v>421654</v>
       </c>
       <c r="R74" t="n">
-        <v>6787819</v>
+        <v>6788448</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8603,10 +8603,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129124152</v>
+        <v>129124145</v>
       </c>
       <c r="B75" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8614,21 +8614,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>421234</v>
+        <v>421591</v>
       </c>
       <c r="R75" t="n">
-        <v>6788411</v>
+        <v>6787819</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8710,10 +8710,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124177</v>
+        <v>129124152</v>
       </c>
       <c r="B76" t="n">
-        <v>78701</v>
+        <v>79035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8721,21 +8721,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421318</v>
+        <v>421234</v>
       </c>
       <c r="R76" t="n">
-        <v>6788511</v>
+        <v>6788411</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8817,32 +8817,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124146</v>
+        <v>129124177</v>
       </c>
       <c r="B77" t="n">
-        <v>91687</v>
+        <v>78701</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421654</v>
+        <v>421318</v>
       </c>
       <c r="R77" t="n">
-        <v>6788448</v>
+        <v>6788511</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9031,10 +9031,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129124090</v>
+        <v>129124143</v>
       </c>
       <c r="B79" t="n">
-        <v>91546</v>
+        <v>78792</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9042,21 +9042,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>421576</v>
+        <v>421596</v>
       </c>
       <c r="R79" t="n">
-        <v>6788373</v>
+        <v>6787835</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9111,12 +9111,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ej märkt med hänsyn</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9143,10 +9138,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129124143</v>
+        <v>129124090</v>
       </c>
       <c r="B80" t="n">
-        <v>78792</v>
+        <v>91546</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9154,21 +9149,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9178,10 +9173,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>421596</v>
+        <v>421576</v>
       </c>
       <c r="R80" t="n">
-        <v>6787835</v>
+        <v>6788373</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9213,7 +9208,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9223,7 +9218,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ej märkt med hänsyn</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9250,10 +9250,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129124134</v>
+        <v>129124168</v>
       </c>
       <c r="B81" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9261,21 +9261,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>421616</v>
+        <v>421329</v>
       </c>
       <c r="R81" t="n">
-        <v>6787882</v>
+        <v>6788222</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9357,10 +9357,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129124129</v>
+        <v>129124157</v>
       </c>
       <c r="B82" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9368,21 +9368,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>421292</v>
+        <v>421271</v>
       </c>
       <c r="R82" t="n">
-        <v>6788456</v>
+        <v>6788641</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9464,10 +9464,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129124083</v>
+        <v>129124167</v>
       </c>
       <c r="B83" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9475,21 +9475,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9499,10 +9499,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>421598</v>
+        <v>421342</v>
       </c>
       <c r="R83" t="n">
-        <v>6787829</v>
+        <v>6788261</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9571,7 +9571,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129124168</v>
+        <v>129124148</v>
       </c>
       <c r="B84" t="n">
         <v>79035</v>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>421329</v>
+        <v>421395</v>
       </c>
       <c r="R84" t="n">
-        <v>6788222</v>
+        <v>6788374</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9678,10 +9678,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129124157</v>
+        <v>129124134</v>
       </c>
       <c r="B85" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9689,21 +9689,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9713,10 +9713,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>421271</v>
+        <v>421616</v>
       </c>
       <c r="R85" t="n">
-        <v>6788641</v>
+        <v>6787882</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9785,10 +9785,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129124167</v>
+        <v>129124083</v>
       </c>
       <c r="B86" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>421342</v>
+        <v>421598</v>
       </c>
       <c r="R86" t="n">
-        <v>6788261</v>
+        <v>6787829</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9892,10 +9892,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129124148</v>
+        <v>129124129</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9903,21 +9903,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>421395</v>
+        <v>421292</v>
       </c>
       <c r="R87" t="n">
-        <v>6788374</v>
+        <v>6788456</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9999,10 +9999,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129124150</v>
+        <v>129124136</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10010,21 +10010,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>421349</v>
+        <v>421598</v>
       </c>
       <c r="R88" t="n">
-        <v>6788397</v>
+        <v>6787834</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10106,50 +10106,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129124123</v>
+        <v>129124132</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>421446</v>
+        <v>421649</v>
       </c>
       <c r="R89" t="n">
-        <v>6788421</v>
+        <v>6787778</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10181,7 +10176,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10191,7 +10186,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10218,10 +10213,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129124132</v>
+        <v>129124150</v>
       </c>
       <c r="B90" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10229,21 +10224,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10253,10 +10248,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>421649</v>
+        <v>421349</v>
       </c>
       <c r="R90" t="n">
-        <v>6787778</v>
+        <v>6788397</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10288,7 +10283,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10298,7 +10293,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10325,45 +10320,50 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129124136</v>
+        <v>129124123</v>
       </c>
       <c r="B91" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>421598</v>
+        <v>421446</v>
       </c>
       <c r="R91" t="n">
-        <v>6787834</v>
+        <v>6788421</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10432,10 +10432,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129124102</v>
+        <v>129124135</v>
       </c>
       <c r="B92" t="n">
-        <v>83006</v>
+        <v>78793</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10443,21 +10443,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>310</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10467,10 +10467,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>421694</v>
+        <v>421594</v>
       </c>
       <c r="R92" t="n">
-        <v>6787682</v>
+        <v>6787870</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10539,7 +10539,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129124135</v>
+        <v>129124128</v>
       </c>
       <c r="B93" t="n">
         <v>78793</v>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>421594</v>
+        <v>421391</v>
       </c>
       <c r="R93" t="n">
-        <v>6787870</v>
+        <v>6788209</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10646,10 +10646,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129124128</v>
+        <v>129124102</v>
       </c>
       <c r="B94" t="n">
-        <v>78793</v>
+        <v>83006</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10657,21 +10657,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>310</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10681,10 +10681,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>421391</v>
+        <v>421694</v>
       </c>
       <c r="R94" t="n">
-        <v>6788209</v>
+        <v>6787682</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10716,7 +10716,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10865,45 +10865,50 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129124060</v>
+        <v>129124125</v>
       </c>
       <c r="B96" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>421338</v>
+        <v>421369</v>
       </c>
       <c r="R96" t="n">
-        <v>6788476</v>
+        <v>6788395</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10935,7 +10940,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10945,7 +10950,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10972,7 +10977,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129124072</v>
+        <v>129124060</v>
       </c>
       <c r="B97" t="n">
         <v>79654</v>
@@ -11007,10 +11012,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>421591</v>
+        <v>421338</v>
       </c>
       <c r="R97" t="n">
-        <v>6787819</v>
+        <v>6788476</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11042,7 +11047,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11052,7 +11057,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11186,50 +11191,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129124125</v>
+        <v>129124072</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>421369</v>
+        <v>421591</v>
       </c>
       <c r="R99" t="n">
-        <v>6788395</v>
+        <v>6787819</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11261,7 +11261,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11298,38 +11298,42 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129124110</v>
+        <v>129124104</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>92857</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11338,10 +11342,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>421271</v>
+        <v>421407</v>
       </c>
       <c r="R100" t="n">
-        <v>6788430</v>
+        <v>6788349</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11373,7 +11377,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11383,7 +11387,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11410,10 +11414,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129124104</v>
+        <v>129124154</v>
       </c>
       <c r="B101" t="n">
-        <v>92857</v>
+        <v>79035</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11421,43 +11425,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>421407</v>
+        <v>421303</v>
       </c>
       <c r="R101" t="n">
-        <v>6788349</v>
+        <v>6788456</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11489,7 +11484,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11499,7 +11494,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11526,7 +11521,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129124154</v>
+        <v>129124147</v>
       </c>
       <c r="B102" t="n">
         <v>79035</v>
@@ -11561,10 +11556,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>421303</v>
+        <v>421437</v>
       </c>
       <c r="R102" t="n">
-        <v>6788456</v>
+        <v>6788275</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11596,7 +11591,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11606,7 +11601,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11633,45 +11628,50 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129124147</v>
+        <v>129124110</v>
       </c>
       <c r="B103" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>421437</v>
+        <v>421271</v>
       </c>
       <c r="R103" t="n">
-        <v>6788275</v>
+        <v>6788430</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11740,10 +11740,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129124071</v>
+        <v>129124165</v>
       </c>
       <c r="B104" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11751,21 +11751,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11775,10 +11775,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>421598</v>
+        <v>421340</v>
       </c>
       <c r="R104" t="n">
-        <v>6787863</v>
+        <v>6788389</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11847,10 +11847,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129124141</v>
+        <v>129124071</v>
       </c>
       <c r="B105" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11858,21 +11858,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>421616</v>
+        <v>421598</v>
       </c>
       <c r="R105" t="n">
-        <v>6787883</v>
+        <v>6787863</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11954,10 +11954,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124165</v>
+        <v>129124141</v>
       </c>
       <c r="B106" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11965,21 +11965,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11989,10 +11989,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421340</v>
+        <v>421616</v>
       </c>
       <c r="R106" t="n">
-        <v>6788389</v>
+        <v>6787883</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12280,10 +12280,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129124080</v>
+        <v>129124181</v>
       </c>
       <c r="B109" t="n">
-        <v>79625</v>
+        <v>78701</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12291,21 +12291,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>421633</v>
+        <v>421537</v>
       </c>
       <c r="R109" t="n">
-        <v>6787841</v>
+        <v>6788706</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12387,7 +12387,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129124181</v>
+        <v>129124175</v>
       </c>
       <c r="B110" t="n">
         <v>78701</v>
@@ -12422,10 +12422,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>421537</v>
+        <v>421343</v>
       </c>
       <c r="R110" t="n">
-        <v>6788706</v>
+        <v>6788400</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12494,10 +12494,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129124175</v>
+        <v>129124053</v>
       </c>
       <c r="B111" t="n">
-        <v>78701</v>
+        <v>79654</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>421343</v>
+        <v>421421</v>
       </c>
       <c r="R111" t="n">
-        <v>6788400</v>
+        <v>6788216</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12601,7 +12601,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124053</v>
+        <v>129124063</v>
       </c>
       <c r="B112" t="n">
         <v>79654</v>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421421</v>
+        <v>421442</v>
       </c>
       <c r="R112" t="n">
-        <v>6788216</v>
+        <v>6788613</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12708,10 +12708,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129124063</v>
+        <v>129124158</v>
       </c>
       <c r="B113" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12719,21 +12719,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12743,10 +12743,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421442</v>
+        <v>421383</v>
       </c>
       <c r="R113" t="n">
-        <v>6788613</v>
+        <v>6788546</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13029,7 +13029,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129124158</v>
+        <v>129124159</v>
       </c>
       <c r="B116" t="n">
         <v>79035</v>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>421383</v>
+        <v>421612</v>
       </c>
       <c r="R116" t="n">
-        <v>6788546</v>
+        <v>6788488</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13136,45 +13136,50 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129124159</v>
+        <v>129124117</v>
       </c>
       <c r="B117" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>421612</v>
+        <v>421611</v>
       </c>
       <c r="R117" t="n">
-        <v>6788488</v>
+        <v>6788482</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13243,7 +13248,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129124117</v>
+        <v>129124116</v>
       </c>
       <c r="B118" t="n">
         <v>8450</v>
@@ -13283,10 +13288,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>421611</v>
+        <v>421615</v>
       </c>
       <c r="R118" t="n">
-        <v>6788482</v>
+        <v>6788580</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13318,7 +13323,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13328,7 +13333,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13355,7 +13360,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129124116</v>
+        <v>129124111</v>
       </c>
       <c r="B119" t="n">
         <v>8450</v>
@@ -13395,10 +13400,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>421615</v>
+        <v>421315</v>
       </c>
       <c r="R119" t="n">
-        <v>6788580</v>
+        <v>6788532</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13430,7 +13435,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13440,7 +13445,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13467,50 +13472,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129124111</v>
+        <v>129124080</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>79625</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>421315</v>
+        <v>421633</v>
       </c>
       <c r="R120" t="n">
-        <v>6788532</v>
+        <v>6787841</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13579,10 +13579,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129124069</v>
+        <v>129124105</v>
       </c>
       <c r="B121" t="n">
-        <v>79654</v>
+        <v>92857</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13590,34 +13590,43 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>421626</v>
+        <v>421613</v>
       </c>
       <c r="R121" t="n">
-        <v>6787879</v>
+        <v>6788634</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13649,7 +13658,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13659,7 +13668,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13686,10 +13695,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129124054</v>
+        <v>129124082</v>
       </c>
       <c r="B122" t="n">
-        <v>79654</v>
+        <v>79625</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13697,21 +13706,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13721,10 +13730,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>421423</v>
+        <v>421601</v>
       </c>
       <c r="R122" t="n">
-        <v>6788261</v>
+        <v>6787830</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13756,7 +13765,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13766,7 +13775,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13793,7 +13802,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129124062</v>
+        <v>129124069</v>
       </c>
       <c r="B123" t="n">
         <v>79654</v>
@@ -13828,10 +13837,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>421395</v>
+        <v>421626</v>
       </c>
       <c r="R123" t="n">
-        <v>6788610</v>
+        <v>6787879</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13863,7 +13872,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13873,7 +13882,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13900,10 +13909,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129124164</v>
+        <v>129124054</v>
       </c>
       <c r="B124" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13911,21 +13920,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13935,10 +13944,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>421345</v>
+        <v>421423</v>
       </c>
       <c r="R124" t="n">
-        <v>6788394</v>
+        <v>6788261</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13970,7 +13979,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13980,7 +13989,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14007,7 +14016,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129124156</v>
+        <v>129124164</v>
       </c>
       <c r="B125" t="n">
         <v>79035</v>
@@ -14042,10 +14051,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>421351</v>
+        <v>421345</v>
       </c>
       <c r="R125" t="n">
-        <v>6788471</v>
+        <v>6788394</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14077,7 +14086,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14087,7 +14096,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14114,10 +14123,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129124105</v>
+        <v>129124062</v>
       </c>
       <c r="B126" t="n">
-        <v>92857</v>
+        <v>79654</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14125,43 +14134,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>421613</v>
+        <v>421395</v>
       </c>
       <c r="R126" t="n">
-        <v>6788634</v>
+        <v>6788610</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14193,7 +14193,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14203,7 +14203,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14230,50 +14230,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129124121</v>
+        <v>129124156</v>
       </c>
       <c r="B127" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421524</v>
+        <v>421351</v>
       </c>
       <c r="R127" t="n">
-        <v>6788399</v>
+        <v>6788471</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14305,7 +14300,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14315,7 +14310,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14342,45 +14337,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129124082</v>
+        <v>129124121</v>
       </c>
       <c r="B128" t="n">
-        <v>79625</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>421601</v>
+        <v>421524</v>
       </c>
       <c r="R128" t="n">
-        <v>6787830</v>
+        <v>6788399</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14449,45 +14449,50 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129124056</v>
+        <v>129124108</v>
       </c>
       <c r="B129" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>421343</v>
+        <v>421362</v>
       </c>
       <c r="R129" t="n">
-        <v>6788400</v>
+        <v>6788387</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14519,7 +14524,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14529,7 +14534,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14556,50 +14561,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129124108</v>
+        <v>129124056</v>
       </c>
       <c r="B130" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>421362</v>
+        <v>421343</v>
       </c>
       <c r="R130" t="n">
-        <v>6788387</v>
+        <v>6788400</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14989,50 +14989,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129124112</v>
+        <v>129124073</v>
       </c>
       <c r="B134" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>421293</v>
+        <v>421595</v>
       </c>
       <c r="R134" t="n">
-        <v>6788551</v>
+        <v>6787823</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15064,7 +15059,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15074,7 +15069,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15101,45 +15096,50 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129124073</v>
+        <v>129124112</v>
       </c>
       <c r="B135" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>421595</v>
+        <v>421293</v>
       </c>
       <c r="R135" t="n">
-        <v>6787823</v>
+        <v>6788551</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15208,45 +15208,50 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129124057</v>
+        <v>129124088</v>
       </c>
       <c r="B136" t="n">
-        <v>79654</v>
+        <v>56913</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>421312</v>
+        <v>421296</v>
       </c>
       <c r="R136" t="n">
-        <v>6788393</v>
+        <v>6788608</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15278,7 +15283,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15288,7 +15293,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15315,10 +15320,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129124163</v>
+        <v>129124057</v>
       </c>
       <c r="B137" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15326,21 +15331,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15350,10 +15355,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>421454</v>
+        <v>421312</v>
       </c>
       <c r="R137" t="n">
-        <v>6788422</v>
+        <v>6788393</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15385,7 +15390,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15395,7 +15400,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15422,50 +15427,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129124088</v>
+        <v>129124163</v>
       </c>
       <c r="B138" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>421296</v>
+        <v>421454</v>
       </c>
       <c r="R138" t="n">
-        <v>6788608</v>
+        <v>6788422</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15641,50 +15641,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129124109</v>
+        <v>129124140</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>421325</v>
+        <v>421656</v>
       </c>
       <c r="R140" t="n">
-        <v>6788393</v>
+        <v>6787791</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15716,7 +15711,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15726,7 +15721,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15753,10 +15748,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129124140</v>
+        <v>129124068</v>
       </c>
       <c r="B141" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15764,21 +15759,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15788,10 +15783,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>421656</v>
+        <v>421675</v>
       </c>
       <c r="R141" t="n">
-        <v>6787791</v>
+        <v>6787696</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15823,7 +15818,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15833,7 +15828,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15860,7 +15855,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129124068</v>
+        <v>129124065</v>
       </c>
       <c r="B142" t="n">
         <v>79654</v>
@@ -15895,10 +15890,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>421675</v>
+        <v>421530</v>
       </c>
       <c r="R142" t="n">
-        <v>6787696</v>
+        <v>6788679</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15930,7 +15925,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15940,7 +15935,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15967,10 +15962,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129124065</v>
+        <v>129124169</v>
       </c>
       <c r="B143" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15978,21 +15973,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16002,10 +15997,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>421530</v>
+        <v>421618</v>
       </c>
       <c r="R143" t="n">
-        <v>6788679</v>
+        <v>6787872</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16037,7 +16032,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16047,7 +16042,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16074,45 +16069,50 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129124169</v>
+        <v>129124109</v>
       </c>
       <c r="B144" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>421618</v>
+        <v>421325</v>
       </c>
       <c r="R144" t="n">
-        <v>6787872</v>
+        <v>6788393</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16181,10 +16181,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124170</v>
+        <v>129124144</v>
       </c>
       <c r="B145" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16192,21 +16192,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421604</v>
+        <v>421602</v>
       </c>
       <c r="R145" t="n">
-        <v>6787823</v>
+        <v>6787829</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16251,7 +16251,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16288,10 +16288,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124087</v>
+        <v>129124170</v>
       </c>
       <c r="B146" t="n">
-        <v>79130</v>
+        <v>79035</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16299,21 +16299,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16323,10 +16323,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421601</v>
+        <v>421604</v>
       </c>
       <c r="R146" t="n">
-        <v>6787830</v>
+        <v>6787823</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16395,7 +16395,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129124144</v>
+        <v>129124138</v>
       </c>
       <c r="B147" t="n">
         <v>78792</v>
@@ -16430,10 +16430,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>421602</v>
+        <v>421292</v>
       </c>
       <c r="R147" t="n">
-        <v>6787829</v>
+        <v>6788456</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16465,7 +16465,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16475,7 +16475,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16502,10 +16502,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129124138</v>
+        <v>129124087</v>
       </c>
       <c r="B148" t="n">
-        <v>78792</v>
+        <v>79130</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16513,21 +16513,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16537,10 +16537,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421292</v>
+        <v>421601</v>
       </c>
       <c r="R148" t="n">
-        <v>6788456</v>
+        <v>6787830</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16572,7 +16572,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16609,50 +16609,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124106</v>
+        <v>129124078</v>
       </c>
       <c r="B149" t="n">
-        <v>8450</v>
+        <v>79625</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421574</v>
+        <v>421640</v>
       </c>
       <c r="R149" t="n">
-        <v>6788374</v>
+        <v>6788394</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16684,7 +16679,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16694,7 +16689,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16721,50 +16716,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124122</v>
+        <v>129124133</v>
       </c>
       <c r="B150" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421477</v>
+        <v>421633</v>
       </c>
       <c r="R150" t="n">
-        <v>6788422</v>
+        <v>6787841</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16796,7 +16786,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16806,7 +16796,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16833,7 +16823,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124120</v>
+        <v>129124106</v>
       </c>
       <c r="B151" t="n">
         <v>8450</v>
@@ -16864,7 +16854,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -16873,10 +16863,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421520</v>
+        <v>421574</v>
       </c>
       <c r="R151" t="n">
-        <v>6788366</v>
+        <v>6788374</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16908,7 +16898,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16918,7 +16908,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16945,45 +16935,50 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129124133</v>
+        <v>129124122</v>
       </c>
       <c r="B152" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>421633</v>
+        <v>421477</v>
       </c>
       <c r="R152" t="n">
-        <v>6787841</v>
+        <v>6788422</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17015,7 +17010,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17025,7 +17020,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17052,45 +17047,50 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129124078</v>
+        <v>129124120</v>
       </c>
       <c r="B153" t="n">
-        <v>79625</v>
+        <v>8450</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>421640</v>
+        <v>421520</v>
       </c>
       <c r="R153" t="n">
-        <v>6788394</v>
+        <v>6788366</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17592,7 +17592,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129124076</v>
+        <v>129124084</v>
       </c>
       <c r="B158" t="n">
         <v>79625</v>
@@ -17627,10 +17627,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>421240</v>
+        <v>421591</v>
       </c>
       <c r="R158" t="n">
-        <v>6788558</v>
+        <v>6787819</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17672,7 +17672,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17699,7 +17699,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129124084</v>
+        <v>129124076</v>
       </c>
       <c r="B159" t="n">
         <v>79625</v>
@@ -17734,10 +17734,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>421591</v>
+        <v>421240</v>
       </c>
       <c r="R159" t="n">
-        <v>6787819</v>
+        <v>6788558</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129093952</v>
+        <v>129093598</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421399</v>
+        <v>421371</v>
       </c>
       <c r="R19" t="n">
-        <v>6788487</v>
+        <v>6788472</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129093598</v>
+        <v>129093952</v>
       </c>
       <c r="B20" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421371</v>
+        <v>421399</v>
       </c>
       <c r="R20" t="n">
-        <v>6788472</v>
+        <v>6788487</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129094076</v>
+        <v>129093167</v>
       </c>
       <c r="B24" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421379</v>
+        <v>421391</v>
       </c>
       <c r="R24" t="n">
-        <v>6788540</v>
+        <v>6788314</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129093167</v>
+        <v>129094076</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,21 +3224,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421391</v>
+        <v>421379</v>
       </c>
       <c r="R25" t="n">
-        <v>6788314</v>
+        <v>6788540</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -5032,45 +5032,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129093117</v>
+        <v>129094242</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>421391</v>
+        <v>421564</v>
       </c>
       <c r="R42" t="n">
-        <v>6788314</v>
+        <v>6788544</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5139,7 +5144,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129094242</v>
+        <v>129094162</v>
       </c>
       <c r="B43" t="n">
         <v>57720</v>
@@ -5179,10 +5184,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>421564</v>
+        <v>421499</v>
       </c>
       <c r="R43" t="n">
-        <v>6788544</v>
+        <v>6788592</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5251,10 +5256,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129094162</v>
+        <v>129095090</v>
       </c>
       <c r="B44" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5262,16 +5267,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5282,7 +5287,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5291,10 +5296,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>421499</v>
+        <v>421500</v>
       </c>
       <c r="R44" t="n">
-        <v>6788592</v>
+        <v>6788425</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,50 +5368,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129095090</v>
+        <v>129093117</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>421500</v>
+        <v>421391</v>
       </c>
       <c r="R45" t="n">
-        <v>6788425</v>
+        <v>6788314</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6229,10 +6229,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129124182</v>
+        <v>129124160</v>
       </c>
       <c r="B53" t="n">
-        <v>78701</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6240,21 +6240,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>421622</v>
+        <v>421611</v>
       </c>
       <c r="R53" t="n">
-        <v>6788520</v>
+        <v>6788481</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6336,10 +6336,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129124179</v>
+        <v>129124166</v>
       </c>
       <c r="B54" t="n">
-        <v>78701</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>421487</v>
+        <v>421316</v>
       </c>
       <c r="R54" t="n">
-        <v>6788638</v>
+        <v>6788317</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6443,7 +6443,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129124176</v>
+        <v>129124182</v>
       </c>
       <c r="B55" t="n">
         <v>78701</v>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>421338</v>
+        <v>421622</v>
       </c>
       <c r="R55" t="n">
-        <v>6788476</v>
+        <v>6788520</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124160</v>
+        <v>129124179</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>78701</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,21 +6561,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421611</v>
+        <v>421487</v>
       </c>
       <c r="R56" t="n">
-        <v>6788481</v>
+        <v>6788638</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6657,10 +6657,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129124070</v>
+        <v>129124176</v>
       </c>
       <c r="B57" t="n">
-        <v>79654</v>
+        <v>78701</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,21 +6668,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>421616</v>
+        <v>421338</v>
       </c>
       <c r="R57" t="n">
-        <v>6787882</v>
+        <v>6788476</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6764,10 +6764,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129124166</v>
+        <v>129124070</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6775,21 +6775,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>421316</v>
+        <v>421616</v>
       </c>
       <c r="R58" t="n">
-        <v>6788317</v>
+        <v>6787882</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8496,32 +8496,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129124146</v>
+        <v>129124177</v>
       </c>
       <c r="B74" t="n">
-        <v>91687</v>
+        <v>78701</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>421654</v>
+        <v>421318</v>
       </c>
       <c r="R74" t="n">
-        <v>6788448</v>
+        <v>6788511</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8603,32 +8603,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129124145</v>
+        <v>129124146</v>
       </c>
       <c r="B75" t="n">
-        <v>78792</v>
+        <v>91687</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>421591</v>
+        <v>421654</v>
       </c>
       <c r="R75" t="n">
-        <v>6787819</v>
+        <v>6788448</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8710,10 +8710,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124152</v>
+        <v>129124145</v>
       </c>
       <c r="B76" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8721,21 +8721,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421234</v>
+        <v>421591</v>
       </c>
       <c r="R76" t="n">
-        <v>6788411</v>
+        <v>6787819</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8817,10 +8817,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124177</v>
+        <v>129124152</v>
       </c>
       <c r="B77" t="n">
-        <v>78701</v>
+        <v>79035</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421318</v>
+        <v>421234</v>
       </c>
       <c r="R77" t="n">
-        <v>6788511</v>
+        <v>6788411</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -11298,42 +11298,38 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129124104</v>
+        <v>129124110</v>
       </c>
       <c r="B100" t="n">
-        <v>92857</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11342,10 +11338,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>421407</v>
+        <v>421271</v>
       </c>
       <c r="R100" t="n">
-        <v>6788349</v>
+        <v>6788430</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11377,7 +11373,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11387,7 +11383,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11414,10 +11410,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129124154</v>
+        <v>129124104</v>
       </c>
       <c r="B101" t="n">
-        <v>79035</v>
+        <v>92857</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11425,34 +11421,43 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>421303</v>
+        <v>421407</v>
       </c>
       <c r="R101" t="n">
-        <v>6788456</v>
+        <v>6788349</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11484,7 +11489,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11494,7 +11499,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11521,7 +11526,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129124147</v>
+        <v>129124154</v>
       </c>
       <c r="B102" t="n">
         <v>79035</v>
@@ -11556,10 +11561,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>421437</v>
+        <v>421303</v>
       </c>
       <c r="R102" t="n">
-        <v>6788275</v>
+        <v>6788456</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11591,7 +11596,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11601,7 +11606,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11628,50 +11633,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129124110</v>
+        <v>129124147</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>421271</v>
+        <v>421437</v>
       </c>
       <c r="R103" t="n">
-        <v>6788430</v>
+        <v>6788275</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11740,45 +11740,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129124165</v>
+        <v>129124127</v>
       </c>
       <c r="B104" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>421340</v>
+        <v>421630</v>
       </c>
       <c r="R104" t="n">
-        <v>6788389</v>
+        <v>6787815</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11810,7 +11815,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11820,7 +11825,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11847,10 +11852,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129124071</v>
+        <v>129124081</v>
       </c>
       <c r="B105" t="n">
-        <v>79654</v>
+        <v>79625</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11858,21 +11863,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11882,10 +11887,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>421598</v>
+        <v>421592</v>
       </c>
       <c r="R105" t="n">
-        <v>6787863</v>
+        <v>6787842</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11917,7 +11922,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11927,7 +11932,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11954,10 +11959,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124141</v>
+        <v>129124165</v>
       </c>
       <c r="B106" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11965,21 +11970,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11989,10 +11994,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421616</v>
+        <v>421340</v>
       </c>
       <c r="R106" t="n">
-        <v>6787883</v>
+        <v>6788389</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12024,7 +12029,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12034,7 +12039,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12061,10 +12066,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129124081</v>
+        <v>129124071</v>
       </c>
       <c r="B107" t="n">
-        <v>79625</v>
+        <v>79654</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12072,21 +12077,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12096,10 +12101,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>421592</v>
+        <v>421598</v>
       </c>
       <c r="R107" t="n">
-        <v>6787842</v>
+        <v>6787863</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12131,7 +12136,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12141,7 +12146,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12168,50 +12173,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129124127</v>
+        <v>129124141</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>421630</v>
+        <v>421616</v>
       </c>
       <c r="R108" t="n">
-        <v>6787815</v>
+        <v>6787883</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14668,45 +14668,50 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129124178</v>
+        <v>129124112</v>
       </c>
       <c r="B131" t="n">
-        <v>78701</v>
+        <v>8450</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>421235</v>
+        <v>421293</v>
       </c>
       <c r="R131" t="n">
-        <v>6788559</v>
+        <v>6788551</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14738,7 +14743,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14748,7 +14753,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14775,7 +14780,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129124180</v>
+        <v>129124178</v>
       </c>
       <c r="B132" t="n">
         <v>78701</v>
@@ -14810,10 +14815,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>421501</v>
+        <v>421235</v>
       </c>
       <c r="R132" t="n">
-        <v>6788671</v>
+        <v>6788559</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14845,7 +14850,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14855,7 +14860,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14882,10 +14887,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129124155</v>
+        <v>129124180</v>
       </c>
       <c r="B133" t="n">
-        <v>79035</v>
+        <v>78701</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14893,21 +14898,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14917,10 +14922,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>421354</v>
+        <v>421501</v>
       </c>
       <c r="R133" t="n">
-        <v>6788463</v>
+        <v>6788671</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14952,7 +14957,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14962,7 +14967,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14989,10 +14994,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129124073</v>
+        <v>129124155</v>
       </c>
       <c r="B134" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15000,21 +15005,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15024,10 +15029,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>421595</v>
+        <v>421354</v>
       </c>
       <c r="R134" t="n">
-        <v>6787823</v>
+        <v>6788463</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15059,7 +15064,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15069,7 +15074,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15096,50 +15101,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129124112</v>
+        <v>129124073</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>421293</v>
+        <v>421595</v>
       </c>
       <c r="R135" t="n">
-        <v>6788551</v>
+        <v>6787823</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15641,45 +15641,50 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129124140</v>
+        <v>129124109</v>
       </c>
       <c r="B140" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>421656</v>
+        <v>421325</v>
       </c>
       <c r="R140" t="n">
-        <v>6787791</v>
+        <v>6788393</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15711,7 +15716,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15721,7 +15726,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15748,10 +15753,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129124068</v>
+        <v>129124140</v>
       </c>
       <c r="B141" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15759,21 +15764,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15783,10 +15788,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>421675</v>
+        <v>421656</v>
       </c>
       <c r="R141" t="n">
-        <v>6787696</v>
+        <v>6787791</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15818,7 +15823,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15828,7 +15833,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15855,7 +15860,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129124065</v>
+        <v>129124068</v>
       </c>
       <c r="B142" t="n">
         <v>79654</v>
@@ -15890,10 +15895,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>421530</v>
+        <v>421675</v>
       </c>
       <c r="R142" t="n">
-        <v>6788679</v>
+        <v>6787696</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15925,7 +15930,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15935,7 +15940,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15962,10 +15967,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129124169</v>
+        <v>129124065</v>
       </c>
       <c r="B143" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15973,21 +15978,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15997,10 +16002,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>421618</v>
+        <v>421530</v>
       </c>
       <c r="R143" t="n">
-        <v>6787872</v>
+        <v>6788679</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16032,7 +16037,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16042,7 +16047,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16069,50 +16074,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129124109</v>
+        <v>129124169</v>
       </c>
       <c r="B144" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>421325</v>
+        <v>421618</v>
       </c>
       <c r="R144" t="n">
-        <v>6788393</v>
+        <v>6787872</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129093598</v>
+        <v>129093952</v>
       </c>
       <c r="B19" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421371</v>
+        <v>421399</v>
       </c>
       <c r="R19" t="n">
-        <v>6788472</v>
+        <v>6788487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129093952</v>
+        <v>129093598</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421399</v>
+        <v>421371</v>
       </c>
       <c r="R20" t="n">
-        <v>6788487</v>
+        <v>6788472</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,32 +2785,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129093188</v>
+        <v>129094196</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421407</v>
+        <v>421526</v>
       </c>
       <c r="R21" t="n">
-        <v>6788409</v>
+        <v>6788587</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129093043</v>
+        <v>129093188</v>
       </c>
       <c r="B22" t="n">
         <v>79035</v>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421355</v>
+        <v>421407</v>
       </c>
       <c r="R22" t="n">
-        <v>6788265</v>
+        <v>6788409</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2999,32 +2999,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129094196</v>
+        <v>129093043</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421526</v>
+        <v>421355</v>
       </c>
       <c r="R23" t="n">
-        <v>6788587</v>
+        <v>6788265</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129093086</v>
+        <v>129093018</v>
       </c>
       <c r="B30" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3759,21 +3759,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421380</v>
+        <v>421341</v>
       </c>
       <c r="R30" t="n">
-        <v>6788287</v>
+        <v>6788261</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3855,7 +3855,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129093018</v>
+        <v>129094179</v>
       </c>
       <c r="B31" t="n">
         <v>79035</v>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421341</v>
+        <v>421509</v>
       </c>
       <c r="R31" t="n">
-        <v>6788261</v>
+        <v>6788597</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3962,10 +3962,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129094179</v>
+        <v>129093086</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3973,21 +3973,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>421509</v>
+        <v>421380</v>
       </c>
       <c r="R32" t="n">
-        <v>6788597</v>
+        <v>6788287</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129094072</v>
+        <v>129095256</v>
       </c>
       <c r="B34" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421379</v>
+        <v>421440</v>
       </c>
       <c r="R34" t="n">
-        <v>6788540</v>
+        <v>6788407</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129095256</v>
+        <v>129094072</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4294,21 +4294,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>421440</v>
+        <v>421379</v>
       </c>
       <c r="R35" t="n">
-        <v>6788407</v>
+        <v>6788540</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5903,45 +5903,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129094103</v>
+        <v>129095582</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>58093</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>421421</v>
+        <v>421342</v>
       </c>
       <c r="R50" t="n">
-        <v>6788547</v>
+        <v>6788310</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6010,50 +6015,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129095582</v>
+        <v>129094103</v>
       </c>
       <c r="B51" t="n">
-        <v>58093</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>421342</v>
+        <v>421421</v>
       </c>
       <c r="R51" t="n">
-        <v>6788310</v>
+        <v>6788547</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6443,10 +6443,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129124182</v>
+        <v>129124070</v>
       </c>
       <c r="B55" t="n">
-        <v>78701</v>
+        <v>79654</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6454,21 +6454,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>421622</v>
+        <v>421616</v>
       </c>
       <c r="R55" t="n">
-        <v>6788520</v>
+        <v>6787882</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124179</v>
+        <v>129124130</v>
       </c>
       <c r="B56" t="n">
-        <v>78701</v>
+        <v>78793</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,21 +6561,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421487</v>
+        <v>421354</v>
       </c>
       <c r="R56" t="n">
-        <v>6788638</v>
+        <v>6788463</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6657,7 +6657,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129124176</v>
+        <v>129124182</v>
       </c>
       <c r="B57" t="n">
         <v>78701</v>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>421338</v>
+        <v>421622</v>
       </c>
       <c r="R57" t="n">
-        <v>6788476</v>
+        <v>6788520</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6764,10 +6764,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129124070</v>
+        <v>129124179</v>
       </c>
       <c r="B58" t="n">
-        <v>79654</v>
+        <v>78701</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6775,21 +6775,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>421616</v>
+        <v>421487</v>
       </c>
       <c r="R58" t="n">
-        <v>6787882</v>
+        <v>6788638</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129124130</v>
+        <v>129124176</v>
       </c>
       <c r="B59" t="n">
-        <v>78793</v>
+        <v>78701</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,21 +6882,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>421354</v>
+        <v>421338</v>
       </c>
       <c r="R59" t="n">
-        <v>6788463</v>
+        <v>6788476</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6978,45 +6978,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129124061</v>
+        <v>129124124</v>
       </c>
       <c r="B60" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>421238</v>
+        <v>421440</v>
       </c>
       <c r="R60" t="n">
-        <v>6788555</v>
+        <v>6788409</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7048,7 +7053,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7058,7 +7063,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7085,10 +7090,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129124149</v>
+        <v>129124131</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7096,21 +7101,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7120,10 +7125,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>421376</v>
+        <v>421659</v>
       </c>
       <c r="R61" t="n">
-        <v>6788380</v>
+        <v>6787750</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7155,7 +7160,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7165,7 +7170,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7192,10 +7197,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129124142</v>
+        <v>129124149</v>
       </c>
       <c r="B62" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7203,21 +7208,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7227,10 +7232,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>421594</v>
+        <v>421376</v>
       </c>
       <c r="R62" t="n">
-        <v>6787870</v>
+        <v>6788380</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7262,7 +7267,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7272,7 +7277,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7299,10 +7304,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129124151</v>
+        <v>129124061</v>
       </c>
       <c r="B63" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7310,21 +7315,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7334,10 +7339,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>421275</v>
+        <v>421238</v>
       </c>
       <c r="R63" t="n">
-        <v>6788430</v>
+        <v>6788555</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7369,7 +7374,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7379,7 +7384,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7406,50 +7411,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129124124</v>
+        <v>129124142</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>421440</v>
+        <v>421594</v>
       </c>
       <c r="R64" t="n">
-        <v>6788409</v>
+        <v>6787870</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7518,10 +7518,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129124131</v>
+        <v>129124151</v>
       </c>
       <c r="B65" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7529,21 +7529,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>421659</v>
+        <v>421275</v>
       </c>
       <c r="R65" t="n">
-        <v>6787750</v>
+        <v>6788430</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7625,32 +7625,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129124173</v>
+        <v>129124074</v>
       </c>
       <c r="B66" t="n">
-        <v>92819</v>
+        <v>79625</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>421621</v>
+        <v>421236</v>
       </c>
       <c r="R66" t="n">
-        <v>6787838</v>
+        <v>6788559</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7705,7 +7705,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På stubbe med 6 brandljud</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7732,45 +7737,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129124058</v>
+        <v>129124114</v>
       </c>
       <c r="B67" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>421246</v>
+        <v>421399</v>
       </c>
       <c r="R67" t="n">
-        <v>6788416</v>
+        <v>6788567</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7802,7 +7812,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7812,7 +7822,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7839,45 +7849,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129124059</v>
+        <v>129124115</v>
       </c>
       <c r="B68" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>421354</v>
+        <v>421608</v>
       </c>
       <c r="R68" t="n">
-        <v>6788463</v>
+        <v>6788661</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7909,7 +7924,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7919,7 +7934,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7946,32 +7961,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129124051</v>
+        <v>129124173</v>
       </c>
       <c r="B69" t="n">
-        <v>79654</v>
+        <v>92819</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7981,10 +7996,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>421392</v>
+        <v>421621</v>
       </c>
       <c r="R69" t="n">
-        <v>6788226</v>
+        <v>6787838</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8016,7 +8031,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8026,7 +8041,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8053,10 +8068,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129124187</v>
+        <v>129124058</v>
       </c>
       <c r="B70" t="n">
-        <v>78438</v>
+        <v>79654</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8064,21 +8079,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8088,10 +8103,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>421639</v>
+        <v>421246</v>
       </c>
       <c r="R70" t="n">
-        <v>6788393</v>
+        <v>6788416</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8123,7 +8138,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8133,7 +8148,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8160,50 +8175,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124114</v>
+        <v>129124059</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>421399</v>
+        <v>421354</v>
       </c>
       <c r="R71" t="n">
-        <v>6788567</v>
+        <v>6788463</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8235,7 +8245,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8245,7 +8255,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8272,50 +8282,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124115</v>
+        <v>129124051</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>421608</v>
+        <v>421392</v>
       </c>
       <c r="R72" t="n">
-        <v>6788661</v>
+        <v>6788226</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8347,7 +8352,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8357,7 +8362,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8384,10 +8389,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129124074</v>
+        <v>129124187</v>
       </c>
       <c r="B73" t="n">
-        <v>79625</v>
+        <v>78438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8395,21 +8400,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8419,10 +8424,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>421236</v>
+        <v>421639</v>
       </c>
       <c r="R73" t="n">
-        <v>6788559</v>
+        <v>6788393</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8454,7 +8459,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8464,12 +8469,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På stubbe med 6 brandljud</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8496,10 +8496,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129124177</v>
+        <v>129124103</v>
       </c>
       <c r="B74" t="n">
-        <v>78701</v>
+        <v>78793</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8507,21 +8507,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>421318</v>
+        <v>421618</v>
       </c>
       <c r="R74" t="n">
-        <v>6788511</v>
+        <v>6787832</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8603,32 +8603,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129124146</v>
+        <v>129124145</v>
       </c>
       <c r="B75" t="n">
-        <v>91687</v>
+        <v>78792</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>421654</v>
+        <v>421591</v>
       </c>
       <c r="R75" t="n">
-        <v>6788448</v>
+        <v>6787819</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8710,10 +8710,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124145</v>
+        <v>129124177</v>
       </c>
       <c r="B76" t="n">
-        <v>78792</v>
+        <v>78701</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8721,21 +8721,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421591</v>
+        <v>421318</v>
       </c>
       <c r="R76" t="n">
-        <v>6787819</v>
+        <v>6788511</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8817,32 +8817,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124152</v>
+        <v>129124146</v>
       </c>
       <c r="B77" t="n">
-        <v>79035</v>
+        <v>91687</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421234</v>
+        <v>421654</v>
       </c>
       <c r="R77" t="n">
-        <v>6788411</v>
+        <v>6788448</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8924,10 +8924,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129124103</v>
+        <v>129124152</v>
       </c>
       <c r="B78" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8935,21 +8935,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>421618</v>
+        <v>421234</v>
       </c>
       <c r="R78" t="n">
-        <v>6787832</v>
+        <v>6788411</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9031,10 +9031,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129124143</v>
+        <v>129124090</v>
       </c>
       <c r="B79" t="n">
-        <v>78792</v>
+        <v>91546</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9042,21 +9042,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>421596</v>
+        <v>421576</v>
       </c>
       <c r="R79" t="n">
-        <v>6787835</v>
+        <v>6788373</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9111,7 +9111,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ej märkt med hänsyn</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9138,10 +9143,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129124090</v>
+        <v>129124143</v>
       </c>
       <c r="B80" t="n">
-        <v>91546</v>
+        <v>78792</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9149,21 +9154,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9173,10 +9178,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>421576</v>
+        <v>421596</v>
       </c>
       <c r="R80" t="n">
-        <v>6788373</v>
+        <v>6787835</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9208,7 +9213,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9218,12 +9223,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ej märkt med hänsyn</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9250,7 +9250,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129124168</v>
+        <v>129124157</v>
       </c>
       <c r="B81" t="n">
         <v>79035</v>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>421329</v>
+        <v>421271</v>
       </c>
       <c r="R81" t="n">
-        <v>6788222</v>
+        <v>6788641</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9357,7 +9357,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129124157</v>
+        <v>129124168</v>
       </c>
       <c r="B82" t="n">
         <v>79035</v>
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>421271</v>
+        <v>421329</v>
       </c>
       <c r="R82" t="n">
-        <v>6788641</v>
+        <v>6788222</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9464,10 +9464,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129124167</v>
+        <v>129124134</v>
       </c>
       <c r="B83" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9475,21 +9475,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9499,10 +9499,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>421342</v>
+        <v>421616</v>
       </c>
       <c r="R83" t="n">
-        <v>6788261</v>
+        <v>6787882</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9571,10 +9571,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129124148</v>
+        <v>129124129</v>
       </c>
       <c r="B84" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9582,21 +9582,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>421395</v>
+        <v>421292</v>
       </c>
       <c r="R84" t="n">
-        <v>6788374</v>
+        <v>6788456</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9678,10 +9678,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129124134</v>
+        <v>129124083</v>
       </c>
       <c r="B85" t="n">
-        <v>78793</v>
+        <v>79625</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9689,21 +9689,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9713,10 +9713,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>421616</v>
+        <v>421598</v>
       </c>
       <c r="R85" t="n">
-        <v>6787882</v>
+        <v>6787829</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9785,10 +9785,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129124083</v>
+        <v>129124167</v>
       </c>
       <c r="B86" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>421598</v>
+        <v>421342</v>
       </c>
       <c r="R86" t="n">
-        <v>6787829</v>
+        <v>6788261</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9892,10 +9892,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129124129</v>
+        <v>129124148</v>
       </c>
       <c r="B87" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9903,21 +9903,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>421292</v>
+        <v>421395</v>
       </c>
       <c r="R87" t="n">
-        <v>6788456</v>
+        <v>6788374</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9999,10 +9999,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129124136</v>
+        <v>129124150</v>
       </c>
       <c r="B88" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10010,21 +10010,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>421598</v>
+        <v>421349</v>
       </c>
       <c r="R88" t="n">
-        <v>6787834</v>
+        <v>6788397</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10106,45 +10106,50 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129124132</v>
+        <v>129124123</v>
       </c>
       <c r="B89" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>421649</v>
+        <v>421446</v>
       </c>
       <c r="R89" t="n">
-        <v>6787778</v>
+        <v>6788421</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10176,7 +10181,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10186,7 +10191,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10213,10 +10218,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129124150</v>
+        <v>129124132</v>
       </c>
       <c r="B90" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10224,21 +10229,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10248,10 +10253,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>421349</v>
+        <v>421649</v>
       </c>
       <c r="R90" t="n">
-        <v>6788397</v>
+        <v>6787778</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10283,7 +10288,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10293,7 +10298,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10320,50 +10325,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129124123</v>
+        <v>129124136</v>
       </c>
       <c r="B91" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>421446</v>
+        <v>421598</v>
       </c>
       <c r="R91" t="n">
-        <v>6788421</v>
+        <v>6787834</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10432,10 +10432,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129124135</v>
+        <v>129124102</v>
       </c>
       <c r="B92" t="n">
-        <v>78793</v>
+        <v>83006</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10443,21 +10443,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>310</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10467,10 +10467,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>421594</v>
+        <v>421694</v>
       </c>
       <c r="R92" t="n">
-        <v>6787870</v>
+        <v>6787682</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10539,10 +10539,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129124128</v>
+        <v>129124096</v>
       </c>
       <c r="B93" t="n">
-        <v>78793</v>
+        <v>57720</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10550,34 +10550,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>421391</v>
+        <v>421596</v>
       </c>
       <c r="R93" t="n">
-        <v>6788209</v>
+        <v>6787836</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10609,7 +10614,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10619,7 +10624,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10646,10 +10651,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129124102</v>
+        <v>129124135</v>
       </c>
       <c r="B94" t="n">
-        <v>83006</v>
+        <v>78793</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10657,21 +10662,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>310</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10681,10 +10686,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>421694</v>
+        <v>421594</v>
       </c>
       <c r="R94" t="n">
-        <v>6787682</v>
+        <v>6787870</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10716,7 +10721,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10726,7 +10731,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10753,10 +10758,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129124096</v>
+        <v>129124128</v>
       </c>
       <c r="B95" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10764,39 +10769,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>421596</v>
+        <v>421391</v>
       </c>
       <c r="R95" t="n">
-        <v>6787836</v>
+        <v>6788209</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10977,10 +10977,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129124060</v>
+        <v>129124153</v>
       </c>
       <c r="B97" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10988,21 +10988,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11012,10 +11012,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>421338</v>
+        <v>421305</v>
       </c>
       <c r="R97" t="n">
-        <v>6788476</v>
+        <v>6788474</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11084,10 +11084,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129124153</v>
+        <v>129124060</v>
       </c>
       <c r="B98" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11095,21 +11095,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11119,10 +11119,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>421305</v>
+        <v>421338</v>
       </c>
       <c r="R98" t="n">
-        <v>6788474</v>
+        <v>6788476</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11298,38 +11298,42 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129124110</v>
+        <v>129124104</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>92857</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11338,10 +11342,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>421271</v>
+        <v>421407</v>
       </c>
       <c r="R100" t="n">
-        <v>6788430</v>
+        <v>6788349</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11373,7 +11377,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11383,7 +11387,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11410,10 +11414,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129124104</v>
+        <v>129124154</v>
       </c>
       <c r="B101" t="n">
-        <v>92857</v>
+        <v>79035</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11421,43 +11425,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>421407</v>
+        <v>421303</v>
       </c>
       <c r="R101" t="n">
-        <v>6788349</v>
+        <v>6788456</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11489,7 +11484,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11499,7 +11494,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11526,7 +11521,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129124154</v>
+        <v>129124147</v>
       </c>
       <c r="B102" t="n">
         <v>79035</v>
@@ -11561,10 +11556,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>421303</v>
+        <v>421437</v>
       </c>
       <c r="R102" t="n">
-        <v>6788456</v>
+        <v>6788275</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11596,7 +11591,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11606,7 +11601,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11633,45 +11628,50 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129124147</v>
+        <v>129124110</v>
       </c>
       <c r="B103" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>421437</v>
+        <v>421271</v>
       </c>
       <c r="R103" t="n">
-        <v>6788275</v>
+        <v>6788430</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11959,10 +11959,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124165</v>
+        <v>129124071</v>
       </c>
       <c r="B106" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11970,21 +11970,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421340</v>
+        <v>421598</v>
       </c>
       <c r="R106" t="n">
-        <v>6788389</v>
+        <v>6787863</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12066,10 +12066,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129124071</v>
+        <v>129124141</v>
       </c>
       <c r="B107" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12077,21 +12077,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12101,10 +12101,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>421598</v>
+        <v>421616</v>
       </c>
       <c r="R107" t="n">
-        <v>6787863</v>
+        <v>6787883</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12173,10 +12173,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129124141</v>
+        <v>129124165</v>
       </c>
       <c r="B108" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12184,21 +12184,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12208,10 +12208,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>421616</v>
+        <v>421340</v>
       </c>
       <c r="R108" t="n">
-        <v>6787883</v>
+        <v>6788389</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12280,45 +12280,50 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129124181</v>
+        <v>129124117</v>
       </c>
       <c r="B109" t="n">
-        <v>78701</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>421537</v>
+        <v>421611</v>
       </c>
       <c r="R109" t="n">
-        <v>6788706</v>
+        <v>6788482</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12350,7 +12355,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12360,7 +12365,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12387,45 +12392,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129124175</v>
+        <v>129124116</v>
       </c>
       <c r="B110" t="n">
-        <v>78701</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>421343</v>
+        <v>421615</v>
       </c>
       <c r="R110" t="n">
-        <v>6788400</v>
+        <v>6788580</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12457,7 +12467,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12467,7 +12477,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12494,45 +12504,50 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129124053</v>
+        <v>129124111</v>
       </c>
       <c r="B111" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>421421</v>
+        <v>421315</v>
       </c>
       <c r="R111" t="n">
-        <v>6788216</v>
+        <v>6788532</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12564,7 +12579,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12574,7 +12589,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12601,10 +12616,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124063</v>
+        <v>129124080</v>
       </c>
       <c r="B112" t="n">
-        <v>79654</v>
+        <v>79625</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12612,21 +12627,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12636,10 +12651,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421442</v>
+        <v>421633</v>
       </c>
       <c r="R112" t="n">
-        <v>6788613</v>
+        <v>6787841</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12671,7 +12686,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12681,7 +12696,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12708,10 +12723,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129124158</v>
+        <v>129124181</v>
       </c>
       <c r="B113" t="n">
-        <v>79035</v>
+        <v>78701</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12719,21 +12734,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12743,10 +12758,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421383</v>
+        <v>421537</v>
       </c>
       <c r="R113" t="n">
-        <v>6788546</v>
+        <v>6788706</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12778,7 +12793,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12788,7 +12803,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12815,10 +12830,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129124139</v>
+        <v>129124175</v>
       </c>
       <c r="B114" t="n">
-        <v>78792</v>
+        <v>78701</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12826,21 +12841,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12850,10 +12865,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>421354</v>
+        <v>421343</v>
       </c>
       <c r="R114" t="n">
-        <v>6788463</v>
+        <v>6788400</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12885,7 +12900,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12895,7 +12910,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12922,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129124052</v>
+        <v>129124159</v>
       </c>
       <c r="B115" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12933,21 +12948,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12957,10 +12972,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>421391</v>
+        <v>421612</v>
       </c>
       <c r="R115" t="n">
-        <v>6788209</v>
+        <v>6788488</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12992,7 +13007,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13002,7 +13017,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13029,10 +13044,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129124159</v>
+        <v>129124053</v>
       </c>
       <c r="B116" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13040,21 +13055,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13064,10 +13079,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>421612</v>
+        <v>421421</v>
       </c>
       <c r="R116" t="n">
-        <v>6788488</v>
+        <v>6788216</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13099,7 +13114,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13109,7 +13124,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13136,50 +13151,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129124117</v>
+        <v>129124063</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>421611</v>
+        <v>421442</v>
       </c>
       <c r="R117" t="n">
-        <v>6788482</v>
+        <v>6788613</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13211,7 +13221,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13221,7 +13231,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13248,50 +13258,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129124116</v>
+        <v>129124139</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>421615</v>
+        <v>421354</v>
       </c>
       <c r="R118" t="n">
-        <v>6788580</v>
+        <v>6788463</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13323,7 +13328,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13333,7 +13338,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13360,50 +13365,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129124111</v>
+        <v>129124052</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>421315</v>
+        <v>421391</v>
       </c>
       <c r="R119" t="n">
-        <v>6788532</v>
+        <v>6788209</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13472,10 +13472,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129124080</v>
+        <v>129124158</v>
       </c>
       <c r="B120" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13483,21 +13483,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13507,10 +13507,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>421633</v>
+        <v>421383</v>
       </c>
       <c r="R120" t="n">
-        <v>6787841</v>
+        <v>6788546</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13579,10 +13579,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129124105</v>
+        <v>129124069</v>
       </c>
       <c r="B121" t="n">
-        <v>92857</v>
+        <v>79654</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13590,43 +13590,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>421613</v>
+        <v>421626</v>
       </c>
       <c r="R121" t="n">
-        <v>6788634</v>
+        <v>6787879</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13658,7 +13649,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13668,7 +13659,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13695,10 +13686,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129124082</v>
+        <v>129124054</v>
       </c>
       <c r="B122" t="n">
-        <v>79625</v>
+        <v>79654</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13706,21 +13697,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13730,10 +13721,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>421601</v>
+        <v>421423</v>
       </c>
       <c r="R122" t="n">
-        <v>6787830</v>
+        <v>6788261</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13765,7 +13756,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13775,7 +13766,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13802,7 +13793,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129124069</v>
+        <v>129124062</v>
       </c>
       <c r="B123" t="n">
         <v>79654</v>
@@ -13837,10 +13828,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>421626</v>
+        <v>421395</v>
       </c>
       <c r="R123" t="n">
-        <v>6787879</v>
+        <v>6788610</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13872,7 +13863,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13882,7 +13873,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13909,10 +13900,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129124054</v>
+        <v>129124105</v>
       </c>
       <c r="B124" t="n">
-        <v>79654</v>
+        <v>92857</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13920,34 +13911,43 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>421423</v>
+        <v>421613</v>
       </c>
       <c r="R124" t="n">
-        <v>6788261</v>
+        <v>6788634</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14016,7 +14016,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129124164</v>
+        <v>129124156</v>
       </c>
       <c r="B125" t="n">
         <v>79035</v>
@@ -14051,10 +14051,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>421345</v>
+        <v>421351</v>
       </c>
       <c r="R125" t="n">
-        <v>6788394</v>
+        <v>6788471</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14086,7 +14086,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14123,10 +14123,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129124062</v>
+        <v>129124164</v>
       </c>
       <c r="B126" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14134,21 +14134,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14158,10 +14158,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>421395</v>
+        <v>421345</v>
       </c>
       <c r="R126" t="n">
-        <v>6788610</v>
+        <v>6788394</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14193,7 +14193,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14203,7 +14203,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14230,45 +14230,50 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129124156</v>
+        <v>129124121</v>
       </c>
       <c r="B127" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421351</v>
+        <v>421524</v>
       </c>
       <c r="R127" t="n">
-        <v>6788471</v>
+        <v>6788399</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14300,7 +14305,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14310,7 +14315,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14337,50 +14342,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129124121</v>
+        <v>129124082</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>79625</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>421524</v>
+        <v>421601</v>
       </c>
       <c r="R128" t="n">
-        <v>6788399</v>
+        <v>6787830</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14449,50 +14449,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129124108</v>
+        <v>129124056</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>421362</v>
+        <v>421343</v>
       </c>
       <c r="R129" t="n">
-        <v>6788387</v>
+        <v>6788400</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14524,7 +14519,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14534,7 +14529,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14561,45 +14556,50 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129124056</v>
+        <v>129124108</v>
       </c>
       <c r="B130" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>421343</v>
+        <v>421362</v>
       </c>
       <c r="R130" t="n">
-        <v>6788400</v>
+        <v>6788387</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14668,50 +14668,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129124112</v>
+        <v>129124178</v>
       </c>
       <c r="B131" t="n">
-        <v>8450</v>
+        <v>78701</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>421293</v>
+        <v>421235</v>
       </c>
       <c r="R131" t="n">
-        <v>6788551</v>
+        <v>6788559</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14743,7 +14738,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14753,7 +14748,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14780,7 +14775,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129124178</v>
+        <v>129124180</v>
       </c>
       <c r="B132" t="n">
         <v>78701</v>
@@ -14815,10 +14810,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>421235</v>
+        <v>421501</v>
       </c>
       <c r="R132" t="n">
-        <v>6788559</v>
+        <v>6788671</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14850,7 +14845,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14860,7 +14855,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14887,10 +14882,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129124180</v>
+        <v>129124073</v>
       </c>
       <c r="B133" t="n">
-        <v>78701</v>
+        <v>79654</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14898,21 +14893,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14922,10 +14917,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>421501</v>
+        <v>421595</v>
       </c>
       <c r="R133" t="n">
-        <v>6788671</v>
+        <v>6787823</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14957,7 +14952,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14967,7 +14962,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15101,45 +15096,50 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129124073</v>
+        <v>129124112</v>
       </c>
       <c r="B135" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>421595</v>
+        <v>421293</v>
       </c>
       <c r="R135" t="n">
-        <v>6787823</v>
+        <v>6788551</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15208,50 +15208,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129124088</v>
+        <v>129124057</v>
       </c>
       <c r="B136" t="n">
-        <v>56913</v>
+        <v>79654</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>421296</v>
+        <v>421312</v>
       </c>
       <c r="R136" t="n">
-        <v>6788608</v>
+        <v>6788393</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15283,7 +15278,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15293,7 +15288,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15320,10 +15315,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129124057</v>
+        <v>129124163</v>
       </c>
       <c r="B137" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15331,21 +15326,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15355,10 +15350,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>421312</v>
+        <v>421454</v>
       </c>
       <c r="R137" t="n">
-        <v>6788393</v>
+        <v>6788422</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15390,7 +15385,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15400,7 +15395,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15427,45 +15422,50 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129124163</v>
+        <v>129124088</v>
       </c>
       <c r="B138" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>421454</v>
+        <v>421296</v>
       </c>
       <c r="R138" t="n">
-        <v>6788422</v>
+        <v>6788608</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15641,50 +15641,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129124109</v>
+        <v>129124169</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>421325</v>
+        <v>421618</v>
       </c>
       <c r="R140" t="n">
-        <v>6788393</v>
+        <v>6787872</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15716,7 +15711,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15726,7 +15721,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16074,45 +16069,50 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129124169</v>
+        <v>129124109</v>
       </c>
       <c r="B144" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>421618</v>
+        <v>421325</v>
       </c>
       <c r="R144" t="n">
-        <v>6787872</v>
+        <v>6788393</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16181,10 +16181,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124144</v>
+        <v>129124170</v>
       </c>
       <c r="B145" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16192,21 +16192,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421602</v>
+        <v>421604</v>
       </c>
       <c r="R145" t="n">
-        <v>6787829</v>
+        <v>6787823</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16251,7 +16251,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16288,10 +16288,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124170</v>
+        <v>129124087</v>
       </c>
       <c r="B146" t="n">
-        <v>79035</v>
+        <v>79130</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16299,21 +16299,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16323,10 +16323,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421604</v>
+        <v>421601</v>
       </c>
       <c r="R146" t="n">
-        <v>6787823</v>
+        <v>6787830</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16395,7 +16395,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129124138</v>
+        <v>129124144</v>
       </c>
       <c r="B147" t="n">
         <v>78792</v>
@@ -16430,10 +16430,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>421292</v>
+        <v>421602</v>
       </c>
       <c r="R147" t="n">
-        <v>6788456</v>
+        <v>6787829</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16465,7 +16465,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16475,7 +16475,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16502,10 +16502,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129124087</v>
+        <v>129124138</v>
       </c>
       <c r="B148" t="n">
-        <v>79130</v>
+        <v>78792</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16513,21 +16513,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16537,10 +16537,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421601</v>
+        <v>421292</v>
       </c>
       <c r="R148" t="n">
-        <v>6787830</v>
+        <v>6788456</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16572,7 +16572,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16609,10 +16609,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124078</v>
+        <v>129124133</v>
       </c>
       <c r="B149" t="n">
-        <v>79625</v>
+        <v>78793</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16620,21 +16620,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16644,10 +16644,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421640</v>
+        <v>421633</v>
       </c>
       <c r="R149" t="n">
-        <v>6788394</v>
+        <v>6787841</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16679,7 +16679,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16716,10 +16716,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124133</v>
+        <v>129124078</v>
       </c>
       <c r="B150" t="n">
-        <v>78793</v>
+        <v>79625</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16727,21 +16727,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16751,10 +16751,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421633</v>
+        <v>421640</v>
       </c>
       <c r="R150" t="n">
-        <v>6787841</v>
+        <v>6788394</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16786,7 +16786,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17592,7 +17592,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129124084</v>
+        <v>129124076</v>
       </c>
       <c r="B158" t="n">
         <v>79625</v>
@@ -17627,10 +17627,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>421591</v>
+        <v>421240</v>
       </c>
       <c r="R158" t="n">
-        <v>6787819</v>
+        <v>6788558</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17672,7 +17672,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17699,7 +17699,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129124076</v>
+        <v>129124084</v>
       </c>
       <c r="B159" t="n">
         <v>79625</v>
@@ -17734,10 +17734,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>421240</v>
+        <v>421591</v>
       </c>
       <c r="R159" t="n">
-        <v>6788558</v>
+        <v>6787819</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129124066</v>
+        <v>129124162</v>
       </c>
       <c r="B2" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421685</v>
+        <v>421720</v>
       </c>
       <c r="R2" t="n">
-        <v>6788462</v>
+        <v>6788450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129124162</v>
+        <v>129124066</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421720</v>
+        <v>421685</v>
       </c>
       <c r="R3" t="n">
-        <v>6788450</v>
+        <v>6788462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>129124171</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129124185</v>
       </c>
       <c r="B5" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129124184</v>
       </c>
       <c r="B6" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>129124067</v>
       </c>
       <c r="B8" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129124161</v>
+        <v>129124183</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>78705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421701</v>
+        <v>421744</v>
       </c>
       <c r="R9" t="n">
-        <v>6788470</v>
+        <v>6788480</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129124183</v>
+        <v>129124161</v>
       </c>
       <c r="B10" t="n">
-        <v>78701</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421744</v>
+        <v>421701</v>
       </c>
       <c r="R10" t="n">
-        <v>6788480</v>
+        <v>6788470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2034,7 +2034,7 @@
         <v>129093027</v>
       </c>
       <c r="B14" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>129094012</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>129093983</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>129095317</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>129094871</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>129093952</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>129093598</v>
       </c>
       <c r="B20" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,32 +2785,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129094196</v>
+        <v>129093188</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421526</v>
+        <v>421407</v>
       </c>
       <c r="R21" t="n">
-        <v>6788587</v>
+        <v>6788409</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129093188</v>
+        <v>129093043</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421407</v>
+        <v>421355</v>
       </c>
       <c r="R22" t="n">
-        <v>6788409</v>
+        <v>6788265</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2999,32 +2999,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129093043</v>
+        <v>129094196</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421355</v>
+        <v>421526</v>
       </c>
       <c r="R23" t="n">
-        <v>6788265</v>
+        <v>6788587</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129093167</v>
+        <v>129094076</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79629</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421391</v>
+        <v>421379</v>
       </c>
       <c r="R24" t="n">
-        <v>6788314</v>
+        <v>6788540</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129094076</v>
+        <v>129093167</v>
       </c>
       <c r="B25" t="n">
-        <v>79625</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,21 +3224,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421379</v>
+        <v>421391</v>
       </c>
       <c r="R25" t="n">
-        <v>6788540</v>
+        <v>6788314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
         <v>129093766</v>
       </c>
       <c r="B26" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>129094170</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>129094800</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129093018</v>
+        <v>129093086</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3759,21 +3759,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421341</v>
+        <v>421380</v>
       </c>
       <c r="R30" t="n">
-        <v>6788261</v>
+        <v>6788287</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129094179</v>
+        <v>129093018</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421509</v>
+        <v>421341</v>
       </c>
       <c r="R31" t="n">
-        <v>6788597</v>
+        <v>6788261</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3962,10 +3962,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129093086</v>
+        <v>129094179</v>
       </c>
       <c r="B32" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3973,21 +3973,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>421380</v>
+        <v>421509</v>
       </c>
       <c r="R32" t="n">
-        <v>6788287</v>
+        <v>6788597</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129095256</v>
+        <v>129094072</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421440</v>
+        <v>421379</v>
       </c>
       <c r="R34" t="n">
-        <v>6788407</v>
+        <v>6788540</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129094072</v>
+        <v>129095256</v>
       </c>
       <c r="B35" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4294,21 +4294,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>421379</v>
+        <v>421440</v>
       </c>
       <c r="R35" t="n">
-        <v>6788540</v>
+        <v>6788407</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4393,7 +4393,7 @@
         <v>129094091</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>129096050</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>129095002</v>
       </c>
       <c r="B38" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>129093008</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>129094542</v>
       </c>
       <c r="B40" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>129093226</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5032,10 +5032,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129094242</v>
+        <v>129095090</v>
       </c>
       <c r="B42" t="n">
-        <v>57720</v>
+        <v>57725</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5043,16 +5043,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5063,7 +5063,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>421564</v>
+        <v>421500</v>
       </c>
       <c r="R42" t="n">
-        <v>6788544</v>
+        <v>6788425</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129094162</v>
+        <v>129094242</v>
       </c>
       <c r="B43" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>421499</v>
+        <v>421564</v>
       </c>
       <c r="R43" t="n">
-        <v>6788592</v>
+        <v>6788544</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5256,10 +5256,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129095090</v>
+        <v>129094162</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>57722</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5267,16 +5267,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5287,7 +5287,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>421500</v>
+        <v>421499</v>
       </c>
       <c r="R44" t="n">
-        <v>6788425</v>
+        <v>6788592</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
         <v>129094551</v>
       </c>
       <c r="B46" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>129093174</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5689,10 +5689,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129093173</v>
+        <v>129095392</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>421390</v>
+        <v>421342</v>
       </c>
       <c r="R48" t="n">
-        <v>6788380</v>
+        <v>6788310</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5796,10 +5796,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129095392</v>
+        <v>129093173</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>421342</v>
+        <v>421390</v>
       </c>
       <c r="R49" t="n">
-        <v>6788310</v>
+        <v>6788380</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5903,50 +5903,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129095582</v>
+        <v>129094103</v>
       </c>
       <c r="B50" t="n">
-        <v>58093</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>421342</v>
+        <v>421421</v>
       </c>
       <c r="R50" t="n">
-        <v>6788310</v>
+        <v>6788547</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6015,45 +6010,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129094103</v>
+        <v>129095582</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>58095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>421421</v>
+        <v>421342</v>
       </c>
       <c r="R51" t="n">
-        <v>6788547</v>
+        <v>6788310</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6125,7 +6125,7 @@
         <v>129094943</v>
       </c>
       <c r="B52" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6229,10 +6229,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129124160</v>
+        <v>129124070</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6240,21 +6240,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>421611</v>
+        <v>421616</v>
       </c>
       <c r="R53" t="n">
-        <v>6788481</v>
+        <v>6787882</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6336,10 +6336,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129124166</v>
+        <v>129124182</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>78705</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>421316</v>
+        <v>421622</v>
       </c>
       <c r="R54" t="n">
-        <v>6788317</v>
+        <v>6788520</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6443,10 +6443,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129124070</v>
+        <v>129124179</v>
       </c>
       <c r="B55" t="n">
-        <v>79654</v>
+        <v>78705</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6454,21 +6454,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>421616</v>
+        <v>421487</v>
       </c>
       <c r="R55" t="n">
-        <v>6787882</v>
+        <v>6788638</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124130</v>
+        <v>129124176</v>
       </c>
       <c r="B56" t="n">
-        <v>78793</v>
+        <v>78705</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,21 +6561,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421354</v>
+        <v>421338</v>
       </c>
       <c r="R56" t="n">
-        <v>6788463</v>
+        <v>6788476</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6657,10 +6657,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129124182</v>
+        <v>129124166</v>
       </c>
       <c r="B57" t="n">
-        <v>78701</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,21 +6668,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>421622</v>
+        <v>421316</v>
       </c>
       <c r="R57" t="n">
-        <v>6788520</v>
+        <v>6788317</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6764,10 +6764,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129124179</v>
+        <v>129124160</v>
       </c>
       <c r="B58" t="n">
-        <v>78701</v>
+        <v>79039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6775,21 +6775,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>421487</v>
+        <v>421611</v>
       </c>
       <c r="R58" t="n">
-        <v>6788638</v>
+        <v>6788481</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129124176</v>
+        <v>129124130</v>
       </c>
       <c r="B59" t="n">
-        <v>78701</v>
+        <v>78797</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,21 +6882,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>421338</v>
+        <v>421354</v>
       </c>
       <c r="R59" t="n">
-        <v>6788476</v>
+        <v>6788463</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6978,50 +6978,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129124124</v>
+        <v>129124061</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79658</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>421440</v>
+        <v>421238</v>
       </c>
       <c r="R60" t="n">
-        <v>6788409</v>
+        <v>6788555</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7053,7 +7048,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7063,7 +7058,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7090,10 +7085,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129124131</v>
+        <v>129124149</v>
       </c>
       <c r="B61" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7101,21 +7096,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7125,10 +7120,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>421659</v>
+        <v>421376</v>
       </c>
       <c r="R61" t="n">
-        <v>6787750</v>
+        <v>6788380</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7160,7 +7155,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7170,7 +7165,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7197,10 +7192,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129124149</v>
+        <v>129124142</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7208,21 +7203,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7232,10 +7227,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>421376</v>
+        <v>421594</v>
       </c>
       <c r="R62" t="n">
-        <v>6788380</v>
+        <v>6787870</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7267,7 +7262,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7277,7 +7272,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7304,10 +7299,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129124061</v>
+        <v>129124151</v>
       </c>
       <c r="B63" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7315,21 +7310,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7339,10 +7334,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>421238</v>
+        <v>421275</v>
       </c>
       <c r="R63" t="n">
-        <v>6788555</v>
+        <v>6788430</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7374,7 +7369,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7384,7 +7379,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7411,45 +7406,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129124142</v>
+        <v>129124124</v>
       </c>
       <c r="B64" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>421594</v>
+        <v>421440</v>
       </c>
       <c r="R64" t="n">
-        <v>6787870</v>
+        <v>6788409</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7518,10 +7518,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129124151</v>
+        <v>129124131</v>
       </c>
       <c r="B65" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7529,21 +7529,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>421275</v>
+        <v>421659</v>
       </c>
       <c r="R65" t="n">
-        <v>6788430</v>
+        <v>6787750</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7625,32 +7625,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129124074</v>
+        <v>129124173</v>
       </c>
       <c r="B66" t="n">
-        <v>79625</v>
+        <v>92826</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>421236</v>
+        <v>421621</v>
       </c>
       <c r="R66" t="n">
-        <v>6788559</v>
+        <v>6787838</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7705,12 +7705,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På stubbe med 6 brandljud</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7737,50 +7732,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129124114</v>
+        <v>129124058</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>79658</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>421399</v>
+        <v>421246</v>
       </c>
       <c r="R67" t="n">
-        <v>6788567</v>
+        <v>6788416</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7812,7 +7802,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7822,7 +7812,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7849,50 +7839,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129124115</v>
+        <v>129124059</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>79658</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>421608</v>
+        <v>421354</v>
       </c>
       <c r="R68" t="n">
-        <v>6788661</v>
+        <v>6788463</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7924,7 +7909,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7934,7 +7919,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7961,32 +7946,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129124173</v>
+        <v>129124051</v>
       </c>
       <c r="B69" t="n">
-        <v>92819</v>
+        <v>79658</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7996,10 +7981,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>421621</v>
+        <v>421392</v>
       </c>
       <c r="R69" t="n">
-        <v>6787838</v>
+        <v>6788226</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8031,7 +8016,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8041,7 +8026,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8068,10 +8053,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129124058</v>
+        <v>129124187</v>
       </c>
       <c r="B70" t="n">
-        <v>79654</v>
+        <v>78442</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8079,21 +8064,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8103,10 +8088,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>421246</v>
+        <v>421639</v>
       </c>
       <c r="R70" t="n">
-        <v>6788416</v>
+        <v>6788393</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8138,7 +8123,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8148,7 +8133,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8175,45 +8160,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124059</v>
+        <v>129124114</v>
       </c>
       <c r="B71" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>421354</v>
+        <v>421399</v>
       </c>
       <c r="R71" t="n">
-        <v>6788463</v>
+        <v>6788567</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8245,7 +8235,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8255,7 +8245,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8282,45 +8272,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124051</v>
+        <v>129124115</v>
       </c>
       <c r="B72" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>421392</v>
+        <v>421608</v>
       </c>
       <c r="R72" t="n">
-        <v>6788226</v>
+        <v>6788661</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8352,7 +8347,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8362,7 +8357,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8389,10 +8384,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129124187</v>
+        <v>129124074</v>
       </c>
       <c r="B73" t="n">
-        <v>78438</v>
+        <v>79629</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8400,21 +8395,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8424,10 +8419,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>421639</v>
+        <v>421236</v>
       </c>
       <c r="R73" t="n">
-        <v>6788393</v>
+        <v>6788559</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8459,7 +8454,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8469,7 +8464,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På stubbe med 6 brandljud</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8496,32 +8496,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129124103</v>
+        <v>129124146</v>
       </c>
       <c r="B74" t="n">
-        <v>78793</v>
+        <v>91694</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>421618</v>
+        <v>421654</v>
       </c>
       <c r="R74" t="n">
-        <v>6787832</v>
+        <v>6788448</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8603,10 +8603,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129124145</v>
+        <v>129124152</v>
       </c>
       <c r="B75" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8614,21 +8614,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>421591</v>
+        <v>421234</v>
       </c>
       <c r="R75" t="n">
-        <v>6787819</v>
+        <v>6788411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8710,10 +8710,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124177</v>
+        <v>129124103</v>
       </c>
       <c r="B76" t="n">
-        <v>78701</v>
+        <v>78797</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8721,21 +8721,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421318</v>
+        <v>421618</v>
       </c>
       <c r="R76" t="n">
-        <v>6788511</v>
+        <v>6787832</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8817,32 +8817,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124146</v>
+        <v>129124177</v>
       </c>
       <c r="B77" t="n">
-        <v>91687</v>
+        <v>78705</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421654</v>
+        <v>421318</v>
       </c>
       <c r="R77" t="n">
-        <v>6788448</v>
+        <v>6788511</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8924,10 +8924,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129124152</v>
+        <v>129124145</v>
       </c>
       <c r="B78" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8935,21 +8935,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>421234</v>
+        <v>421591</v>
       </c>
       <c r="R78" t="n">
-        <v>6788411</v>
+        <v>6787819</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9031,10 +9031,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129124090</v>
+        <v>129124143</v>
       </c>
       <c r="B79" t="n">
-        <v>91546</v>
+        <v>78796</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9042,21 +9042,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>421576</v>
+        <v>421596</v>
       </c>
       <c r="R79" t="n">
-        <v>6788373</v>
+        <v>6787835</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9111,12 +9111,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ej märkt med hänsyn</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9143,10 +9138,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129124143</v>
+        <v>129124090</v>
       </c>
       <c r="B80" t="n">
-        <v>78792</v>
+        <v>91553</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9154,21 +9149,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9178,10 +9173,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>421596</v>
+        <v>421576</v>
       </c>
       <c r="R80" t="n">
-        <v>6787835</v>
+        <v>6788373</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9213,7 +9208,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9223,7 +9218,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ej märkt med hänsyn</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9250,10 +9250,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129124157</v>
+        <v>129124134</v>
       </c>
       <c r="B81" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9261,21 +9261,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>421271</v>
+        <v>421616</v>
       </c>
       <c r="R81" t="n">
-        <v>6788641</v>
+        <v>6787882</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9357,10 +9357,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129124168</v>
+        <v>129124129</v>
       </c>
       <c r="B82" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9368,21 +9368,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>421329</v>
+        <v>421292</v>
       </c>
       <c r="R82" t="n">
-        <v>6788222</v>
+        <v>6788456</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9464,10 +9464,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129124134</v>
+        <v>129124083</v>
       </c>
       <c r="B83" t="n">
-        <v>78793</v>
+        <v>79629</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9475,21 +9475,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9499,10 +9499,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>421616</v>
+        <v>421598</v>
       </c>
       <c r="R83" t="n">
-        <v>6787882</v>
+        <v>6787829</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9571,10 +9571,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129124129</v>
+        <v>129124168</v>
       </c>
       <c r="B84" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9582,21 +9582,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>421292</v>
+        <v>421329</v>
       </c>
       <c r="R84" t="n">
-        <v>6788456</v>
+        <v>6788222</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9678,10 +9678,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129124083</v>
+        <v>129124157</v>
       </c>
       <c r="B85" t="n">
-        <v>79625</v>
+        <v>79039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9689,21 +9689,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9713,10 +9713,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>421598</v>
+        <v>421271</v>
       </c>
       <c r="R85" t="n">
-        <v>6787829</v>
+        <v>6788641</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9788,7 +9788,7 @@
         <v>129124167</v>
       </c>
       <c r="B86" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>129124148</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9999,45 +9999,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129124150</v>
+        <v>129124123</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>421349</v>
+        <v>421446</v>
       </c>
       <c r="R88" t="n">
-        <v>6788397</v>
+        <v>6788421</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10069,7 +10074,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10079,7 +10084,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10106,50 +10111,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129124123</v>
+        <v>129124150</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>421446</v>
+        <v>421349</v>
       </c>
       <c r="R89" t="n">
-        <v>6788421</v>
+        <v>6788397</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10221,7 +10221,7 @@
         <v>129124132</v>
       </c>
       <c r="B90" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>129124136</v>
       </c>
       <c r="B91" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10432,10 +10432,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129124102</v>
+        <v>129124096</v>
       </c>
       <c r="B92" t="n">
-        <v>83006</v>
+        <v>57722</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10443,34 +10443,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>310</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>421694</v>
+        <v>421596</v>
       </c>
       <c r="R92" t="n">
-        <v>6787682</v>
+        <v>6787836</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10502,7 +10507,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10512,7 +10517,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10539,10 +10544,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129124096</v>
+        <v>129124102</v>
       </c>
       <c r="B93" t="n">
-        <v>57720</v>
+        <v>83010</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10550,39 +10555,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>310</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>421596</v>
+        <v>421694</v>
       </c>
       <c r="R93" t="n">
-        <v>6787836</v>
+        <v>6787682</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10654,7 +10654,7 @@
         <v>129124135</v>
       </c>
       <c r="B94" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>129124128</v>
       </c>
       <c r="B95" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10865,50 +10865,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129124125</v>
+        <v>129124153</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>421369</v>
+        <v>421305</v>
       </c>
       <c r="R96" t="n">
-        <v>6788395</v>
+        <v>6788474</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10940,7 +10935,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10950,7 +10945,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10977,10 +10972,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129124153</v>
+        <v>129124060</v>
       </c>
       <c r="B97" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10988,21 +10983,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11012,10 +11007,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>421305</v>
+        <v>421338</v>
       </c>
       <c r="R97" t="n">
-        <v>6788474</v>
+        <v>6788476</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11047,7 +11042,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11057,7 +11052,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11084,10 +11079,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129124060</v>
+        <v>129124072</v>
       </c>
       <c r="B98" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11119,10 +11114,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>421338</v>
+        <v>421591</v>
       </c>
       <c r="R98" t="n">
-        <v>6788476</v>
+        <v>6787819</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11154,7 +11149,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11164,7 +11159,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11191,45 +11186,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129124072</v>
+        <v>129124125</v>
       </c>
       <c r="B99" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>421591</v>
+        <v>421369</v>
       </c>
       <c r="R99" t="n">
-        <v>6787819</v>
+        <v>6788395</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11261,7 +11261,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11298,10 +11298,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129124104</v>
+        <v>129124154</v>
       </c>
       <c r="B100" t="n">
-        <v>92857</v>
+        <v>79039</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11309,43 +11309,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>421407</v>
+        <v>421303</v>
       </c>
       <c r="R100" t="n">
-        <v>6788349</v>
+        <v>6788456</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11377,7 +11368,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11387,7 +11378,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11414,10 +11405,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129124154</v>
+        <v>129124147</v>
       </c>
       <c r="B101" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11449,10 +11440,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>421303</v>
+        <v>421437</v>
       </c>
       <c r="R101" t="n">
-        <v>6788456</v>
+        <v>6788275</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11484,7 +11475,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11494,7 +11485,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11521,45 +11512,50 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129124147</v>
+        <v>129124110</v>
       </c>
       <c r="B102" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>421437</v>
+        <v>421271</v>
       </c>
       <c r="R102" t="n">
-        <v>6788275</v>
+        <v>6788430</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11591,7 +11587,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11601,7 +11597,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11628,38 +11624,42 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129124110</v>
+        <v>129124104</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>92864</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11668,10 +11668,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>421271</v>
+        <v>421407</v>
       </c>
       <c r="R103" t="n">
-        <v>6788430</v>
+        <v>6788349</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11740,50 +11740,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129124127</v>
+        <v>129124071</v>
       </c>
       <c r="B104" t="n">
-        <v>8450</v>
+        <v>79658</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>421630</v>
+        <v>421598</v>
       </c>
       <c r="R104" t="n">
-        <v>6787815</v>
+        <v>6787863</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11815,7 +11810,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11825,7 +11820,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11852,10 +11847,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129124081</v>
+        <v>129124141</v>
       </c>
       <c r="B105" t="n">
-        <v>79625</v>
+        <v>78796</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11863,21 +11858,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11887,10 +11882,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>421592</v>
+        <v>421616</v>
       </c>
       <c r="R105" t="n">
-        <v>6787842</v>
+        <v>6787883</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11922,7 +11917,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11932,7 +11927,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11959,10 +11954,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124071</v>
+        <v>129124081</v>
       </c>
       <c r="B106" t="n">
-        <v>79654</v>
+        <v>79629</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11970,21 +11965,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11994,10 +11989,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421598</v>
+        <v>421592</v>
       </c>
       <c r="R106" t="n">
-        <v>6787863</v>
+        <v>6787842</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12029,7 +12024,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12039,7 +12034,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12066,10 +12061,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129124141</v>
+        <v>129124165</v>
       </c>
       <c r="B107" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12077,21 +12072,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12101,10 +12096,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>421616</v>
+        <v>421340</v>
       </c>
       <c r="R107" t="n">
-        <v>6787883</v>
+        <v>6788389</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12136,7 +12131,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12146,7 +12141,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12173,45 +12168,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129124165</v>
+        <v>129124127</v>
       </c>
       <c r="B108" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>421340</v>
+        <v>421630</v>
       </c>
       <c r="R108" t="n">
-        <v>6788389</v>
+        <v>6787815</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12280,50 +12280,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129124117</v>
+        <v>129124181</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>78705</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>421611</v>
+        <v>421537</v>
       </c>
       <c r="R109" t="n">
-        <v>6788482</v>
+        <v>6788706</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12355,7 +12350,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12365,7 +12360,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12392,50 +12387,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129124116</v>
+        <v>129124175</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>78705</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>421615</v>
+        <v>421343</v>
       </c>
       <c r="R110" t="n">
-        <v>6788580</v>
+        <v>6788400</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12467,7 +12457,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12477,7 +12467,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12504,50 +12494,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129124111</v>
+        <v>129124159</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>421315</v>
+        <v>421612</v>
       </c>
       <c r="R111" t="n">
-        <v>6788532</v>
+        <v>6788488</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12579,7 +12564,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12589,7 +12574,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12616,10 +12601,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124080</v>
+        <v>129124063</v>
       </c>
       <c r="B112" t="n">
-        <v>79625</v>
+        <v>79658</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12627,21 +12612,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12651,10 +12636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421633</v>
+        <v>421442</v>
       </c>
       <c r="R112" t="n">
-        <v>6787841</v>
+        <v>6788613</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12686,7 +12671,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12696,7 +12681,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12723,10 +12708,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129124181</v>
+        <v>129124158</v>
       </c>
       <c r="B113" t="n">
-        <v>78701</v>
+        <v>79039</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12734,21 +12719,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12758,10 +12743,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421537</v>
+        <v>421383</v>
       </c>
       <c r="R113" t="n">
-        <v>6788706</v>
+        <v>6788546</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12793,7 +12778,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12803,7 +12788,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12830,10 +12815,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129124175</v>
+        <v>129124139</v>
       </c>
       <c r="B114" t="n">
-        <v>78701</v>
+        <v>78796</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12841,21 +12826,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12865,10 +12850,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>421343</v>
+        <v>421354</v>
       </c>
       <c r="R114" t="n">
-        <v>6788400</v>
+        <v>6788463</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12900,7 +12885,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12910,7 +12895,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12937,10 +12922,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129124159</v>
+        <v>129124052</v>
       </c>
       <c r="B115" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,21 +12933,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12972,10 +12957,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>421612</v>
+        <v>421391</v>
       </c>
       <c r="R115" t="n">
-        <v>6788488</v>
+        <v>6788209</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13007,7 +12992,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13017,7 +13002,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13047,7 +13032,7 @@
         <v>129124053</v>
       </c>
       <c r="B116" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13151,45 +13136,50 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129124063</v>
+        <v>129124117</v>
       </c>
       <c r="B117" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>421442</v>
+        <v>421611</v>
       </c>
       <c r="R117" t="n">
-        <v>6788613</v>
+        <v>6788482</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13221,7 +13211,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13231,7 +13221,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13258,45 +13248,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129124139</v>
+        <v>129124116</v>
       </c>
       <c r="B118" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>421354</v>
+        <v>421615</v>
       </c>
       <c r="R118" t="n">
-        <v>6788463</v>
+        <v>6788580</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13328,7 +13323,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13338,7 +13333,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13365,45 +13360,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129124052</v>
+        <v>129124111</v>
       </c>
       <c r="B119" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>421391</v>
+        <v>421315</v>
       </c>
       <c r="R119" t="n">
-        <v>6788209</v>
+        <v>6788532</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13472,10 +13472,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129124158</v>
+        <v>129124080</v>
       </c>
       <c r="B120" t="n">
-        <v>79035</v>
+        <v>79629</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13483,21 +13483,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13507,10 +13507,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>421383</v>
+        <v>421633</v>
       </c>
       <c r="R120" t="n">
-        <v>6788546</v>
+        <v>6787841</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13579,10 +13579,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129124069</v>
+        <v>129124164</v>
       </c>
       <c r="B121" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13590,21 +13590,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13614,10 +13614,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>421626</v>
+        <v>421345</v>
       </c>
       <c r="R121" t="n">
-        <v>6787879</v>
+        <v>6788394</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13686,45 +13686,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129124054</v>
+        <v>129124121</v>
       </c>
       <c r="B122" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>421423</v>
+        <v>421524</v>
       </c>
       <c r="R122" t="n">
-        <v>6788261</v>
+        <v>6788399</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13756,7 +13761,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13766,7 +13771,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13793,10 +13798,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129124062</v>
+        <v>129124082</v>
       </c>
       <c r="B123" t="n">
-        <v>79654</v>
+        <v>79629</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13804,21 +13809,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13828,10 +13833,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>421395</v>
+        <v>421601</v>
       </c>
       <c r="R123" t="n">
-        <v>6788610</v>
+        <v>6787830</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13863,7 +13868,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13873,7 +13878,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13903,7 +13908,7 @@
         <v>129124105</v>
       </c>
       <c r="B124" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14016,10 +14021,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129124156</v>
+        <v>129124054</v>
       </c>
       <c r="B125" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14027,21 +14032,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14051,10 +14056,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>421351</v>
+        <v>421423</v>
       </c>
       <c r="R125" t="n">
-        <v>6788471</v>
+        <v>6788261</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14086,7 +14091,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14096,7 +14101,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14123,10 +14128,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129124164</v>
+        <v>129124062</v>
       </c>
       <c r="B126" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14134,21 +14139,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14158,10 +14163,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>421345</v>
+        <v>421395</v>
       </c>
       <c r="R126" t="n">
-        <v>6788394</v>
+        <v>6788610</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14193,7 +14198,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14203,7 +14208,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14230,50 +14235,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129124121</v>
+        <v>129124156</v>
       </c>
       <c r="B127" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421524</v>
+        <v>421351</v>
       </c>
       <c r="R127" t="n">
-        <v>6788399</v>
+        <v>6788471</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14342,10 +14342,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129124082</v>
+        <v>129124069</v>
       </c>
       <c r="B128" t="n">
-        <v>79625</v>
+        <v>79658</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14353,21 +14353,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>421601</v>
+        <v>421626</v>
       </c>
       <c r="R128" t="n">
-        <v>6787830</v>
+        <v>6787879</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14452,7 +14452,7 @@
         <v>129124056</v>
       </c>
       <c r="B129" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>129124178</v>
       </c>
       <c r="B131" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>129124180</v>
       </c>
       <c r="B132" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14882,10 +14882,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129124073</v>
+        <v>129124155</v>
       </c>
       <c r="B133" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>421595</v>
+        <v>421354</v>
       </c>
       <c r="R133" t="n">
-        <v>6787823</v>
+        <v>6788463</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14989,10 +14989,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129124155</v>
+        <v>129124073</v>
       </c>
       <c r="B134" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15000,21 +15000,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15024,10 +15024,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>421354</v>
+        <v>421595</v>
       </c>
       <c r="R134" t="n">
-        <v>6788463</v>
+        <v>6787823</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15059,7 +15059,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15208,10 +15208,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129124057</v>
+        <v>129124077</v>
       </c>
       <c r="B136" t="n">
-        <v>79654</v>
+        <v>79629</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15219,21 +15219,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15243,10 +15243,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>421312</v>
+        <v>421633</v>
       </c>
       <c r="R136" t="n">
-        <v>6788393</v>
+        <v>6788617</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15318,7 +15318,7 @@
         <v>129124163</v>
       </c>
       <c r="B137" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15422,50 +15422,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129124088</v>
+        <v>129124057</v>
       </c>
       <c r="B138" t="n">
-        <v>56913</v>
+        <v>79658</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>421296</v>
+        <v>421312</v>
       </c>
       <c r="R138" t="n">
-        <v>6788608</v>
+        <v>6788393</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15497,7 +15492,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15507,7 +15502,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15534,45 +15529,50 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129124077</v>
+        <v>129124088</v>
       </c>
       <c r="B139" t="n">
-        <v>79625</v>
+        <v>56915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>421633</v>
+        <v>421296</v>
       </c>
       <c r="R139" t="n">
-        <v>6788617</v>
+        <v>6788608</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15641,10 +15641,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129124169</v>
+        <v>129124140</v>
       </c>
       <c r="B140" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15652,21 +15652,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15676,10 +15676,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>421618</v>
+        <v>421656</v>
       </c>
       <c r="R140" t="n">
-        <v>6787872</v>
+        <v>6787791</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15748,10 +15748,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129124140</v>
+        <v>129124068</v>
       </c>
       <c r="B141" t="n">
-        <v>78792</v>
+        <v>79658</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15759,21 +15759,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15783,10 +15783,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>421656</v>
+        <v>421675</v>
       </c>
       <c r="R141" t="n">
-        <v>6787791</v>
+        <v>6787696</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15855,10 +15855,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129124068</v>
+        <v>129124169</v>
       </c>
       <c r="B142" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15866,21 +15866,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15890,10 +15890,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>421675</v>
+        <v>421618</v>
       </c>
       <c r="R142" t="n">
-        <v>6787696</v>
+        <v>6787872</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15925,7 +15925,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15965,7 +15965,7 @@
         <v>129124065</v>
       </c>
       <c r="B143" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16181,10 +16181,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124170</v>
+        <v>129124087</v>
       </c>
       <c r="B145" t="n">
-        <v>79035</v>
+        <v>79134</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16192,21 +16192,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421604</v>
+        <v>421601</v>
       </c>
       <c r="R145" t="n">
-        <v>6787823</v>
+        <v>6787830</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16251,7 +16251,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16288,10 +16288,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124087</v>
+        <v>129124170</v>
       </c>
       <c r="B146" t="n">
-        <v>79130</v>
+        <v>79039</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16299,21 +16299,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16323,10 +16323,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421601</v>
+        <v>421604</v>
       </c>
       <c r="R146" t="n">
-        <v>6787830</v>
+        <v>6787823</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16398,7 +16398,7 @@
         <v>129124144</v>
       </c>
       <c r="B147" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>129124138</v>
       </c>
       <c r="B148" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16609,45 +16609,50 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124133</v>
+        <v>129124106</v>
       </c>
       <c r="B149" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421633</v>
+        <v>421574</v>
       </c>
       <c r="R149" t="n">
-        <v>6787841</v>
+        <v>6788374</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16679,7 +16684,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16689,7 +16694,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16716,45 +16721,50 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124078</v>
+        <v>129124122</v>
       </c>
       <c r="B150" t="n">
-        <v>79625</v>
+        <v>8450</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421640</v>
+        <v>421477</v>
       </c>
       <c r="R150" t="n">
-        <v>6788394</v>
+        <v>6788422</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16786,7 +16796,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16796,7 +16806,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16823,7 +16833,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124106</v>
+        <v>129124120</v>
       </c>
       <c r="B151" t="n">
         <v>8450</v>
@@ -16854,7 +16864,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -16863,10 +16873,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421574</v>
+        <v>421520</v>
       </c>
       <c r="R151" t="n">
-        <v>6788374</v>
+        <v>6788366</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16898,7 +16908,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16908,7 +16918,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16935,50 +16945,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129124122</v>
+        <v>129124133</v>
       </c>
       <c r="B152" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>421477</v>
+        <v>421633</v>
       </c>
       <c r="R152" t="n">
-        <v>6788422</v>
+        <v>6787841</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17010,7 +17015,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17020,7 +17025,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17047,50 +17052,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129124120</v>
+        <v>129124078</v>
       </c>
       <c r="B153" t="n">
-        <v>8450</v>
+        <v>79629</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>421520</v>
+        <v>421640</v>
       </c>
       <c r="R153" t="n">
-        <v>6788366</v>
+        <v>6788394</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17162,7 +17162,7 @@
         <v>129124186</v>
       </c>
       <c r="B154" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>129124064</v>
       </c>
       <c r="B155" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>129124137</v>
       </c>
       <c r="B156" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17592,10 +17592,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129124076</v>
+        <v>129124084</v>
       </c>
       <c r="B158" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17627,10 +17627,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>421240</v>
+        <v>421591</v>
       </c>
       <c r="R158" t="n">
-        <v>6788558</v>
+        <v>6787819</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17672,7 +17672,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17699,10 +17699,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129124084</v>
+        <v>129124076</v>
       </c>
       <c r="B159" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17734,10 +17734,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>421591</v>
+        <v>421240</v>
       </c>
       <c r="R159" t="n">
-        <v>6787819</v>
+        <v>6788558</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -3106,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129094076</v>
+        <v>129093167</v>
       </c>
       <c r="B24" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421379</v>
+        <v>421391</v>
       </c>
       <c r="R24" t="n">
-        <v>6788540</v>
+        <v>6788314</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129093167</v>
+        <v>129094076</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79629</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,21 +3224,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421391</v>
+        <v>421379</v>
       </c>
       <c r="R25" t="n">
-        <v>6788314</v>
+        <v>6788540</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129093174</v>
+        <v>129093173</v>
       </c>
       <c r="B47" t="n">
         <v>79039</v>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>421394</v>
+        <v>421390</v>
       </c>
       <c r="R47" t="n">
-        <v>6788396</v>
+        <v>6788380</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129095392</v>
+        <v>129093174</v>
       </c>
       <c r="B48" t="n">
         <v>79039</v>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>421342</v>
+        <v>421394</v>
       </c>
       <c r="R48" t="n">
-        <v>6788310</v>
+        <v>6788396</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5796,7 +5796,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129093173</v>
+        <v>129095392</v>
       </c>
       <c r="B49" t="n">
         <v>79039</v>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>421390</v>
+        <v>421342</v>
       </c>
       <c r="R49" t="n">
-        <v>6788380</v>
+        <v>6788310</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -8496,32 +8496,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129124146</v>
+        <v>129124152</v>
       </c>
       <c r="B74" t="n">
-        <v>91694</v>
+        <v>79039</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>421654</v>
+        <v>421234</v>
       </c>
       <c r="R74" t="n">
-        <v>6788448</v>
+        <v>6788411</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8603,10 +8603,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129124152</v>
+        <v>129124145</v>
       </c>
       <c r="B75" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8614,21 +8614,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>421234</v>
+        <v>421591</v>
       </c>
       <c r="R75" t="n">
-        <v>6788411</v>
+        <v>6787819</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8710,10 +8710,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124103</v>
+        <v>129124177</v>
       </c>
       <c r="B76" t="n">
-        <v>78797</v>
+        <v>78705</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8721,21 +8721,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421618</v>
+        <v>421318</v>
       </c>
       <c r="R76" t="n">
-        <v>6787832</v>
+        <v>6788511</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8817,32 +8817,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124177</v>
+        <v>129124146</v>
       </c>
       <c r="B77" t="n">
-        <v>78705</v>
+        <v>91694</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421318</v>
+        <v>421654</v>
       </c>
       <c r="R77" t="n">
-        <v>6788511</v>
+        <v>6788448</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8924,10 +8924,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129124145</v>
+        <v>129124103</v>
       </c>
       <c r="B78" t="n">
-        <v>78796</v>
+        <v>78797</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8935,21 +8935,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>421591</v>
+        <v>421618</v>
       </c>
       <c r="R78" t="n">
-        <v>6787819</v>
+        <v>6787832</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9571,7 +9571,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129124168</v>
+        <v>129124157</v>
       </c>
       <c r="B84" t="n">
         <v>79039</v>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>421329</v>
+        <v>421271</v>
       </c>
       <c r="R84" t="n">
-        <v>6788222</v>
+        <v>6788641</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9678,7 +9678,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129124157</v>
+        <v>129124167</v>
       </c>
       <c r="B85" t="n">
         <v>79039</v>
@@ -9713,10 +9713,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>421271</v>
+        <v>421342</v>
       </c>
       <c r="R85" t="n">
-        <v>6788641</v>
+        <v>6788261</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9785,7 +9785,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129124167</v>
+        <v>129124148</v>
       </c>
       <c r="B86" t="n">
         <v>79039</v>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>421342</v>
+        <v>421395</v>
       </c>
       <c r="R86" t="n">
-        <v>6788261</v>
+        <v>6788374</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9892,7 +9892,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129124148</v>
+        <v>129124168</v>
       </c>
       <c r="B87" t="n">
         <v>79039</v>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>421395</v>
+        <v>421329</v>
       </c>
       <c r="R87" t="n">
-        <v>6788374</v>
+        <v>6788222</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10111,10 +10111,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129124150</v>
+        <v>129124132</v>
       </c>
       <c r="B89" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10122,21 +10122,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>421349</v>
+        <v>421649</v>
       </c>
       <c r="R89" t="n">
-        <v>6788397</v>
+        <v>6787778</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10218,7 +10218,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129124132</v>
+        <v>129124136</v>
       </c>
       <c r="B90" t="n">
         <v>78797</v>
@@ -10253,10 +10253,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>421649</v>
+        <v>421598</v>
       </c>
       <c r="R90" t="n">
-        <v>6787778</v>
+        <v>6787834</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10325,10 +10325,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129124136</v>
+        <v>129124150</v>
       </c>
       <c r="B91" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10336,21 +10336,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10360,10 +10360,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>421598</v>
+        <v>421349</v>
       </c>
       <c r="R91" t="n">
-        <v>6787834</v>
+        <v>6788397</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10865,45 +10865,50 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129124153</v>
+        <v>129124125</v>
       </c>
       <c r="B96" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>421305</v>
+        <v>421369</v>
       </c>
       <c r="R96" t="n">
-        <v>6788474</v>
+        <v>6788395</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10935,7 +10940,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10945,7 +10950,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10972,10 +10977,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129124060</v>
+        <v>129124153</v>
       </c>
       <c r="B97" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10983,21 +10988,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11007,10 +11012,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>421338</v>
+        <v>421305</v>
       </c>
       <c r="R97" t="n">
-        <v>6788476</v>
+        <v>6788474</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11042,7 +11047,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11052,7 +11057,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11079,7 +11084,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129124072</v>
+        <v>129124060</v>
       </c>
       <c r="B98" t="n">
         <v>79658</v>
@@ -11114,10 +11119,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>421591</v>
+        <v>421338</v>
       </c>
       <c r="R98" t="n">
-        <v>6787819</v>
+        <v>6788476</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11149,7 +11154,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11159,7 +11164,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11186,50 +11191,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129124125</v>
+        <v>129124072</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>79658</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>421369</v>
+        <v>421591</v>
       </c>
       <c r="R99" t="n">
-        <v>6788395</v>
+        <v>6787819</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11261,7 +11261,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13579,10 +13579,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129124164</v>
+        <v>129124105</v>
       </c>
       <c r="B121" t="n">
-        <v>79039</v>
+        <v>92864</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13590,34 +13590,43 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>421345</v>
+        <v>421613</v>
       </c>
       <c r="R121" t="n">
-        <v>6788394</v>
+        <v>6788634</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13649,7 +13658,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13659,7 +13668,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13686,50 +13695,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129124121</v>
+        <v>129124054</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>79658</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>421524</v>
+        <v>421423</v>
       </c>
       <c r="R122" t="n">
-        <v>6788399</v>
+        <v>6788261</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13761,7 +13765,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13771,7 +13775,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13798,10 +13802,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129124082</v>
+        <v>129124062</v>
       </c>
       <c r="B123" t="n">
-        <v>79629</v>
+        <v>79658</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13809,21 +13813,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13833,10 +13837,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>421601</v>
+        <v>421395</v>
       </c>
       <c r="R123" t="n">
-        <v>6787830</v>
+        <v>6788610</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13868,7 +13872,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13878,7 +13882,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13905,10 +13909,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129124105</v>
+        <v>129124156</v>
       </c>
       <c r="B124" t="n">
-        <v>92864</v>
+        <v>79039</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13916,43 +13920,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>421613</v>
+        <v>421351</v>
       </c>
       <c r="R124" t="n">
-        <v>6788634</v>
+        <v>6788471</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13984,7 +13979,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13994,7 +13989,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14021,7 +14016,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129124054</v>
+        <v>129124069</v>
       </c>
       <c r="B125" t="n">
         <v>79658</v>
@@ -14056,10 +14051,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>421423</v>
+        <v>421626</v>
       </c>
       <c r="R125" t="n">
-        <v>6788261</v>
+        <v>6787879</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14091,7 +14086,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14101,7 +14096,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14128,10 +14123,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129124062</v>
+        <v>129124164</v>
       </c>
       <c r="B126" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14139,21 +14134,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14163,10 +14158,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>421395</v>
+        <v>421345</v>
       </c>
       <c r="R126" t="n">
-        <v>6788610</v>
+        <v>6788394</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14198,7 +14193,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14208,7 +14203,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14235,45 +14230,50 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129124156</v>
+        <v>129124121</v>
       </c>
       <c r="B127" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421351</v>
+        <v>421524</v>
       </c>
       <c r="R127" t="n">
-        <v>6788471</v>
+        <v>6788399</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14342,10 +14342,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129124069</v>
+        <v>129124082</v>
       </c>
       <c r="B128" t="n">
-        <v>79658</v>
+        <v>79629</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14353,21 +14353,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>421626</v>
+        <v>421601</v>
       </c>
       <c r="R128" t="n">
-        <v>6787879</v>
+        <v>6787830</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16181,45 +16181,50 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124087</v>
+        <v>129124106</v>
       </c>
       <c r="B145" t="n">
-        <v>79134</v>
+        <v>8450</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>967</v>
+        <v>106545</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421601</v>
+        <v>421574</v>
       </c>
       <c r="R145" t="n">
-        <v>6787830</v>
+        <v>6788374</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16251,7 +16256,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16261,7 +16266,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16288,45 +16293,50 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124170</v>
+        <v>129124122</v>
       </c>
       <c r="B146" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421604</v>
+        <v>421477</v>
       </c>
       <c r="R146" t="n">
-        <v>6787823</v>
+        <v>6788422</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16358,7 +16368,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16368,7 +16378,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16395,10 +16405,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129124144</v>
+        <v>129124078</v>
       </c>
       <c r="B147" t="n">
-        <v>78796</v>
+        <v>79629</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16406,21 +16416,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16430,10 +16440,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>421602</v>
+        <v>421640</v>
       </c>
       <c r="R147" t="n">
-        <v>6787829</v>
+        <v>6788394</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16465,7 +16475,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16475,7 +16485,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16502,10 +16512,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129124138</v>
+        <v>129124087</v>
       </c>
       <c r="B148" t="n">
-        <v>78796</v>
+        <v>79134</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16513,21 +16523,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16537,10 +16547,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421292</v>
+        <v>421601</v>
       </c>
       <c r="R148" t="n">
-        <v>6788456</v>
+        <v>6787830</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16572,7 +16582,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16582,7 +16592,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16609,50 +16619,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124106</v>
+        <v>129124170</v>
       </c>
       <c r="B149" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421574</v>
+        <v>421604</v>
       </c>
       <c r="R149" t="n">
-        <v>6788374</v>
+        <v>6787823</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16684,7 +16689,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16694,7 +16699,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16721,50 +16726,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124122</v>
+        <v>129124144</v>
       </c>
       <c r="B150" t="n">
-        <v>8450</v>
+        <v>78796</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421477</v>
+        <v>421602</v>
       </c>
       <c r="R150" t="n">
-        <v>6788422</v>
+        <v>6787829</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16833,50 +16833,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124120</v>
+        <v>129124138</v>
       </c>
       <c r="B151" t="n">
-        <v>8450</v>
+        <v>78796</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421520</v>
+        <v>421292</v>
       </c>
       <c r="R151" t="n">
-        <v>6788366</v>
+        <v>6788456</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16908,7 +16903,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16918,7 +16913,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16945,45 +16940,50 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129124133</v>
+        <v>129124120</v>
       </c>
       <c r="B152" t="n">
-        <v>78797</v>
+        <v>8450</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>421633</v>
+        <v>421520</v>
       </c>
       <c r="R152" t="n">
-        <v>6787841</v>
+        <v>6788366</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17052,10 +17052,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129124078</v>
+        <v>129124133</v>
       </c>
       <c r="B153" t="n">
-        <v>79629</v>
+        <v>78797</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17063,21 +17063,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17087,10 +17087,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>421640</v>
+        <v>421633</v>
       </c>
       <c r="R153" t="n">
-        <v>6788394</v>
+        <v>6787841</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17159,10 +17159,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129124186</v>
+        <v>129124064</v>
       </c>
       <c r="B154" t="n">
-        <v>78705</v>
+        <v>79658</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17170,21 +17170,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17194,10 +17194,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>421626</v>
+        <v>421501</v>
       </c>
       <c r="R154" t="n">
-        <v>6787877</v>
+        <v>6788671</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17266,10 +17266,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129124064</v>
+        <v>129124137</v>
       </c>
       <c r="B155" t="n">
-        <v>79658</v>
+        <v>78796</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17277,21 +17277,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17301,10 +17301,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>421501</v>
+        <v>421312</v>
       </c>
       <c r="R155" t="n">
-        <v>6788671</v>
+        <v>6788393</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17346,7 +17346,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17373,10 +17373,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129124137</v>
+        <v>129124186</v>
       </c>
       <c r="B156" t="n">
-        <v>78796</v>
+        <v>78705</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17384,21 +17384,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17408,10 +17408,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>421312</v>
+        <v>421626</v>
       </c>
       <c r="R156" t="n">
-        <v>6788393</v>
+        <v>6787877</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17443,7 +17443,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17453,7 +17453,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD156" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129124162</v>
+        <v>129124066</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421720</v>
+        <v>421685</v>
       </c>
       <c r="R2" t="n">
-        <v>6788450</v>
+        <v>6788462</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129124066</v>
+        <v>129124162</v>
       </c>
       <c r="B3" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421685</v>
+        <v>421720</v>
       </c>
       <c r="R3" t="n">
-        <v>6788462</v>
+        <v>6788450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>129124171</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129094091</v>
+        <v>129096050</v>
       </c>
       <c r="B36" t="n">
         <v>79039</v>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>421397</v>
+        <v>421635</v>
       </c>
       <c r="R36" t="n">
-        <v>6788565</v>
+        <v>6787819</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4497,7 +4497,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096050</v>
+        <v>129094091</v>
       </c>
       <c r="B37" t="n">
         <v>79039</v>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>421635</v>
+        <v>421397</v>
       </c>
       <c r="R37" t="n">
-        <v>6787819</v>
+        <v>6788565</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4711,10 +4711,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129093008</v>
+        <v>129094542</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79629</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4722,21 +4722,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>421318</v>
+        <v>421564</v>
       </c>
       <c r="R39" t="n">
-        <v>6788252</v>
+        <v>6788544</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4818,10 +4818,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129094542</v>
+        <v>129093008</v>
       </c>
       <c r="B40" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4829,21 +4829,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>421564</v>
+        <v>421318</v>
       </c>
       <c r="R40" t="n">
-        <v>6788544</v>
+        <v>6788252</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5032,10 +5032,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129095090</v>
+        <v>129094242</v>
       </c>
       <c r="B42" t="n">
-        <v>57725</v>
+        <v>57722</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5043,16 +5043,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5063,7 +5063,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>421500</v>
+        <v>421564</v>
       </c>
       <c r="R42" t="n">
-        <v>6788425</v>
+        <v>6788544</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5144,7 +5144,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129094242</v>
+        <v>129094162</v>
       </c>
       <c r="B43" t="n">
         <v>57722</v>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>421564</v>
+        <v>421499</v>
       </c>
       <c r="R43" t="n">
-        <v>6788544</v>
+        <v>6788592</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5256,10 +5256,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129094162</v>
+        <v>129095090</v>
       </c>
       <c r="B44" t="n">
-        <v>57722</v>
+        <v>57725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5267,16 +5267,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5287,7 +5287,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>421499</v>
+        <v>421500</v>
       </c>
       <c r="R44" t="n">
-        <v>6788592</v>
+        <v>6788425</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129093174</v>
+        <v>129095392</v>
       </c>
       <c r="B48" t="n">
         <v>79039</v>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>421394</v>
+        <v>421342</v>
       </c>
       <c r="R48" t="n">
-        <v>6788396</v>
+        <v>6788310</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5796,7 +5796,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129095392</v>
+        <v>129093174</v>
       </c>
       <c r="B49" t="n">
         <v>79039</v>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>421342</v>
+        <v>421394</v>
       </c>
       <c r="R49" t="n">
-        <v>6788310</v>
+        <v>6788396</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5903,10 +5903,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129094103</v>
+        <v>129094943</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>79629</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5914,21 +5914,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>421421</v>
+        <v>421534</v>
       </c>
       <c r="R50" t="n">
-        <v>6788547</v>
+        <v>6788452</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6010,50 +6010,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129095582</v>
+        <v>129094103</v>
       </c>
       <c r="B51" t="n">
-        <v>58095</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>421342</v>
+        <v>421421</v>
       </c>
       <c r="R51" t="n">
-        <v>6788310</v>
+        <v>6788547</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6122,45 +6117,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129094943</v>
+        <v>129095582</v>
       </c>
       <c r="B52" t="n">
-        <v>79629</v>
+        <v>58095</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>421534</v>
+        <v>421342</v>
       </c>
       <c r="R52" t="n">
-        <v>6788452</v>
+        <v>6788310</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6229,10 +6229,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129124070</v>
+        <v>129124182</v>
       </c>
       <c r="B53" t="n">
-        <v>79658</v>
+        <v>78705</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6240,21 +6240,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>421616</v>
+        <v>421622</v>
       </c>
       <c r="R53" t="n">
-        <v>6787882</v>
+        <v>6788520</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6336,7 +6336,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129124182</v>
+        <v>129124179</v>
       </c>
       <c r="B54" t="n">
         <v>78705</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>421622</v>
+        <v>421487</v>
       </c>
       <c r="R54" t="n">
-        <v>6788520</v>
+        <v>6788638</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6443,7 +6443,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129124179</v>
+        <v>129124176</v>
       </c>
       <c r="B55" t="n">
         <v>78705</v>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>421487</v>
+        <v>421338</v>
       </c>
       <c r="R55" t="n">
-        <v>6788638</v>
+        <v>6788476</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124176</v>
+        <v>129124160</v>
       </c>
       <c r="B56" t="n">
-        <v>78705</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,21 +6561,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421338</v>
+        <v>421611</v>
       </c>
       <c r="R56" t="n">
-        <v>6788476</v>
+        <v>6788481</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6657,10 +6657,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129124166</v>
+        <v>129124070</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,21 +6668,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>421316</v>
+        <v>421616</v>
       </c>
       <c r="R57" t="n">
-        <v>6788317</v>
+        <v>6787882</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6764,7 +6764,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129124160</v>
+        <v>129124166</v>
       </c>
       <c r="B58" t="n">
         <v>79039</v>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>421611</v>
+        <v>421316</v>
       </c>
       <c r="R58" t="n">
-        <v>6788481</v>
+        <v>6788317</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6978,10 +6978,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129124061</v>
+        <v>129124151</v>
       </c>
       <c r="B60" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,21 +6989,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>421238</v>
+        <v>421275</v>
       </c>
       <c r="R60" t="n">
-        <v>6788555</v>
+        <v>6788430</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7085,10 +7085,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129124149</v>
+        <v>129124061</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7096,21 +7096,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>421376</v>
+        <v>421238</v>
       </c>
       <c r="R61" t="n">
-        <v>6788380</v>
+        <v>6788555</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7192,10 +7192,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129124142</v>
+        <v>129124149</v>
       </c>
       <c r="B62" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7203,21 +7203,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>421594</v>
+        <v>421376</v>
       </c>
       <c r="R62" t="n">
-        <v>6787870</v>
+        <v>6788380</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7299,10 +7299,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129124151</v>
+        <v>129124142</v>
       </c>
       <c r="B63" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7310,21 +7310,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>421275</v>
+        <v>421594</v>
       </c>
       <c r="R63" t="n">
-        <v>6788430</v>
+        <v>6787870</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7628,7 +7628,7 @@
         <v>129124173</v>
       </c>
       <c r="B66" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8603,32 +8603,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129124145</v>
+        <v>129124146</v>
       </c>
       <c r="B75" t="n">
-        <v>78796</v>
+        <v>91701</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>421591</v>
+        <v>421654</v>
       </c>
       <c r="R75" t="n">
-        <v>6787819</v>
+        <v>6788448</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8817,32 +8817,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124146</v>
+        <v>129124145</v>
       </c>
       <c r="B77" t="n">
-        <v>91694</v>
+        <v>78796</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421654</v>
+        <v>421591</v>
       </c>
       <c r="R77" t="n">
-        <v>6788448</v>
+        <v>6787819</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9031,10 +9031,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129124143</v>
+        <v>129124090</v>
       </c>
       <c r="B79" t="n">
-        <v>78796</v>
+        <v>91560</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9042,21 +9042,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>421596</v>
+        <v>421576</v>
       </c>
       <c r="R79" t="n">
-        <v>6787835</v>
+        <v>6788373</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9111,7 +9111,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ej märkt med hänsyn</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9138,10 +9143,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129124090</v>
+        <v>129124143</v>
       </c>
       <c r="B80" t="n">
-        <v>91553</v>
+        <v>78796</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9149,21 +9154,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9173,10 +9178,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>421576</v>
+        <v>421596</v>
       </c>
       <c r="R80" t="n">
-        <v>6788373</v>
+        <v>6787835</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9208,7 +9213,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9218,12 +9223,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ej märkt med hänsyn</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9250,10 +9250,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129124134</v>
+        <v>129124168</v>
       </c>
       <c r="B81" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9261,21 +9261,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>421616</v>
+        <v>421329</v>
       </c>
       <c r="R81" t="n">
-        <v>6787882</v>
+        <v>6788222</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9357,10 +9357,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129124129</v>
+        <v>129124157</v>
       </c>
       <c r="B82" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9368,21 +9368,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>421292</v>
+        <v>421271</v>
       </c>
       <c r="R82" t="n">
-        <v>6788456</v>
+        <v>6788641</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9464,10 +9464,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129124083</v>
+        <v>129124167</v>
       </c>
       <c r="B83" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9475,21 +9475,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9499,10 +9499,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>421598</v>
+        <v>421342</v>
       </c>
       <c r="R83" t="n">
-        <v>6787829</v>
+        <v>6788261</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9571,7 +9571,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129124157</v>
+        <v>129124148</v>
       </c>
       <c r="B84" t="n">
         <v>79039</v>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>421271</v>
+        <v>421395</v>
       </c>
       <c r="R84" t="n">
-        <v>6788641</v>
+        <v>6788374</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9678,10 +9678,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129124167</v>
+        <v>129124083</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>79629</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9689,21 +9689,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9713,10 +9713,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>421342</v>
+        <v>421598</v>
       </c>
       <c r="R85" t="n">
-        <v>6788261</v>
+        <v>6787829</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9785,10 +9785,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129124148</v>
+        <v>129124134</v>
       </c>
       <c r="B86" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>421395</v>
+        <v>421616</v>
       </c>
       <c r="R86" t="n">
-        <v>6788374</v>
+        <v>6787882</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9892,10 +9892,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129124168</v>
+        <v>129124129</v>
       </c>
       <c r="B87" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9903,21 +9903,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>421329</v>
+        <v>421292</v>
       </c>
       <c r="R87" t="n">
-        <v>6788222</v>
+        <v>6788456</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9999,50 +9999,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129124123</v>
+        <v>129124136</v>
       </c>
       <c r="B88" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>421446</v>
+        <v>421598</v>
       </c>
       <c r="R88" t="n">
-        <v>6788421</v>
+        <v>6787834</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10074,7 +10069,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10084,7 +10079,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10218,10 +10213,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129124136</v>
+        <v>129124150</v>
       </c>
       <c r="B90" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10229,21 +10224,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10253,10 +10248,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>421598</v>
+        <v>421349</v>
       </c>
       <c r="R90" t="n">
-        <v>6787834</v>
+        <v>6788397</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10288,7 +10283,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10298,7 +10293,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10325,45 +10320,50 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129124150</v>
+        <v>129124123</v>
       </c>
       <c r="B91" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>421349</v>
+        <v>421446</v>
       </c>
       <c r="R91" t="n">
-        <v>6788397</v>
+        <v>6788421</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10432,10 +10432,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129124096</v>
+        <v>129124102</v>
       </c>
       <c r="B92" t="n">
-        <v>57722</v>
+        <v>83000</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10443,39 +10443,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>310</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>421596</v>
+        <v>421694</v>
       </c>
       <c r="R92" t="n">
-        <v>6787836</v>
+        <v>6787682</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10507,7 +10502,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10517,7 +10512,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10544,10 +10539,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129124102</v>
+        <v>129124096</v>
       </c>
       <c r="B93" t="n">
-        <v>83010</v>
+        <v>57722</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10555,34 +10550,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>310</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>421694</v>
+        <v>421596</v>
       </c>
       <c r="R93" t="n">
-        <v>6787682</v>
+        <v>6787836</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10865,50 +10865,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129124125</v>
+        <v>129124060</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>79658</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>421369</v>
+        <v>421338</v>
       </c>
       <c r="R96" t="n">
-        <v>6788395</v>
+        <v>6788476</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10940,7 +10935,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10950,7 +10945,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11084,7 +11079,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129124060</v>
+        <v>129124072</v>
       </c>
       <c r="B98" t="n">
         <v>79658</v>
@@ -11119,10 +11114,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>421338</v>
+        <v>421591</v>
       </c>
       <c r="R98" t="n">
-        <v>6788476</v>
+        <v>6787819</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11154,7 +11149,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11164,7 +11159,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11191,45 +11186,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129124072</v>
+        <v>129124125</v>
       </c>
       <c r="B99" t="n">
-        <v>79658</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>421591</v>
+        <v>421369</v>
       </c>
       <c r="R99" t="n">
-        <v>6787819</v>
+        <v>6788395</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11261,7 +11261,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11298,10 +11298,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129124154</v>
+        <v>129124104</v>
       </c>
       <c r="B100" t="n">
-        <v>79039</v>
+        <v>92871</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11309,34 +11309,43 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>421303</v>
+        <v>421407</v>
       </c>
       <c r="R100" t="n">
-        <v>6788456</v>
+        <v>6788349</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11368,7 +11377,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11378,7 +11387,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11405,7 +11414,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129124147</v>
+        <v>129124154</v>
       </c>
       <c r="B101" t="n">
         <v>79039</v>
@@ -11440,10 +11449,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>421437</v>
+        <v>421303</v>
       </c>
       <c r="R101" t="n">
-        <v>6788275</v>
+        <v>6788456</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11475,7 +11484,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11485,7 +11494,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11512,50 +11521,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129124110</v>
+        <v>129124147</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>421271</v>
+        <v>421437</v>
       </c>
       <c r="R102" t="n">
-        <v>6788430</v>
+        <v>6788275</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11587,7 +11591,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11597,7 +11601,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11624,42 +11628,38 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129124104</v>
+        <v>129124110</v>
       </c>
       <c r="B103" t="n">
-        <v>92864</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11668,10 +11668,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>421407</v>
+        <v>421271</v>
       </c>
       <c r="R103" t="n">
-        <v>6788349</v>
+        <v>6788430</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11740,10 +11740,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129124071</v>
+        <v>129124165</v>
       </c>
       <c r="B104" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11751,21 +11751,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11775,10 +11775,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>421598</v>
+        <v>421340</v>
       </c>
       <c r="R104" t="n">
-        <v>6787863</v>
+        <v>6788389</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11847,10 +11847,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129124141</v>
+        <v>129124071</v>
       </c>
       <c r="B105" t="n">
-        <v>78796</v>
+        <v>79658</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11858,21 +11858,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>421616</v>
+        <v>421598</v>
       </c>
       <c r="R105" t="n">
-        <v>6787883</v>
+        <v>6787863</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11954,10 +11954,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124081</v>
+        <v>129124141</v>
       </c>
       <c r="B106" t="n">
-        <v>79629</v>
+        <v>78796</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11965,21 +11965,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11989,10 +11989,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421592</v>
+        <v>421616</v>
       </c>
       <c r="R106" t="n">
-        <v>6787842</v>
+        <v>6787883</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12061,45 +12061,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129124165</v>
+        <v>129124127</v>
       </c>
       <c r="B107" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>421340</v>
+        <v>421630</v>
       </c>
       <c r="R107" t="n">
-        <v>6788389</v>
+        <v>6787815</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12131,7 +12136,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12141,7 +12146,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12168,50 +12173,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129124127</v>
+        <v>129124081</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>79629</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>421630</v>
+        <v>421592</v>
       </c>
       <c r="R108" t="n">
-        <v>6787815</v>
+        <v>6787842</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12601,7 +12601,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124063</v>
+        <v>129124053</v>
       </c>
       <c r="B112" t="n">
         <v>79658</v>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421442</v>
+        <v>421421</v>
       </c>
       <c r="R112" t="n">
-        <v>6788613</v>
+        <v>6788216</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12708,10 +12708,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129124158</v>
+        <v>129124063</v>
       </c>
       <c r="B113" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12719,21 +12719,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12743,10 +12743,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421383</v>
+        <v>421442</v>
       </c>
       <c r="R113" t="n">
-        <v>6788546</v>
+        <v>6788613</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12815,10 +12815,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129124139</v>
+        <v>129124158</v>
       </c>
       <c r="B114" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12826,21 +12826,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>421354</v>
+        <v>421383</v>
       </c>
       <c r="R114" t="n">
-        <v>6788463</v>
+        <v>6788546</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12922,10 +12922,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129124052</v>
+        <v>129124139</v>
       </c>
       <c r="B115" t="n">
-        <v>79658</v>
+        <v>78796</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12933,21 +12933,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>421391</v>
+        <v>421354</v>
       </c>
       <c r="R115" t="n">
-        <v>6788209</v>
+        <v>6788463</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13029,7 +13029,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129124053</v>
+        <v>129124052</v>
       </c>
       <c r="B116" t="n">
         <v>79658</v>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>421421</v>
+        <v>421391</v>
       </c>
       <c r="R116" t="n">
-        <v>6788216</v>
+        <v>6788209</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13579,10 +13579,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129124105</v>
+        <v>129124156</v>
       </c>
       <c r="B121" t="n">
-        <v>92864</v>
+        <v>79039</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13590,43 +13590,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>421613</v>
+        <v>421351</v>
       </c>
       <c r="R121" t="n">
-        <v>6788634</v>
+        <v>6788471</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13658,7 +13649,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13668,7 +13659,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13695,10 +13686,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129124054</v>
+        <v>129124105</v>
       </c>
       <c r="B122" t="n">
-        <v>79658</v>
+        <v>92871</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13706,34 +13697,43 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>421423</v>
+        <v>421613</v>
       </c>
       <c r="R122" t="n">
-        <v>6788261</v>
+        <v>6788634</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13765,7 +13765,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13802,45 +13802,50 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129124062</v>
+        <v>129124121</v>
       </c>
       <c r="B123" t="n">
-        <v>79658</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>421395</v>
+        <v>421524</v>
       </c>
       <c r="R123" t="n">
-        <v>6788610</v>
+        <v>6788399</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13872,7 +13877,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13882,7 +13887,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13909,10 +13914,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129124156</v>
+        <v>129124082</v>
       </c>
       <c r="B124" t="n">
-        <v>79039</v>
+        <v>79629</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13920,21 +13925,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13944,10 +13949,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>421351</v>
+        <v>421601</v>
       </c>
       <c r="R124" t="n">
-        <v>6788471</v>
+        <v>6787830</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13979,7 +13984,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13989,7 +13994,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14123,10 +14128,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129124164</v>
+        <v>129124054</v>
       </c>
       <c r="B126" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14134,21 +14139,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14158,10 +14163,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>421345</v>
+        <v>421423</v>
       </c>
       <c r="R126" t="n">
-        <v>6788394</v>
+        <v>6788261</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14193,7 +14198,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14203,7 +14208,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14230,50 +14235,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129124121</v>
+        <v>129124164</v>
       </c>
       <c r="B127" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421524</v>
+        <v>421345</v>
       </c>
       <c r="R127" t="n">
-        <v>6788399</v>
+        <v>6788394</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14342,10 +14342,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129124082</v>
+        <v>129124062</v>
       </c>
       <c r="B128" t="n">
-        <v>79629</v>
+        <v>79658</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14353,21 +14353,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>421601</v>
+        <v>421395</v>
       </c>
       <c r="R128" t="n">
-        <v>6787830</v>
+        <v>6788610</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15208,10 +15208,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129124077</v>
+        <v>129124057</v>
       </c>
       <c r="B136" t="n">
-        <v>79629</v>
+        <v>79658</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15219,21 +15219,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15243,10 +15243,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>421633</v>
+        <v>421312</v>
       </c>
       <c r="R136" t="n">
-        <v>6788617</v>
+        <v>6788393</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15422,45 +15422,50 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129124057</v>
+        <v>129124088</v>
       </c>
       <c r="B138" t="n">
-        <v>79658</v>
+        <v>56915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>421312</v>
+        <v>421296</v>
       </c>
       <c r="R138" t="n">
-        <v>6788393</v>
+        <v>6788608</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15492,7 +15497,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15502,7 +15507,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15529,50 +15534,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129124088</v>
+        <v>129124077</v>
       </c>
       <c r="B139" t="n">
-        <v>56915</v>
+        <v>79629</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>421296</v>
+        <v>421633</v>
       </c>
       <c r="R139" t="n">
-        <v>6788608</v>
+        <v>6788617</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15641,45 +15641,50 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129124140</v>
+        <v>129124109</v>
       </c>
       <c r="B140" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>421656</v>
+        <v>421325</v>
       </c>
       <c r="R140" t="n">
-        <v>6787791</v>
+        <v>6788393</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15711,7 +15716,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15721,7 +15726,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15748,10 +15753,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129124068</v>
+        <v>129124140</v>
       </c>
       <c r="B141" t="n">
-        <v>79658</v>
+        <v>78796</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15759,21 +15764,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15783,10 +15788,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>421675</v>
+        <v>421656</v>
       </c>
       <c r="R141" t="n">
-        <v>6787696</v>
+        <v>6787791</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15818,7 +15823,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15828,7 +15833,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15855,10 +15860,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129124169</v>
+        <v>129124068</v>
       </c>
       <c r="B142" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15866,21 +15871,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15890,10 +15895,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>421618</v>
+        <v>421675</v>
       </c>
       <c r="R142" t="n">
-        <v>6787872</v>
+        <v>6787696</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15925,7 +15930,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15935,7 +15940,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16069,50 +16074,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129124109</v>
+        <v>129124169</v>
       </c>
       <c r="B144" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>421325</v>
+        <v>421618</v>
       </c>
       <c r="R144" t="n">
-        <v>6788393</v>
+        <v>6787872</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16181,50 +16181,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124106</v>
+        <v>129124087</v>
       </c>
       <c r="B145" t="n">
-        <v>8450</v>
+        <v>79134</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>967</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421574</v>
+        <v>421601</v>
       </c>
       <c r="R145" t="n">
-        <v>6788374</v>
+        <v>6787830</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16256,7 +16251,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16266,7 +16261,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16293,7 +16288,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124122</v>
+        <v>129124106</v>
       </c>
       <c r="B146" t="n">
         <v>8450</v>
@@ -16324,7 +16319,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -16333,10 +16328,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421477</v>
+        <v>421574</v>
       </c>
       <c r="R146" t="n">
-        <v>6788422</v>
+        <v>6788374</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16368,7 +16363,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16378,7 +16373,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16405,45 +16400,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129124078</v>
+        <v>129124122</v>
       </c>
       <c r="B147" t="n">
-        <v>79629</v>
+        <v>8450</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>421640</v>
+        <v>421477</v>
       </c>
       <c r="R147" t="n">
-        <v>6788394</v>
+        <v>6788422</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16485,7 +16485,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16512,45 +16512,50 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129124087</v>
+        <v>129124120</v>
       </c>
       <c r="B148" t="n">
-        <v>79134</v>
+        <v>8450</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>967</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421601</v>
+        <v>421520</v>
       </c>
       <c r="R148" t="n">
-        <v>6787830</v>
+        <v>6788366</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16582,7 +16587,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16592,7 +16597,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16619,10 +16624,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124170</v>
+        <v>129124078</v>
       </c>
       <c r="B149" t="n">
-        <v>79039</v>
+        <v>79629</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16630,21 +16635,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16654,10 +16659,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421604</v>
+        <v>421640</v>
       </c>
       <c r="R149" t="n">
-        <v>6787823</v>
+        <v>6788394</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16689,7 +16694,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16699,7 +16704,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16726,10 +16731,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124144</v>
+        <v>129124133</v>
       </c>
       <c r="B150" t="n">
-        <v>78796</v>
+        <v>78797</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16737,21 +16742,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16761,10 +16766,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421602</v>
+        <v>421633</v>
       </c>
       <c r="R150" t="n">
-        <v>6787829</v>
+        <v>6787841</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16796,7 +16801,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16806,7 +16811,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16833,10 +16838,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124138</v>
+        <v>129124170</v>
       </c>
       <c r="B151" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16844,21 +16849,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16868,10 +16873,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421292</v>
+        <v>421604</v>
       </c>
       <c r="R151" t="n">
-        <v>6788456</v>
+        <v>6787823</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16903,7 +16908,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16913,7 +16918,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16940,50 +16945,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129124120</v>
+        <v>129124144</v>
       </c>
       <c r="B152" t="n">
-        <v>8450</v>
+        <v>78796</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>421520</v>
+        <v>421602</v>
       </c>
       <c r="R152" t="n">
-        <v>6788366</v>
+        <v>6787829</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17052,10 +17052,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129124133</v>
+        <v>129124138</v>
       </c>
       <c r="B153" t="n">
-        <v>78797</v>
+        <v>78796</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17063,21 +17063,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17087,10 +17087,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>421633</v>
+        <v>421292</v>
       </c>
       <c r="R153" t="n">
-        <v>6787841</v>
+        <v>6788456</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17159,10 +17159,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129124064</v>
+        <v>129124186</v>
       </c>
       <c r="B154" t="n">
-        <v>79658</v>
+        <v>78705</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17170,21 +17170,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17194,10 +17194,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>421501</v>
+        <v>421626</v>
       </c>
       <c r="R154" t="n">
-        <v>6788671</v>
+        <v>6787877</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17266,45 +17266,50 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129124137</v>
+        <v>129124119</v>
       </c>
       <c r="B155" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>421312</v>
+        <v>421653</v>
       </c>
       <c r="R155" t="n">
-        <v>6788393</v>
+        <v>6788387</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17336,7 +17341,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17346,7 +17351,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17373,10 +17378,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129124186</v>
+        <v>129124084</v>
       </c>
       <c r="B156" t="n">
-        <v>78705</v>
+        <v>79629</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17384,21 +17389,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17408,10 +17413,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>421626</v>
+        <v>421591</v>
       </c>
       <c r="R156" t="n">
-        <v>6787877</v>
+        <v>6787819</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17443,7 +17448,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17453,7 +17458,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17480,50 +17485,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129124119</v>
+        <v>129124076</v>
       </c>
       <c r="B157" t="n">
-        <v>8450</v>
+        <v>79629</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>421653</v>
+        <v>421240</v>
       </c>
       <c r="R157" t="n">
-        <v>6788387</v>
+        <v>6788558</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17555,7 +17555,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17565,7 +17565,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17592,10 +17592,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129124084</v>
+        <v>129124064</v>
       </c>
       <c r="B158" t="n">
-        <v>79629</v>
+        <v>79658</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17603,21 +17603,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17627,10 +17627,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>421591</v>
+        <v>421501</v>
       </c>
       <c r="R158" t="n">
-        <v>6787819</v>
+        <v>6788671</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17672,7 +17672,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17699,10 +17699,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129124076</v>
+        <v>129124137</v>
       </c>
       <c r="B159" t="n">
-        <v>79629</v>
+        <v>78796</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17710,21 +17710,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17734,10 +17734,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>421240</v>
+        <v>421312</v>
       </c>
       <c r="R159" t="n">
-        <v>6788558</v>
+        <v>6788393</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129124066</v>
       </c>
       <c r="B2" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129124162</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129124171</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129124185</v>
       </c>
       <c r="B5" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129124184</v>
       </c>
       <c r="B6" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>129124067</v>
       </c>
       <c r="B8" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129124183</v>
+        <v>129124161</v>
       </c>
       <c r="B9" t="n">
-        <v>78705</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421744</v>
+        <v>421701</v>
       </c>
       <c r="R9" t="n">
-        <v>6788480</v>
+        <v>6788470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129124161</v>
+        <v>129124183</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>78707</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421701</v>
+        <v>421744</v>
       </c>
       <c r="R10" t="n">
-        <v>6788470</v>
+        <v>6788480</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2034,7 +2034,7 @@
         <v>129093027</v>
       </c>
       <c r="B14" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129094012</v>
+        <v>129095317</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421379</v>
+        <v>421398</v>
       </c>
       <c r="R15" t="n">
-        <v>6788540</v>
+        <v>6788372</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129093983</v>
+        <v>129094012</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421400</v>
+        <v>421379</v>
       </c>
       <c r="R16" t="n">
-        <v>6788524</v>
+        <v>6788540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129095317</v>
+        <v>129093983</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421398</v>
+        <v>421400</v>
       </c>
       <c r="R17" t="n">
-        <v>6788372</v>
+        <v>6788524</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
         <v>129094871</v>
       </c>
       <c r="B18" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129093952</v>
+        <v>129093598</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421399</v>
+        <v>421371</v>
       </c>
       <c r="R19" t="n">
-        <v>6788487</v>
+        <v>6788472</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129093598</v>
+        <v>129093952</v>
       </c>
       <c r="B20" t="n">
-        <v>79629</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421371</v>
+        <v>421399</v>
       </c>
       <c r="R20" t="n">
-        <v>6788472</v>
+        <v>6788487</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129093188</v>
+        <v>129093202</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>129093043</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129093167</v>
+        <v>129094076</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>79631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421391</v>
+        <v>421379</v>
       </c>
       <c r="R24" t="n">
-        <v>6788314</v>
+        <v>6788540</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129094076</v>
+        <v>129093167</v>
       </c>
       <c r="B25" t="n">
-        <v>79629</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,21 +3224,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421379</v>
+        <v>421391</v>
       </c>
       <c r="R25" t="n">
-        <v>6788540</v>
+        <v>6788314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
         <v>129093766</v>
       </c>
       <c r="B26" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>129094170</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>129094800</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>129093086</v>
       </c>
       <c r="B30" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129093018</v>
+        <v>129094179</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421341</v>
+        <v>421509</v>
       </c>
       <c r="R31" t="n">
-        <v>6788261</v>
+        <v>6788597</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3962,10 +3962,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129094179</v>
+        <v>129093018</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>421509</v>
+        <v>421341</v>
       </c>
       <c r="R32" t="n">
-        <v>6788597</v>
+        <v>6788261</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4179,7 +4179,7 @@
         <v>129094072</v>
       </c>
       <c r="B34" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>129095256</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>129096050</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>129094091</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>129095002</v>
       </c>
       <c r="B38" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4711,10 +4711,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129094542</v>
+        <v>129093008</v>
       </c>
       <c r="B39" t="n">
-        <v>79629</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4722,21 +4722,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>421564</v>
+        <v>421318</v>
       </c>
       <c r="R39" t="n">
-        <v>6788544</v>
+        <v>6788252</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4818,10 +4818,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129093008</v>
+        <v>129094542</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79631</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4829,21 +4829,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>421318</v>
+        <v>421564</v>
       </c>
       <c r="R40" t="n">
-        <v>6788252</v>
+        <v>6788544</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4925,10 +4925,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129093226</v>
+        <v>129095090</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4936,34 +4936,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>421395</v>
+        <v>421500</v>
       </c>
       <c r="R41" t="n">
-        <v>6788438</v>
+        <v>6788425</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5032,10 +5037,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129094242</v>
+        <v>129093226</v>
       </c>
       <c r="B42" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5043,39 +5048,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>421564</v>
+        <v>421395</v>
       </c>
       <c r="R42" t="n">
-        <v>6788544</v>
+        <v>6788438</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5144,50 +5144,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129094162</v>
+        <v>129093117</v>
       </c>
       <c r="B43" t="n">
-        <v>57722</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>421499</v>
+        <v>421391</v>
       </c>
       <c r="R43" t="n">
-        <v>6788592</v>
+        <v>6788314</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5256,10 +5251,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129095090</v>
+        <v>129094242</v>
       </c>
       <c r="B44" t="n">
-        <v>57725</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5267,16 +5262,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5287,7 +5282,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5296,10 +5291,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>421500</v>
+        <v>421564</v>
       </c>
       <c r="R44" t="n">
-        <v>6788425</v>
+        <v>6788544</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5368,45 +5363,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129093117</v>
+        <v>129094162</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>421391</v>
+        <v>421499</v>
       </c>
       <c r="R45" t="n">
-        <v>6788314</v>
+        <v>6788592</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
         <v>129094551</v>
       </c>
       <c r="B46" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>129093173</v>
       </c>
       <c r="B47" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>129095392</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>129093174</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>129094943</v>
       </c>
       <c r="B50" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>129094103</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>129095582</v>
       </c>
       <c r="B52" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>129124182</v>
       </c>
       <c r="B53" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>129124179</v>
       </c>
       <c r="B54" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>129124176</v>
       </c>
       <c r="B55" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6550,10 +6550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124160</v>
+        <v>129124130</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,21 +6561,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421611</v>
+        <v>421354</v>
       </c>
       <c r="R56" t="n">
-        <v>6788481</v>
+        <v>6788463</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6657,10 +6657,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129124070</v>
+        <v>129124160</v>
       </c>
       <c r="B57" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,21 +6668,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>421616</v>
+        <v>421611</v>
       </c>
       <c r="R57" t="n">
-        <v>6787882</v>
+        <v>6788481</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6764,10 +6764,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129124166</v>
+        <v>129124070</v>
       </c>
       <c r="B58" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6775,21 +6775,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>421316</v>
+        <v>421616</v>
       </c>
       <c r="R58" t="n">
-        <v>6788317</v>
+        <v>6787882</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129124130</v>
+        <v>129124166</v>
       </c>
       <c r="B59" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,21 +6882,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>421354</v>
+        <v>421316</v>
       </c>
       <c r="R59" t="n">
-        <v>6788463</v>
+        <v>6788317</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6978,45 +6978,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129124151</v>
+        <v>129124124</v>
       </c>
       <c r="B60" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>421275</v>
+        <v>421440</v>
       </c>
       <c r="R60" t="n">
-        <v>6788430</v>
+        <v>6788409</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7048,7 +7053,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7058,7 +7063,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7088,7 +7093,7 @@
         <v>129124061</v>
       </c>
       <c r="B61" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7195,7 +7200,7 @@
         <v>129124149</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7302,7 +7307,7 @@
         <v>129124142</v>
       </c>
       <c r="B63" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7406,50 +7411,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129124124</v>
+        <v>129124151</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>421440</v>
+        <v>421275</v>
       </c>
       <c r="R64" t="n">
-        <v>6788409</v>
+        <v>6788430</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7521,7 +7521,7 @@
         <v>129124131</v>
       </c>
       <c r="B65" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7625,32 +7625,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129124173</v>
+        <v>129124058</v>
       </c>
       <c r="B66" t="n">
-        <v>92833</v>
+        <v>79660</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>421621</v>
+        <v>421246</v>
       </c>
       <c r="R66" t="n">
-        <v>6787838</v>
+        <v>6788416</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7732,10 +7732,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129124058</v>
+        <v>129124059</v>
       </c>
       <c r="B67" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>421246</v>
+        <v>421354</v>
       </c>
       <c r="R67" t="n">
-        <v>6788416</v>
+        <v>6788463</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7839,10 +7839,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129124059</v>
+        <v>129124051</v>
       </c>
       <c r="B68" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7874,10 +7874,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>421354</v>
+        <v>421392</v>
       </c>
       <c r="R68" t="n">
-        <v>6788463</v>
+        <v>6788226</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7946,10 +7946,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129124051</v>
+        <v>129124187</v>
       </c>
       <c r="B69" t="n">
-        <v>79658</v>
+        <v>78444</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7957,21 +7957,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>421392</v>
+        <v>421639</v>
       </c>
       <c r="R69" t="n">
-        <v>6788226</v>
+        <v>6788393</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8053,10 +8053,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129124187</v>
+        <v>129124074</v>
       </c>
       <c r="B70" t="n">
-        <v>78442</v>
+        <v>79631</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8064,21 +8064,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8088,10 +8088,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>421639</v>
+        <v>421236</v>
       </c>
       <c r="R70" t="n">
-        <v>6788393</v>
+        <v>6788559</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8133,7 +8133,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På stubbe med 6 brandljud</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8160,10 +8165,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124114</v>
+        <v>129124173</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>92835</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8171,39 +8176,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>421399</v>
+        <v>421621</v>
       </c>
       <c r="R71" t="n">
-        <v>6788567</v>
+        <v>6787838</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8272,7 +8272,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124115</v>
+        <v>129124114</v>
       </c>
       <c r="B72" t="n">
         <v>8450</v>
@@ -8312,10 +8312,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>421608</v>
+        <v>421399</v>
       </c>
       <c r="R72" t="n">
-        <v>6788661</v>
+        <v>6788567</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8384,45 +8384,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129124074</v>
+        <v>129124115</v>
       </c>
       <c r="B73" t="n">
-        <v>79629</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>421236</v>
+        <v>421608</v>
       </c>
       <c r="R73" t="n">
-        <v>6788559</v>
+        <v>6788661</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8454,7 +8459,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8464,12 +8469,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På stubbe med 6 brandljud</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8496,10 +8496,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129124152</v>
+        <v>129124177</v>
       </c>
       <c r="B74" t="n">
-        <v>79039</v>
+        <v>78707</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8507,21 +8507,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>421234</v>
+        <v>421318</v>
       </c>
       <c r="R74" t="n">
-        <v>6788411</v>
+        <v>6788511</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8606,7 +8606,7 @@
         <v>129124146</v>
       </c>
       <c r="B75" t="n">
-        <v>91701</v>
+        <v>91703</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8710,10 +8710,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124177</v>
+        <v>129124145</v>
       </c>
       <c r="B76" t="n">
-        <v>78705</v>
+        <v>78798</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8721,21 +8721,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421318</v>
+        <v>421591</v>
       </c>
       <c r="R76" t="n">
-        <v>6788511</v>
+        <v>6787819</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8817,10 +8817,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124145</v>
+        <v>129124152</v>
       </c>
       <c r="B77" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421591</v>
+        <v>421234</v>
       </c>
       <c r="R77" t="n">
-        <v>6787819</v>
+        <v>6788411</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8927,7 +8927,7 @@
         <v>129124103</v>
       </c>
       <c r="B78" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>129124090</v>
       </c>
       <c r="B79" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>129124143</v>
       </c>
       <c r="B80" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>129124168</v>
       </c>
       <c r="B81" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>129124157</v>
       </c>
       <c r="B82" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>129124167</v>
       </c>
       <c r="B83" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>129124148</v>
       </c>
       <c r="B84" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129124083</v>
+        <v>129124134</v>
       </c>
       <c r="B85" t="n">
-        <v>79629</v>
+        <v>78799</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9689,21 +9689,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9713,10 +9713,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>421598</v>
+        <v>421616</v>
       </c>
       <c r="R85" t="n">
-        <v>6787829</v>
+        <v>6787882</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9785,10 +9785,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129124134</v>
+        <v>129124129</v>
       </c>
       <c r="B86" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>421616</v>
+        <v>421292</v>
       </c>
       <c r="R86" t="n">
-        <v>6787882</v>
+        <v>6788456</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9892,10 +9892,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129124129</v>
+        <v>129124083</v>
       </c>
       <c r="B87" t="n">
-        <v>78797</v>
+        <v>79631</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9903,21 +9903,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>421292</v>
+        <v>421598</v>
       </c>
       <c r="R87" t="n">
-        <v>6788456</v>
+        <v>6787829</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9999,10 +9999,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129124136</v>
+        <v>129124150</v>
       </c>
       <c r="B88" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10010,21 +10010,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>421598</v>
+        <v>421349</v>
       </c>
       <c r="R88" t="n">
-        <v>6787834</v>
+        <v>6788397</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10109,7 +10109,7 @@
         <v>129124132</v>
       </c>
       <c r="B89" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129124150</v>
+        <v>129124136</v>
       </c>
       <c r="B90" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10248,10 +10248,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>421349</v>
+        <v>421598</v>
       </c>
       <c r="R90" t="n">
-        <v>6788397</v>
+        <v>6787834</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10435,7 +10435,7 @@
         <v>129124102</v>
       </c>
       <c r="B92" t="n">
-        <v>83000</v>
+        <v>83002</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10539,10 +10539,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129124096</v>
+        <v>129124135</v>
       </c>
       <c r="B93" t="n">
-        <v>57722</v>
+        <v>78799</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10550,39 +10550,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>421596</v>
+        <v>421594</v>
       </c>
       <c r="R93" t="n">
-        <v>6787836</v>
+        <v>6787870</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10614,7 +10609,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10624,7 +10619,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10651,10 +10646,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129124135</v>
+        <v>129124128</v>
       </c>
       <c r="B94" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10686,10 +10681,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>421594</v>
+        <v>421391</v>
       </c>
       <c r="R94" t="n">
-        <v>6787870</v>
+        <v>6788209</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10721,7 +10716,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10731,7 +10726,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10758,10 +10753,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129124128</v>
+        <v>129124096</v>
       </c>
       <c r="B95" t="n">
-        <v>78797</v>
+        <v>57724</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10769,34 +10764,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>421391</v>
+        <v>421596</v>
       </c>
       <c r="R95" t="n">
-        <v>6788209</v>
+        <v>6787836</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10865,10 +10865,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129124060</v>
+        <v>129124153</v>
       </c>
       <c r="B96" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10876,21 +10876,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10900,10 +10900,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>421338</v>
+        <v>421305</v>
       </c>
       <c r="R96" t="n">
-        <v>6788476</v>
+        <v>6788474</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10972,10 +10972,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129124153</v>
+        <v>129124060</v>
       </c>
       <c r="B97" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10983,21 +10983,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>421305</v>
+        <v>421338</v>
       </c>
       <c r="R97" t="n">
-        <v>6788474</v>
+        <v>6788476</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11082,7 +11082,7 @@
         <v>129124072</v>
       </c>
       <c r="B98" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11298,10 +11298,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129124104</v>
+        <v>129124154</v>
       </c>
       <c r="B100" t="n">
-        <v>92871</v>
+        <v>79041</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11309,43 +11309,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>421407</v>
+        <v>421303</v>
       </c>
       <c r="R100" t="n">
-        <v>6788349</v>
+        <v>6788456</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11377,7 +11368,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11387,7 +11378,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11414,10 +11405,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129124154</v>
+        <v>129124147</v>
       </c>
       <c r="B101" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11449,10 +11440,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>421303</v>
+        <v>421437</v>
       </c>
       <c r="R101" t="n">
-        <v>6788456</v>
+        <v>6788275</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11484,7 +11475,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11494,7 +11485,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11521,10 +11512,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129124147</v>
+        <v>129124104</v>
       </c>
       <c r="B102" t="n">
-        <v>79039</v>
+        <v>92873</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11532,34 +11523,43 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>421437</v>
+        <v>421407</v>
       </c>
       <c r="R102" t="n">
-        <v>6788275</v>
+        <v>6788349</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11591,7 +11591,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11740,45 +11740,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129124165</v>
+        <v>129124127</v>
       </c>
       <c r="B104" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>421340</v>
+        <v>421630</v>
       </c>
       <c r="R104" t="n">
-        <v>6788389</v>
+        <v>6787815</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11810,7 +11815,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11820,7 +11825,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11847,10 +11852,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129124071</v>
+        <v>129124165</v>
       </c>
       <c r="B105" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11858,21 +11863,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11882,10 +11887,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>421598</v>
+        <v>421340</v>
       </c>
       <c r="R105" t="n">
-        <v>6787863</v>
+        <v>6788389</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11917,7 +11922,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11927,7 +11932,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11954,10 +11959,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124141</v>
+        <v>129124071</v>
       </c>
       <c r="B106" t="n">
-        <v>78796</v>
+        <v>79660</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11965,21 +11970,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11989,10 +11994,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421616</v>
+        <v>421598</v>
       </c>
       <c r="R106" t="n">
-        <v>6787883</v>
+        <v>6787863</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12024,7 +12029,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12034,7 +12039,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12061,50 +12066,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129124127</v>
+        <v>129124141</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>421630</v>
+        <v>421616</v>
       </c>
       <c r="R107" t="n">
-        <v>6787815</v>
+        <v>6787883</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12176,7 +12176,7 @@
         <v>129124081</v>
       </c>
       <c r="B108" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12280,45 +12280,50 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129124181</v>
+        <v>129124117</v>
       </c>
       <c r="B109" t="n">
-        <v>78705</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>421537</v>
+        <v>421611</v>
       </c>
       <c r="R109" t="n">
-        <v>6788706</v>
+        <v>6788482</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12350,7 +12355,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12360,7 +12365,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12387,45 +12392,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129124175</v>
+        <v>129124116</v>
       </c>
       <c r="B110" t="n">
-        <v>78705</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>421343</v>
+        <v>421615</v>
       </c>
       <c r="R110" t="n">
-        <v>6788400</v>
+        <v>6788580</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12457,7 +12467,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12467,7 +12477,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12494,45 +12504,50 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129124159</v>
+        <v>129124111</v>
       </c>
       <c r="B111" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>421612</v>
+        <v>421315</v>
       </c>
       <c r="R111" t="n">
-        <v>6788488</v>
+        <v>6788532</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12564,7 +12579,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12574,7 +12589,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12601,10 +12616,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124053</v>
+        <v>129124181</v>
       </c>
       <c r="B112" t="n">
-        <v>79658</v>
+        <v>78707</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12612,21 +12627,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12636,10 +12651,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421421</v>
+        <v>421537</v>
       </c>
       <c r="R112" t="n">
-        <v>6788216</v>
+        <v>6788706</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12671,7 +12686,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12681,7 +12696,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12708,10 +12723,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129124063</v>
+        <v>129124175</v>
       </c>
       <c r="B113" t="n">
-        <v>79658</v>
+        <v>78707</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12719,21 +12734,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12743,10 +12758,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421442</v>
+        <v>421343</v>
       </c>
       <c r="R113" t="n">
-        <v>6788613</v>
+        <v>6788400</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12778,7 +12793,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12788,7 +12803,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12815,10 +12830,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129124158</v>
+        <v>129124053</v>
       </c>
       <c r="B114" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12826,21 +12841,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12850,10 +12865,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>421383</v>
+        <v>421421</v>
       </c>
       <c r="R114" t="n">
-        <v>6788546</v>
+        <v>6788216</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12885,7 +12900,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12895,7 +12910,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12922,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129124139</v>
+        <v>129124063</v>
       </c>
       <c r="B115" t="n">
-        <v>78796</v>
+        <v>79660</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12933,21 +12948,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12957,10 +12972,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>421354</v>
+        <v>421442</v>
       </c>
       <c r="R115" t="n">
-        <v>6788463</v>
+        <v>6788613</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12992,7 +13007,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13002,7 +13017,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13029,10 +13044,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129124052</v>
+        <v>129124139</v>
       </c>
       <c r="B116" t="n">
-        <v>79658</v>
+        <v>78798</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13040,21 +13055,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13064,10 +13079,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>421391</v>
+        <v>421354</v>
       </c>
       <c r="R116" t="n">
-        <v>6788209</v>
+        <v>6788463</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13099,7 +13114,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13109,7 +13124,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13136,50 +13151,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129124117</v>
+        <v>129124052</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>421611</v>
+        <v>421391</v>
       </c>
       <c r="R117" t="n">
-        <v>6788482</v>
+        <v>6788209</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13211,7 +13221,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13221,7 +13231,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13248,50 +13258,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129124116</v>
+        <v>129124159</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>421615</v>
+        <v>421612</v>
       </c>
       <c r="R118" t="n">
-        <v>6788580</v>
+        <v>6788488</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13323,7 +13328,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13333,7 +13338,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13360,50 +13365,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129124111</v>
+        <v>129124158</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>421315</v>
+        <v>421383</v>
       </c>
       <c r="R119" t="n">
-        <v>6788532</v>
+        <v>6788546</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13475,7 +13475,7 @@
         <v>129124080</v>
       </c>
       <c r="B120" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13579,10 +13579,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129124156</v>
+        <v>129124069</v>
       </c>
       <c r="B121" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13590,21 +13590,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13614,10 +13614,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>421351</v>
+        <v>421626</v>
       </c>
       <c r="R121" t="n">
-        <v>6788471</v>
+        <v>6787879</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13686,10 +13686,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129124105</v>
+        <v>129124164</v>
       </c>
       <c r="B122" t="n">
-        <v>92871</v>
+        <v>79041</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13697,43 +13697,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>421613</v>
+        <v>421345</v>
       </c>
       <c r="R122" t="n">
-        <v>6788634</v>
+        <v>6788394</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13765,7 +13756,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13775,7 +13766,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13802,50 +13793,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129124121</v>
+        <v>129124156</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>421524</v>
+        <v>421351</v>
       </c>
       <c r="R123" t="n">
-        <v>6788399</v>
+        <v>6788471</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13877,7 +13863,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13887,7 +13873,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13914,10 +13900,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129124082</v>
+        <v>129124105</v>
       </c>
       <c r="B124" t="n">
-        <v>79629</v>
+        <v>92873</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13925,34 +13911,43 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>5966</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>421601</v>
+        <v>421613</v>
       </c>
       <c r="R124" t="n">
-        <v>6787830</v>
+        <v>6788634</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13984,7 +13979,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13994,7 +13989,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14021,45 +14016,50 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129124069</v>
+        <v>129124121</v>
       </c>
       <c r="B125" t="n">
-        <v>79658</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>421626</v>
+        <v>421524</v>
       </c>
       <c r="R125" t="n">
-        <v>6787879</v>
+        <v>6788399</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14131,7 +14131,7 @@
         <v>129124054</v>
       </c>
       <c r="B126" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14235,10 +14235,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129124164</v>
+        <v>129124062</v>
       </c>
       <c r="B127" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14246,21 +14246,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14270,10 +14270,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421345</v>
+        <v>421395</v>
       </c>
       <c r="R127" t="n">
-        <v>6788394</v>
+        <v>6788610</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14342,10 +14342,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129124062</v>
+        <v>129124082</v>
       </c>
       <c r="B128" t="n">
-        <v>79658</v>
+        <v>79631</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14353,21 +14353,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>421395</v>
+        <v>421601</v>
       </c>
       <c r="R128" t="n">
-        <v>6788610</v>
+        <v>6787830</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14452,7 +14452,7 @@
         <v>129124056</v>
       </c>
       <c r="B129" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14668,10 +14668,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129124178</v>
+        <v>129124155</v>
       </c>
       <c r="B131" t="n">
-        <v>78705</v>
+        <v>79041</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14679,21 +14679,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14703,10 +14703,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>421235</v>
+        <v>421354</v>
       </c>
       <c r="R131" t="n">
-        <v>6788559</v>
+        <v>6788463</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14775,10 +14775,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129124180</v>
+        <v>129124073</v>
       </c>
       <c r="B132" t="n">
-        <v>78705</v>
+        <v>79660</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14786,21 +14786,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14810,10 +14810,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>421501</v>
+        <v>421595</v>
       </c>
       <c r="R132" t="n">
-        <v>6788671</v>
+        <v>6787823</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14882,10 +14882,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129124155</v>
+        <v>129124178</v>
       </c>
       <c r="B133" t="n">
-        <v>79039</v>
+        <v>78707</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>421354</v>
+        <v>421235</v>
       </c>
       <c r="R133" t="n">
-        <v>6788463</v>
+        <v>6788559</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14989,10 +14989,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129124073</v>
+        <v>129124180</v>
       </c>
       <c r="B134" t="n">
-        <v>79658</v>
+        <v>78707</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15000,21 +15000,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15024,10 +15024,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>421595</v>
+        <v>421501</v>
       </c>
       <c r="R134" t="n">
-        <v>6787823</v>
+        <v>6788671</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15059,7 +15059,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15211,7 +15211,7 @@
         <v>129124057</v>
       </c>
       <c r="B136" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>129124163</v>
       </c>
       <c r="B137" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>129124088</v>
       </c>
       <c r="B138" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>129124077</v>
       </c>
       <c r="B139" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15641,50 +15641,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129124109</v>
+        <v>129124140</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>421325</v>
+        <v>421656</v>
       </c>
       <c r="R140" t="n">
-        <v>6788393</v>
+        <v>6787791</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15716,7 +15711,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15726,7 +15721,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15753,10 +15748,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129124140</v>
+        <v>129124068</v>
       </c>
       <c r="B141" t="n">
-        <v>78796</v>
+        <v>79660</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15764,21 +15759,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15788,10 +15783,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>421656</v>
+        <v>421675</v>
       </c>
       <c r="R141" t="n">
-        <v>6787791</v>
+        <v>6787696</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15823,7 +15818,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15833,7 +15828,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15860,10 +15855,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129124068</v>
+        <v>129124065</v>
       </c>
       <c r="B142" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15895,10 +15890,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>421675</v>
+        <v>421530</v>
       </c>
       <c r="R142" t="n">
-        <v>6787696</v>
+        <v>6788679</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15930,7 +15925,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15940,7 +15935,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15967,10 +15962,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129124065</v>
+        <v>129124169</v>
       </c>
       <c r="B143" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15978,21 +15973,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16002,10 +15997,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>421530</v>
+        <v>421618</v>
       </c>
       <c r="R143" t="n">
-        <v>6788679</v>
+        <v>6787872</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16037,7 +16032,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16047,7 +16042,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16074,45 +16069,50 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129124169</v>
+        <v>129124109</v>
       </c>
       <c r="B144" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>421618</v>
+        <v>421325</v>
       </c>
       <c r="R144" t="n">
-        <v>6787872</v>
+        <v>6788393</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16181,10 +16181,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124087</v>
+        <v>129124144</v>
       </c>
       <c r="B145" t="n">
-        <v>79134</v>
+        <v>78798</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16192,21 +16192,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421601</v>
+        <v>421602</v>
       </c>
       <c r="R145" t="n">
-        <v>6787830</v>
+        <v>6787829</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16288,50 +16288,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124106</v>
+        <v>129124170</v>
       </c>
       <c r="B146" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421574</v>
+        <v>421604</v>
       </c>
       <c r="R146" t="n">
-        <v>6788374</v>
+        <v>6787823</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16363,7 +16358,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16373,7 +16368,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16400,50 +16395,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129124122</v>
+        <v>129124138</v>
       </c>
       <c r="B147" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>421477</v>
+        <v>421292</v>
       </c>
       <c r="R147" t="n">
-        <v>6788422</v>
+        <v>6788456</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16475,7 +16465,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16485,7 +16475,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16512,50 +16502,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129124120</v>
+        <v>129124087</v>
       </c>
       <c r="B148" t="n">
-        <v>8450</v>
+        <v>79136</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>106545</v>
+        <v>967</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421520</v>
+        <v>421601</v>
       </c>
       <c r="R148" t="n">
-        <v>6788366</v>
+        <v>6787830</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16587,7 +16572,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16597,7 +16582,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16624,45 +16609,50 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124078</v>
+        <v>129124106</v>
       </c>
       <c r="B149" t="n">
-        <v>79629</v>
+        <v>8450</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421640</v>
+        <v>421574</v>
       </c>
       <c r="R149" t="n">
-        <v>6788394</v>
+        <v>6788374</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16694,7 +16684,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16704,7 +16694,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16731,45 +16721,50 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124133</v>
+        <v>129124122</v>
       </c>
       <c r="B150" t="n">
-        <v>78797</v>
+        <v>8450</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421633</v>
+        <v>421477</v>
       </c>
       <c r="R150" t="n">
-        <v>6787841</v>
+        <v>6788422</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16801,7 +16796,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16811,7 +16806,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16838,45 +16833,50 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124170</v>
+        <v>129124120</v>
       </c>
       <c r="B151" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421604</v>
+        <v>421520</v>
       </c>
       <c r="R151" t="n">
-        <v>6787823</v>
+        <v>6788366</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16945,10 +16945,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129124144</v>
+        <v>129124133</v>
       </c>
       <c r="B152" t="n">
-        <v>78796</v>
+        <v>78799</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16956,21 +16956,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16980,10 +16980,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>421602</v>
+        <v>421633</v>
       </c>
       <c r="R152" t="n">
-        <v>6787829</v>
+        <v>6787841</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17052,10 +17052,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129124138</v>
+        <v>129124078</v>
       </c>
       <c r="B153" t="n">
-        <v>78796</v>
+        <v>79631</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17063,21 +17063,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17087,10 +17087,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>421292</v>
+        <v>421640</v>
       </c>
       <c r="R153" t="n">
-        <v>6788456</v>
+        <v>6788394</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17162,7 +17162,7 @@
         <v>129124186</v>
       </c>
       <c r="B154" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17266,50 +17266,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129124119</v>
+        <v>129124064</v>
       </c>
       <c r="B155" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>421653</v>
+        <v>421501</v>
       </c>
       <c r="R155" t="n">
-        <v>6788387</v>
+        <v>6788671</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17341,7 +17336,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17351,7 +17346,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17378,10 +17373,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129124084</v>
+        <v>129124137</v>
       </c>
       <c r="B156" t="n">
-        <v>79629</v>
+        <v>78798</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17389,21 +17384,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17413,10 +17408,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>421591</v>
+        <v>421312</v>
       </c>
       <c r="R156" t="n">
-        <v>6787819</v>
+        <v>6788393</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17448,7 +17443,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17458,7 +17453,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17485,45 +17480,50 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129124076</v>
+        <v>129124119</v>
       </c>
       <c r="B157" t="n">
-        <v>79629</v>
+        <v>8450</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>421240</v>
+        <v>421653</v>
       </c>
       <c r="R157" t="n">
-        <v>6788558</v>
+        <v>6788387</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17555,7 +17555,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17565,7 +17565,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17592,10 +17592,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129124064</v>
+        <v>129124076</v>
       </c>
       <c r="B158" t="n">
-        <v>79658</v>
+        <v>79631</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17603,21 +17603,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17627,10 +17627,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>421501</v>
+        <v>421240</v>
       </c>
       <c r="R158" t="n">
-        <v>6788671</v>
+        <v>6788558</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17672,7 +17672,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17699,10 +17699,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129124137</v>
+        <v>129124084</v>
       </c>
       <c r="B159" t="n">
-        <v>78796</v>
+        <v>79631</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17710,21 +17710,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17734,10 +17734,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>421312</v>
+        <v>421591</v>
       </c>
       <c r="R159" t="n">
-        <v>6788393</v>
+        <v>6787819</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129124161</v>
+        <v>129124183</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421701</v>
+        <v>421744</v>
       </c>
       <c r="R9" t="n">
-        <v>6788470</v>
+        <v>6788480</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129124183</v>
+        <v>129124161</v>
       </c>
       <c r="B10" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421744</v>
+        <v>421701</v>
       </c>
       <c r="R10" t="n">
-        <v>6788480</v>
+        <v>6788470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2138,7 +2138,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129095317</v>
+        <v>129094012</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421398</v>
+        <v>421379</v>
       </c>
       <c r="R15" t="n">
-        <v>6788372</v>
+        <v>6788540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2245,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129094012</v>
+        <v>129093983</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421379</v>
+        <v>421400</v>
       </c>
       <c r="R16" t="n">
-        <v>6788540</v>
+        <v>6788524</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,7 +2352,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129093983</v>
+        <v>129095317</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421400</v>
+        <v>421398</v>
       </c>
       <c r="R17" t="n">
-        <v>6788524</v>
+        <v>6788372</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129093598</v>
+        <v>129093952</v>
       </c>
       <c r="B19" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421371</v>
+        <v>421399</v>
       </c>
       <c r="R19" t="n">
-        <v>6788472</v>
+        <v>6788487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129093952</v>
+        <v>129093598</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421399</v>
+        <v>421371</v>
       </c>
       <c r="R20" t="n">
-        <v>6788487</v>
+        <v>6788472</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129093202</v>
+        <v>129093188</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129094076</v>
+        <v>129093167</v>
       </c>
       <c r="B24" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421379</v>
+        <v>421391</v>
       </c>
       <c r="R24" t="n">
-        <v>6788540</v>
+        <v>6788314</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129093167</v>
+        <v>129094076</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,21 +3224,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421391</v>
+        <v>421379</v>
       </c>
       <c r="R25" t="n">
-        <v>6788314</v>
+        <v>6788540</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129093766</v>
+        <v>129094170</v>
       </c>
       <c r="B26" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3331,21 +3331,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421371</v>
+        <v>421499</v>
       </c>
       <c r="R26" t="n">
-        <v>6788472</v>
+        <v>6788592</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129094170</v>
+        <v>129093766</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3438,21 +3438,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421499</v>
+        <v>421371</v>
       </c>
       <c r="R27" t="n">
-        <v>6788592</v>
+        <v>6788472</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3855,7 +3855,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129094179</v>
+        <v>129093018</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421509</v>
+        <v>421341</v>
       </c>
       <c r="R31" t="n">
-        <v>6788597</v>
+        <v>6788261</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3962,7 +3962,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129093018</v>
+        <v>129094179</v>
       </c>
       <c r="B32" t="n">
         <v>79041</v>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>421341</v>
+        <v>421509</v>
       </c>
       <c r="R32" t="n">
-        <v>6788261</v>
+        <v>6788597</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4390,7 +4390,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096050</v>
+        <v>129094091</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>421635</v>
+        <v>421397</v>
       </c>
       <c r="R36" t="n">
-        <v>6787819</v>
+        <v>6788565</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4497,7 +4497,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129094091</v>
+        <v>129096050</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>421397</v>
+        <v>421635</v>
       </c>
       <c r="R37" t="n">
-        <v>6788565</v>
+        <v>6787819</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4925,50 +4925,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129095090</v>
+        <v>129093117</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>421500</v>
+        <v>421391</v>
       </c>
       <c r="R41" t="n">
-        <v>6788425</v>
+        <v>6788314</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5144,45 +5139,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129093117</v>
+        <v>129094242</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>421391</v>
+        <v>421564</v>
       </c>
       <c r="R43" t="n">
-        <v>6788314</v>
+        <v>6788544</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5251,7 +5251,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129094242</v>
+        <v>129094162</v>
       </c>
       <c r="B44" t="n">
         <v>57724</v>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>421564</v>
+        <v>421499</v>
       </c>
       <c r="R44" t="n">
-        <v>6788544</v>
+        <v>6788592</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,10 +5363,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129094162</v>
+        <v>129095090</v>
       </c>
       <c r="B45" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5374,16 +5374,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5394,7 +5394,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>421499</v>
+        <v>421500</v>
       </c>
       <c r="R45" t="n">
-        <v>6788592</v>
+        <v>6788425</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129093173</v>
+        <v>129093174</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>421390</v>
+        <v>421394</v>
       </c>
       <c r="R47" t="n">
-        <v>6788380</v>
+        <v>6788396</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129095392</v>
+        <v>129093173</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>421342</v>
+        <v>421390</v>
       </c>
       <c r="R48" t="n">
-        <v>6788310</v>
+        <v>6788380</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5796,7 +5796,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129093174</v>
+        <v>129095392</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>421394</v>
+        <v>421342</v>
       </c>
       <c r="R49" t="n">
-        <v>6788396</v>
+        <v>6788310</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5903,10 +5903,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129094943</v>
+        <v>129094103</v>
       </c>
       <c r="B50" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5914,21 +5914,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>421534</v>
+        <v>421421</v>
       </c>
       <c r="R50" t="n">
-        <v>6788452</v>
+        <v>6788547</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6010,45 +6010,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129094103</v>
+        <v>129095582</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>421421</v>
+        <v>421342</v>
       </c>
       <c r="R51" t="n">
-        <v>6788547</v>
+        <v>6788310</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6117,50 +6122,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129095582</v>
+        <v>129094943</v>
       </c>
       <c r="B52" t="n">
-        <v>58097</v>
+        <v>79631</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>421342</v>
+        <v>421534</v>
       </c>
       <c r="R52" t="n">
-        <v>6788310</v>
+        <v>6788452</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6229,10 +6229,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129124182</v>
+        <v>129124160</v>
       </c>
       <c r="B53" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6240,21 +6240,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>421622</v>
+        <v>421611</v>
       </c>
       <c r="R53" t="n">
-        <v>6788520</v>
+        <v>6788481</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6336,10 +6336,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129124179</v>
+        <v>129124166</v>
       </c>
       <c r="B54" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>421487</v>
+        <v>421316</v>
       </c>
       <c r="R54" t="n">
-        <v>6788638</v>
+        <v>6788317</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6443,10 +6443,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129124176</v>
+        <v>129124130</v>
       </c>
       <c r="B55" t="n">
-        <v>78707</v>
+        <v>78799</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6454,21 +6454,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>421338</v>
+        <v>421354</v>
       </c>
       <c r="R55" t="n">
-        <v>6788476</v>
+        <v>6788463</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124130</v>
+        <v>129124182</v>
       </c>
       <c r="B56" t="n">
-        <v>78799</v>
+        <v>78707</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,21 +6561,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421354</v>
+        <v>421622</v>
       </c>
       <c r="R56" t="n">
-        <v>6788463</v>
+        <v>6788520</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6657,10 +6657,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129124160</v>
+        <v>129124179</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,21 +6668,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>421611</v>
+        <v>421487</v>
       </c>
       <c r="R57" t="n">
-        <v>6788481</v>
+        <v>6788638</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6764,10 +6764,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129124070</v>
+        <v>129124176</v>
       </c>
       <c r="B58" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6775,21 +6775,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>421616</v>
+        <v>421338</v>
       </c>
       <c r="R58" t="n">
-        <v>6787882</v>
+        <v>6788476</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129124166</v>
+        <v>129124070</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,21 +6882,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>421316</v>
+        <v>421616</v>
       </c>
       <c r="R59" t="n">
-        <v>6788317</v>
+        <v>6787882</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6978,50 +6978,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129124124</v>
+        <v>129124151</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>421440</v>
+        <v>421275</v>
       </c>
       <c r="R60" t="n">
-        <v>6788409</v>
+        <v>6788430</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7053,7 +7048,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7063,7 +7058,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7090,10 +7085,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129124061</v>
+        <v>129124149</v>
       </c>
       <c r="B61" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7101,21 +7096,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7125,10 +7120,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>421238</v>
+        <v>421376</v>
       </c>
       <c r="R61" t="n">
-        <v>6788555</v>
+        <v>6788380</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7160,7 +7155,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7170,7 +7165,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7197,10 +7192,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129124149</v>
+        <v>129124061</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7208,21 +7203,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7232,10 +7227,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>421376</v>
+        <v>421238</v>
       </c>
       <c r="R62" t="n">
-        <v>6788380</v>
+        <v>6788555</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7267,7 +7262,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7277,7 +7272,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7411,45 +7406,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129124151</v>
+        <v>129124124</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>421275</v>
+        <v>421440</v>
       </c>
       <c r="R64" t="n">
-        <v>6788430</v>
+        <v>6788409</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7625,32 +7625,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129124058</v>
+        <v>129124173</v>
       </c>
       <c r="B66" t="n">
-        <v>79660</v>
+        <v>92835</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>421246</v>
+        <v>421621</v>
       </c>
       <c r="R66" t="n">
-        <v>6788416</v>
+        <v>6787838</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7732,45 +7732,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129124059</v>
+        <v>129124114</v>
       </c>
       <c r="B67" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>421354</v>
+        <v>421399</v>
       </c>
       <c r="R67" t="n">
-        <v>6788463</v>
+        <v>6788567</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7802,7 +7807,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7812,7 +7817,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7839,45 +7844,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129124051</v>
+        <v>129124115</v>
       </c>
       <c r="B68" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>421392</v>
+        <v>421608</v>
       </c>
       <c r="R68" t="n">
-        <v>6788226</v>
+        <v>6788661</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7909,7 +7919,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7919,7 +7929,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7946,10 +7956,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129124187</v>
+        <v>129124074</v>
       </c>
       <c r="B69" t="n">
-        <v>78444</v>
+        <v>79631</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7957,21 +7967,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7981,10 +7991,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>421639</v>
+        <v>421236</v>
       </c>
       <c r="R69" t="n">
-        <v>6788393</v>
+        <v>6788559</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8016,7 +8026,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8026,7 +8036,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På stubbe med 6 brandljud</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8053,10 +8068,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129124074</v>
+        <v>129124058</v>
       </c>
       <c r="B70" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8064,21 +8079,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8088,10 +8103,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>421236</v>
+        <v>421246</v>
       </c>
       <c r="R70" t="n">
-        <v>6788559</v>
+        <v>6788416</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8123,7 +8138,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8133,12 +8148,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På stubbe med 6 brandljud</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8165,32 +8175,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124173</v>
+        <v>129124059</v>
       </c>
       <c r="B71" t="n">
-        <v>92835</v>
+        <v>79660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8200,10 +8210,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>421621</v>
+        <v>421354</v>
       </c>
       <c r="R71" t="n">
-        <v>6787838</v>
+        <v>6788463</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8235,7 +8245,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8245,7 +8255,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8272,50 +8282,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124114</v>
+        <v>129124051</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>421399</v>
+        <v>421392</v>
       </c>
       <c r="R72" t="n">
-        <v>6788567</v>
+        <v>6788226</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8347,7 +8352,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8357,7 +8362,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8384,50 +8389,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129124115</v>
+        <v>129124187</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>78444</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6437</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>421608</v>
+        <v>421639</v>
       </c>
       <c r="R73" t="n">
-        <v>6788661</v>
+        <v>6788393</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8603,32 +8603,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129124146</v>
+        <v>129124145</v>
       </c>
       <c r="B75" t="n">
-        <v>91703</v>
+        <v>78798</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>421654</v>
+        <v>421591</v>
       </c>
       <c r="R75" t="n">
-        <v>6788448</v>
+        <v>6787819</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8710,10 +8710,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124145</v>
+        <v>129124152</v>
       </c>
       <c r="B76" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8721,21 +8721,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421591</v>
+        <v>421234</v>
       </c>
       <c r="R76" t="n">
-        <v>6787819</v>
+        <v>6788411</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8817,10 +8817,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124152</v>
+        <v>129124103</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421234</v>
+        <v>421618</v>
       </c>
       <c r="R77" t="n">
-        <v>6788411</v>
+        <v>6787832</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8924,32 +8924,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129124103</v>
+        <v>129124146</v>
       </c>
       <c r="B78" t="n">
-        <v>78799</v>
+        <v>91703</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>421618</v>
+        <v>421654</v>
       </c>
       <c r="R78" t="n">
-        <v>6787832</v>
+        <v>6788448</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9031,10 +9031,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129124090</v>
+        <v>129124143</v>
       </c>
       <c r="B79" t="n">
-        <v>91562</v>
+        <v>78798</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9042,21 +9042,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>421576</v>
+        <v>421596</v>
       </c>
       <c r="R79" t="n">
-        <v>6788373</v>
+        <v>6787835</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9111,12 +9111,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ej märkt med hänsyn</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9143,10 +9138,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129124143</v>
+        <v>129124090</v>
       </c>
       <c r="B80" t="n">
-        <v>78798</v>
+        <v>91562</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9154,21 +9149,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9178,10 +9173,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>421596</v>
+        <v>421576</v>
       </c>
       <c r="R80" t="n">
-        <v>6787835</v>
+        <v>6788373</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9213,7 +9208,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9223,7 +9218,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ej märkt med hänsyn</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10106,45 +10106,50 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129124132</v>
+        <v>129124123</v>
       </c>
       <c r="B89" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>421649</v>
+        <v>421446</v>
       </c>
       <c r="R89" t="n">
-        <v>6787778</v>
+        <v>6788421</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10176,7 +10181,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10186,7 +10191,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10213,7 +10218,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129124136</v>
+        <v>129124132</v>
       </c>
       <c r="B90" t="n">
         <v>78799</v>
@@ -10248,10 +10253,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>421598</v>
+        <v>421649</v>
       </c>
       <c r="R90" t="n">
-        <v>6787834</v>
+        <v>6787778</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10283,7 +10288,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10293,7 +10298,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10320,50 +10325,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129124123</v>
+        <v>129124136</v>
       </c>
       <c r="B91" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>421446</v>
+        <v>421598</v>
       </c>
       <c r="R91" t="n">
-        <v>6788421</v>
+        <v>6787834</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10539,10 +10539,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129124135</v>
+        <v>129124096</v>
       </c>
       <c r="B93" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10550,34 +10550,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>421594</v>
+        <v>421596</v>
       </c>
       <c r="R93" t="n">
-        <v>6787870</v>
+        <v>6787836</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10609,7 +10614,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10619,7 +10624,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10646,7 +10651,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129124128</v>
+        <v>129124135</v>
       </c>
       <c r="B94" t="n">
         <v>78799</v>
@@ -10681,10 +10686,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>421391</v>
+        <v>421594</v>
       </c>
       <c r="R94" t="n">
-        <v>6788209</v>
+        <v>6787870</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10716,7 +10721,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10726,7 +10731,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10753,10 +10758,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129124096</v>
+        <v>129124128</v>
       </c>
       <c r="B95" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10764,39 +10769,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>421596</v>
+        <v>421391</v>
       </c>
       <c r="R95" t="n">
-        <v>6787836</v>
+        <v>6788209</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11298,10 +11298,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129124154</v>
+        <v>129124104</v>
       </c>
       <c r="B100" t="n">
-        <v>79041</v>
+        <v>92873</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11309,34 +11309,43 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>421303</v>
+        <v>421407</v>
       </c>
       <c r="R100" t="n">
-        <v>6788456</v>
+        <v>6788349</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11368,7 +11377,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11378,7 +11387,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11405,7 +11414,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129124147</v>
+        <v>129124154</v>
       </c>
       <c r="B101" t="n">
         <v>79041</v>
@@ -11440,10 +11449,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>421437</v>
+        <v>421303</v>
       </c>
       <c r="R101" t="n">
-        <v>6788275</v>
+        <v>6788456</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11475,7 +11484,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11485,7 +11494,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11512,10 +11521,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129124104</v>
+        <v>129124147</v>
       </c>
       <c r="B102" t="n">
-        <v>92873</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11523,43 +11532,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>421407</v>
+        <v>421437</v>
       </c>
       <c r="R102" t="n">
-        <v>6788349</v>
+        <v>6788275</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11591,7 +11591,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11740,50 +11740,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129124127</v>
+        <v>129124165</v>
       </c>
       <c r="B104" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>421630</v>
+        <v>421340</v>
       </c>
       <c r="R104" t="n">
-        <v>6787815</v>
+        <v>6788389</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11815,7 +11810,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11825,7 +11820,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11852,10 +11847,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129124165</v>
+        <v>129124071</v>
       </c>
       <c r="B105" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11863,21 +11858,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11887,10 +11882,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>421340</v>
+        <v>421598</v>
       </c>
       <c r="R105" t="n">
-        <v>6788389</v>
+        <v>6787863</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11922,7 +11917,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11932,7 +11927,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11959,10 +11954,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124071</v>
+        <v>129124141</v>
       </c>
       <c r="B106" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11970,21 +11965,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11994,10 +11989,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421598</v>
+        <v>421616</v>
       </c>
       <c r="R106" t="n">
-        <v>6787863</v>
+        <v>6787883</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12029,7 +12024,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12039,7 +12034,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12066,45 +12061,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129124141</v>
+        <v>129124127</v>
       </c>
       <c r="B107" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>421616</v>
+        <v>421630</v>
       </c>
       <c r="R107" t="n">
-        <v>6787883</v>
+        <v>6787815</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12280,50 +12280,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129124117</v>
+        <v>129124181</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>78707</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>421611</v>
+        <v>421537</v>
       </c>
       <c r="R109" t="n">
-        <v>6788482</v>
+        <v>6788706</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12355,7 +12350,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12365,7 +12360,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12392,50 +12387,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129124116</v>
+        <v>129124175</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>78707</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>421615</v>
+        <v>421343</v>
       </c>
       <c r="R110" t="n">
-        <v>6788580</v>
+        <v>6788400</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12467,7 +12457,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12477,7 +12467,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12504,50 +12494,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129124111</v>
+        <v>129124158</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>421315</v>
+        <v>421383</v>
       </c>
       <c r="R111" t="n">
-        <v>6788532</v>
+        <v>6788546</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12579,7 +12564,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12589,7 +12574,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12616,10 +12601,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124181</v>
+        <v>129124159</v>
       </c>
       <c r="B112" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12627,21 +12612,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12651,10 +12636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421537</v>
+        <v>421612</v>
       </c>
       <c r="R112" t="n">
-        <v>6788706</v>
+        <v>6788488</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12686,7 +12671,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12696,7 +12681,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12723,10 +12708,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129124175</v>
+        <v>129124053</v>
       </c>
       <c r="B113" t="n">
-        <v>78707</v>
+        <v>79660</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12734,21 +12719,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12758,10 +12743,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421343</v>
+        <v>421421</v>
       </c>
       <c r="R113" t="n">
-        <v>6788400</v>
+        <v>6788216</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12793,7 +12778,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12803,7 +12788,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12830,7 +12815,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129124053</v>
+        <v>129124063</v>
       </c>
       <c r="B114" t="n">
         <v>79660</v>
@@ -12865,10 +12850,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>421421</v>
+        <v>421442</v>
       </c>
       <c r="R114" t="n">
-        <v>6788216</v>
+        <v>6788613</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12900,7 +12885,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12910,7 +12895,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12937,10 +12922,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129124063</v>
+        <v>129124139</v>
       </c>
       <c r="B115" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,21 +12933,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12972,10 +12957,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>421442</v>
+        <v>421354</v>
       </c>
       <c r="R115" t="n">
-        <v>6788613</v>
+        <v>6788463</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13007,7 +12992,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13017,7 +13002,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13044,10 +13029,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129124139</v>
+        <v>129124052</v>
       </c>
       <c r="B116" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13055,21 +13040,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13079,10 +13064,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>421354</v>
+        <v>421391</v>
       </c>
       <c r="R116" t="n">
-        <v>6788463</v>
+        <v>6788209</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13114,7 +13099,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13124,7 +13109,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13151,45 +13136,50 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129124052</v>
+        <v>129124117</v>
       </c>
       <c r="B117" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>421391</v>
+        <v>421611</v>
       </c>
       <c r="R117" t="n">
-        <v>6788209</v>
+        <v>6788482</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13221,7 +13211,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13231,7 +13221,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13258,45 +13248,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129124159</v>
+        <v>129124116</v>
       </c>
       <c r="B118" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>421612</v>
+        <v>421615</v>
       </c>
       <c r="R118" t="n">
-        <v>6788488</v>
+        <v>6788580</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13328,7 +13323,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13338,7 +13333,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13365,45 +13360,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129124158</v>
+        <v>129124111</v>
       </c>
       <c r="B119" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>421383</v>
+        <v>421315</v>
       </c>
       <c r="R119" t="n">
-        <v>6788546</v>
+        <v>6788532</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13579,10 +13579,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129124069</v>
+        <v>129124082</v>
       </c>
       <c r="B121" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13590,21 +13590,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13614,10 +13614,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>421626</v>
+        <v>421601</v>
       </c>
       <c r="R121" t="n">
-        <v>6787879</v>
+        <v>6787830</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13686,45 +13686,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129124164</v>
+        <v>129124121</v>
       </c>
       <c r="B122" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>421345</v>
+        <v>421524</v>
       </c>
       <c r="R122" t="n">
-        <v>6788394</v>
+        <v>6788399</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13756,7 +13761,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13766,7 +13771,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14016,50 +14021,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129124121</v>
+        <v>129124164</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>421524</v>
+        <v>421345</v>
       </c>
       <c r="R125" t="n">
-        <v>6788399</v>
+        <v>6788394</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14128,7 +14128,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129124054</v>
+        <v>129124069</v>
       </c>
       <c r="B126" t="n">
         <v>79660</v>
@@ -14163,10 +14163,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>421423</v>
+        <v>421626</v>
       </c>
       <c r="R126" t="n">
-        <v>6788261</v>
+        <v>6787879</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14235,7 +14235,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129124062</v>
+        <v>129124054</v>
       </c>
       <c r="B127" t="n">
         <v>79660</v>
@@ -14270,10 +14270,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421395</v>
+        <v>421423</v>
       </c>
       <c r="R127" t="n">
-        <v>6788610</v>
+        <v>6788261</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14342,10 +14342,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129124082</v>
+        <v>129124062</v>
       </c>
       <c r="B128" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14353,21 +14353,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>421601</v>
+        <v>421395</v>
       </c>
       <c r="R128" t="n">
-        <v>6787830</v>
+        <v>6788610</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14668,10 +14668,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129124155</v>
+        <v>129124178</v>
       </c>
       <c r="B131" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14679,21 +14679,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14703,10 +14703,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>421354</v>
+        <v>421235</v>
       </c>
       <c r="R131" t="n">
-        <v>6788463</v>
+        <v>6788559</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14775,10 +14775,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129124073</v>
+        <v>129124180</v>
       </c>
       <c r="B132" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14786,21 +14786,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14810,10 +14810,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>421595</v>
+        <v>421501</v>
       </c>
       <c r="R132" t="n">
-        <v>6787823</v>
+        <v>6788671</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14882,45 +14882,50 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129124178</v>
+        <v>129124112</v>
       </c>
       <c r="B133" t="n">
-        <v>78707</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>421235</v>
+        <v>421293</v>
       </c>
       <c r="R133" t="n">
-        <v>6788559</v>
+        <v>6788551</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14952,7 +14957,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14962,7 +14967,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14989,10 +14994,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129124180</v>
+        <v>129124155</v>
       </c>
       <c r="B134" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15000,21 +15005,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15024,10 +15029,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>421501</v>
+        <v>421354</v>
       </c>
       <c r="R134" t="n">
-        <v>6788671</v>
+        <v>6788463</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15059,7 +15064,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15069,7 +15074,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15096,50 +15101,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129124112</v>
+        <v>129124073</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>421293</v>
+        <v>421595</v>
       </c>
       <c r="R135" t="n">
-        <v>6788551</v>
+        <v>6787823</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15208,10 +15208,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129124057</v>
+        <v>129124163</v>
       </c>
       <c r="B136" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15219,21 +15219,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15243,10 +15243,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>421312</v>
+        <v>421454</v>
       </c>
       <c r="R136" t="n">
-        <v>6788393</v>
+        <v>6788422</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15315,10 +15315,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129124163</v>
+        <v>129124057</v>
       </c>
       <c r="B137" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15326,21 +15326,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15350,10 +15350,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>421454</v>
+        <v>421312</v>
       </c>
       <c r="R137" t="n">
-        <v>6788422</v>
+        <v>6788393</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15395,7 +15395,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16181,10 +16181,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124144</v>
+        <v>129124170</v>
       </c>
       <c r="B145" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16192,21 +16192,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421602</v>
+        <v>421604</v>
       </c>
       <c r="R145" t="n">
-        <v>6787829</v>
+        <v>6787823</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16251,7 +16251,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16288,10 +16288,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124170</v>
+        <v>129124144</v>
       </c>
       <c r="B146" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16299,21 +16299,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16323,10 +16323,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421604</v>
+        <v>421602</v>
       </c>
       <c r="R146" t="n">
-        <v>6787823</v>
+        <v>6787829</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16502,45 +16502,50 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129124087</v>
+        <v>129124106</v>
       </c>
       <c r="B148" t="n">
-        <v>79136</v>
+        <v>8450</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>967</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421601</v>
+        <v>421574</v>
       </c>
       <c r="R148" t="n">
-        <v>6787830</v>
+        <v>6788374</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16572,7 +16577,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16582,7 +16587,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16609,7 +16614,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124106</v>
+        <v>129124122</v>
       </c>
       <c r="B149" t="n">
         <v>8450</v>
@@ -16640,7 +16645,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -16649,10 +16654,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421574</v>
+        <v>421477</v>
       </c>
       <c r="R149" t="n">
-        <v>6788374</v>
+        <v>6788422</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16684,7 +16689,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16694,7 +16699,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16721,7 +16726,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124122</v>
+        <v>129124120</v>
       </c>
       <c r="B150" t="n">
         <v>8450</v>
@@ -16761,10 +16766,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421477</v>
+        <v>421520</v>
       </c>
       <c r="R150" t="n">
-        <v>6788422</v>
+        <v>6788366</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16796,7 +16801,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16806,7 +16811,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16833,50 +16838,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124120</v>
+        <v>129124087</v>
       </c>
       <c r="B151" t="n">
-        <v>8450</v>
+        <v>79136</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>967</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421520</v>
+        <v>421601</v>
       </c>
       <c r="R151" t="n">
-        <v>6788366</v>
+        <v>6787830</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD151" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -3534,32 +3534,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129094800</v>
+        <v>129094249</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421501</v>
+        <v>421564</v>
       </c>
       <c r="R28" t="n">
-        <v>6788477</v>
+        <v>6788544</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,32 +3641,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129094249</v>
+        <v>129094800</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421564</v>
+        <v>421501</v>
       </c>
       <c r="R29" t="n">
-        <v>6788544</v>
+        <v>6788477</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -5903,10 +5903,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129094103</v>
+        <v>129094943</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5914,21 +5914,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>421421</v>
+        <v>421534</v>
       </c>
       <c r="R50" t="n">
-        <v>6788547</v>
+        <v>6788452</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6122,10 +6122,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129094943</v>
+        <v>129094103</v>
       </c>
       <c r="B52" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6133,21 +6133,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>421534</v>
+        <v>421421</v>
       </c>
       <c r="R52" t="n">
-        <v>6788452</v>
+        <v>6788547</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6443,10 +6443,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129124130</v>
+        <v>129124070</v>
       </c>
       <c r="B55" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6454,21 +6454,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>421354</v>
+        <v>421616</v>
       </c>
       <c r="R55" t="n">
-        <v>6788463</v>
+        <v>6787882</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124182</v>
+        <v>129124130</v>
       </c>
       <c r="B56" t="n">
-        <v>78707</v>
+        <v>78799</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,21 +6561,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421622</v>
+        <v>421354</v>
       </c>
       <c r="R56" t="n">
-        <v>6788520</v>
+        <v>6788463</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6657,7 +6657,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129124179</v>
+        <v>129124182</v>
       </c>
       <c r="B57" t="n">
         <v>78707</v>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>421487</v>
+        <v>421622</v>
       </c>
       <c r="R57" t="n">
-        <v>6788638</v>
+        <v>6788520</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6764,7 +6764,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129124176</v>
+        <v>129124179</v>
       </c>
       <c r="B58" t="n">
         <v>78707</v>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>421338</v>
+        <v>421487</v>
       </c>
       <c r="R58" t="n">
-        <v>6788476</v>
+        <v>6788638</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129124070</v>
+        <v>129124176</v>
       </c>
       <c r="B59" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,21 +6882,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>421616</v>
+        <v>421338</v>
       </c>
       <c r="R59" t="n">
-        <v>6787882</v>
+        <v>6788476</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8496,32 +8496,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129124177</v>
+        <v>129124146</v>
       </c>
       <c r="B74" t="n">
-        <v>78707</v>
+        <v>91703</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>421318</v>
+        <v>421654</v>
       </c>
       <c r="R74" t="n">
-        <v>6788511</v>
+        <v>6788448</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8603,10 +8603,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129124145</v>
+        <v>129124177</v>
       </c>
       <c r="B75" t="n">
-        <v>78798</v>
+        <v>78707</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8614,21 +8614,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>421591</v>
+        <v>421318</v>
       </c>
       <c r="R75" t="n">
-        <v>6787819</v>
+        <v>6788511</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8710,10 +8710,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124152</v>
+        <v>129124145</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8721,21 +8721,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421234</v>
+        <v>421591</v>
       </c>
       <c r="R76" t="n">
-        <v>6788411</v>
+        <v>6787819</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8817,10 +8817,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124103</v>
+        <v>129124152</v>
       </c>
       <c r="B77" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421618</v>
+        <v>421234</v>
       </c>
       <c r="R77" t="n">
-        <v>6787832</v>
+        <v>6788411</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8924,32 +8924,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129124146</v>
+        <v>129124103</v>
       </c>
       <c r="B78" t="n">
-        <v>91703</v>
+        <v>78799</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>421654</v>
+        <v>421618</v>
       </c>
       <c r="R78" t="n">
-        <v>6788448</v>
+        <v>6787832</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10432,10 +10432,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129124102</v>
+        <v>129124096</v>
       </c>
       <c r="B92" t="n">
-        <v>83002</v>
+        <v>57724</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10443,34 +10443,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>310</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>421694</v>
+        <v>421596</v>
       </c>
       <c r="R92" t="n">
-        <v>6787682</v>
+        <v>6787836</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10502,7 +10507,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10512,7 +10517,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10539,10 +10544,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129124096</v>
+        <v>129124102</v>
       </c>
       <c r="B93" t="n">
-        <v>57724</v>
+        <v>83002</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10550,39 +10555,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>310</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>421596</v>
+        <v>421694</v>
       </c>
       <c r="R93" t="n">
-        <v>6787836</v>
+        <v>6787682</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12280,45 +12280,50 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129124181</v>
+        <v>129124117</v>
       </c>
       <c r="B109" t="n">
-        <v>78707</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>421537</v>
+        <v>421611</v>
       </c>
       <c r="R109" t="n">
-        <v>6788706</v>
+        <v>6788482</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12350,7 +12355,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12360,7 +12365,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12387,45 +12392,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129124175</v>
+        <v>129124116</v>
       </c>
       <c r="B110" t="n">
-        <v>78707</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>421343</v>
+        <v>421615</v>
       </c>
       <c r="R110" t="n">
-        <v>6788400</v>
+        <v>6788580</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12457,7 +12467,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12467,7 +12477,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12494,45 +12504,50 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129124158</v>
+        <v>129124111</v>
       </c>
       <c r="B111" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>421383</v>
+        <v>421315</v>
       </c>
       <c r="R111" t="n">
-        <v>6788546</v>
+        <v>6788532</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12564,7 +12579,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12574,7 +12589,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12601,10 +12616,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124159</v>
+        <v>129124080</v>
       </c>
       <c r="B112" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12612,21 +12627,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12636,10 +12651,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421612</v>
+        <v>421633</v>
       </c>
       <c r="R112" t="n">
-        <v>6788488</v>
+        <v>6787841</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12671,7 +12686,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12681,7 +12696,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12708,10 +12723,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129124053</v>
+        <v>129124181</v>
       </c>
       <c r="B113" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12719,21 +12734,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12743,10 +12758,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421421</v>
+        <v>421537</v>
       </c>
       <c r="R113" t="n">
-        <v>6788216</v>
+        <v>6788706</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12778,7 +12793,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12788,7 +12803,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12815,10 +12830,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129124063</v>
+        <v>129124175</v>
       </c>
       <c r="B114" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12826,21 +12841,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12850,10 +12865,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>421442</v>
+        <v>421343</v>
       </c>
       <c r="R114" t="n">
-        <v>6788613</v>
+        <v>6788400</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12885,7 +12900,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12895,7 +12910,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12922,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129124139</v>
+        <v>129124158</v>
       </c>
       <c r="B115" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12933,21 +12948,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12957,10 +12972,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>421354</v>
+        <v>421383</v>
       </c>
       <c r="R115" t="n">
-        <v>6788463</v>
+        <v>6788546</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12992,7 +13007,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13002,7 +13017,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13029,10 +13044,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129124052</v>
+        <v>129124159</v>
       </c>
       <c r="B116" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13040,21 +13055,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13064,10 +13079,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>421391</v>
+        <v>421612</v>
       </c>
       <c r="R116" t="n">
-        <v>6788209</v>
+        <v>6788488</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13099,7 +13114,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13109,7 +13124,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13136,50 +13151,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129124117</v>
+        <v>129124053</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>421611</v>
+        <v>421421</v>
       </c>
       <c r="R117" t="n">
-        <v>6788482</v>
+        <v>6788216</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13211,7 +13221,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13221,7 +13231,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13248,50 +13258,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129124116</v>
+        <v>129124063</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>421615</v>
+        <v>421442</v>
       </c>
       <c r="R118" t="n">
-        <v>6788580</v>
+        <v>6788613</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13323,7 +13328,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13333,7 +13338,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13360,50 +13365,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129124111</v>
+        <v>129124139</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>421315</v>
+        <v>421354</v>
       </c>
       <c r="R119" t="n">
-        <v>6788532</v>
+        <v>6788463</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13472,10 +13472,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129124080</v>
+        <v>129124052</v>
       </c>
       <c r="B120" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13483,21 +13483,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13507,10 +13507,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>421633</v>
+        <v>421391</v>
       </c>
       <c r="R120" t="n">
-        <v>6787841</v>
+        <v>6788209</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13579,10 +13579,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129124082</v>
+        <v>129124164</v>
       </c>
       <c r="B121" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13590,21 +13590,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13614,10 +13614,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>421601</v>
+        <v>421345</v>
       </c>
       <c r="R121" t="n">
-        <v>6787830</v>
+        <v>6788394</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13798,10 +13798,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129124156</v>
+        <v>129124082</v>
       </c>
       <c r="B123" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13809,21 +13809,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13833,10 +13833,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>421351</v>
+        <v>421601</v>
       </c>
       <c r="R123" t="n">
-        <v>6788471</v>
+        <v>6787830</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13868,7 +13868,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13905,10 +13905,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129124105</v>
+        <v>129124156</v>
       </c>
       <c r="B124" t="n">
-        <v>92873</v>
+        <v>79041</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13916,43 +13916,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>421613</v>
+        <v>421351</v>
       </c>
       <c r="R124" t="n">
-        <v>6788634</v>
+        <v>6788471</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13984,7 +13975,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13994,7 +13985,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14021,10 +14012,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129124164</v>
+        <v>129124105</v>
       </c>
       <c r="B125" t="n">
-        <v>79041</v>
+        <v>92873</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14032,34 +14023,43 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>421345</v>
+        <v>421613</v>
       </c>
       <c r="R125" t="n">
-        <v>6788394</v>
+        <v>6788634</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14668,10 +14668,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129124178</v>
+        <v>129124155</v>
       </c>
       <c r="B131" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14679,21 +14679,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14703,10 +14703,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>421235</v>
+        <v>421354</v>
       </c>
       <c r="R131" t="n">
-        <v>6788559</v>
+        <v>6788463</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14775,10 +14775,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129124180</v>
+        <v>129124073</v>
       </c>
       <c r="B132" t="n">
-        <v>78707</v>
+        <v>79660</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14786,21 +14786,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14810,10 +14810,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>421501</v>
+        <v>421595</v>
       </c>
       <c r="R132" t="n">
-        <v>6788671</v>
+        <v>6787823</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14882,50 +14882,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129124112</v>
+        <v>129124178</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>78707</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>421293</v>
+        <v>421235</v>
       </c>
       <c r="R133" t="n">
-        <v>6788551</v>
+        <v>6788559</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14957,7 +14952,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14967,7 +14962,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14994,10 +14989,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129124155</v>
+        <v>129124180</v>
       </c>
       <c r="B134" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15005,21 +15000,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15029,10 +15024,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>421354</v>
+        <v>421501</v>
       </c>
       <c r="R134" t="n">
-        <v>6788463</v>
+        <v>6788671</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15064,7 +15059,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15074,7 +15069,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15101,45 +15096,50 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129124073</v>
+        <v>129124112</v>
       </c>
       <c r="B135" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>421595</v>
+        <v>421293</v>
       </c>
       <c r="R135" t="n">
-        <v>6787823</v>
+        <v>6788551</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17159,10 +17159,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129124186</v>
+        <v>129124064</v>
       </c>
       <c r="B154" t="n">
-        <v>78707</v>
+        <v>79660</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17170,21 +17170,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17194,10 +17194,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>421626</v>
+        <v>421501</v>
       </c>
       <c r="R154" t="n">
-        <v>6787877</v>
+        <v>6788671</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17266,10 +17266,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129124064</v>
+        <v>129124137</v>
       </c>
       <c r="B155" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17277,21 +17277,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17301,10 +17301,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>421501</v>
+        <v>421312</v>
       </c>
       <c r="R155" t="n">
-        <v>6788671</v>
+        <v>6788393</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17346,7 +17346,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17373,10 +17373,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129124137</v>
+        <v>129124186</v>
       </c>
       <c r="B156" t="n">
-        <v>78798</v>
+        <v>78707</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17384,21 +17384,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17408,10 +17408,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>421312</v>
+        <v>421626</v>
       </c>
       <c r="R156" t="n">
-        <v>6788393</v>
+        <v>6787877</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17443,7 +17443,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17453,7 +17453,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17480,50 +17480,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129124119</v>
+        <v>129124076</v>
       </c>
       <c r="B157" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>421653</v>
+        <v>421240</v>
       </c>
       <c r="R157" t="n">
-        <v>6788387</v>
+        <v>6788558</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17555,7 +17550,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17565,7 +17560,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17592,7 +17587,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129124076</v>
+        <v>129124084</v>
       </c>
       <c r="B158" t="n">
         <v>79631</v>
@@ -17627,10 +17622,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>421240</v>
+        <v>421591</v>
       </c>
       <c r="R158" t="n">
-        <v>6788558</v>
+        <v>6787819</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17662,7 +17657,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17672,7 +17667,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17699,45 +17694,50 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129124084</v>
+        <v>129124119</v>
       </c>
       <c r="B159" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>421591</v>
+        <v>421653</v>
       </c>
       <c r="R159" t="n">
-        <v>6787819</v>
+        <v>6788387</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129124171</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129124183</v>
+        <v>129124161</v>
       </c>
       <c r="B9" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421744</v>
+        <v>421701</v>
       </c>
       <c r="R9" t="n">
-        <v>6788480</v>
+        <v>6788470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129124161</v>
+        <v>129124183</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421701</v>
+        <v>421744</v>
       </c>
       <c r="R10" t="n">
-        <v>6788470</v>
+        <v>6788480</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -3320,10 +3320,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129094170</v>
+        <v>129093766</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3331,21 +3331,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421499</v>
+        <v>421371</v>
       </c>
       <c r="R26" t="n">
-        <v>6788592</v>
+        <v>6788472</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129093766</v>
+        <v>129094170</v>
       </c>
       <c r="B27" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3438,21 +3438,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421371</v>
+        <v>421499</v>
       </c>
       <c r="R27" t="n">
-        <v>6788472</v>
+        <v>6788592</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3534,32 +3534,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129094249</v>
+        <v>129094800</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421564</v>
+        <v>421501</v>
       </c>
       <c r="R28" t="n">
-        <v>6788544</v>
+        <v>6788477</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,32 +3641,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129094800</v>
+        <v>129094249</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421501</v>
+        <v>421564</v>
       </c>
       <c r="R29" t="n">
-        <v>6788477</v>
+        <v>6788544</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4925,32 +4925,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129093117</v>
+        <v>129093226</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>421391</v>
+        <v>421395</v>
       </c>
       <c r="R41" t="n">
-        <v>6788314</v>
+        <v>6788438</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5032,32 +5032,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129093226</v>
+        <v>129093117</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>421395</v>
+        <v>421391</v>
       </c>
       <c r="R42" t="n">
-        <v>6788438</v>
+        <v>6788314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5903,10 +5903,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129094943</v>
+        <v>129094103</v>
       </c>
       <c r="B50" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5914,21 +5914,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>421534</v>
+        <v>421421</v>
       </c>
       <c r="R50" t="n">
-        <v>6788452</v>
+        <v>6788547</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6122,10 +6122,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129094103</v>
+        <v>129094943</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6133,21 +6133,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>421421</v>
+        <v>421534</v>
       </c>
       <c r="R52" t="n">
-        <v>6788547</v>
+        <v>6788452</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6229,10 +6229,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129124160</v>
+        <v>129124182</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6240,21 +6240,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>421611</v>
+        <v>421622</v>
       </c>
       <c r="R53" t="n">
-        <v>6788481</v>
+        <v>6788520</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6336,10 +6336,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129124166</v>
+        <v>129124179</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>421316</v>
+        <v>421487</v>
       </c>
       <c r="R54" t="n">
-        <v>6788317</v>
+        <v>6788638</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6443,10 +6443,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129124070</v>
+        <v>129124176</v>
       </c>
       <c r="B55" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6454,21 +6454,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>421616</v>
+        <v>421338</v>
       </c>
       <c r="R55" t="n">
-        <v>6787882</v>
+        <v>6788476</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124130</v>
+        <v>129124160</v>
       </c>
       <c r="B56" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,21 +6561,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421354</v>
+        <v>421611</v>
       </c>
       <c r="R56" t="n">
-        <v>6788463</v>
+        <v>6788481</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6657,10 +6657,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129124182</v>
+        <v>129124070</v>
       </c>
       <c r="B57" t="n">
-        <v>78707</v>
+        <v>79660</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,21 +6668,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>421622</v>
+        <v>421616</v>
       </c>
       <c r="R57" t="n">
-        <v>6788520</v>
+        <v>6787882</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6764,10 +6764,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129124179</v>
+        <v>129124130</v>
       </c>
       <c r="B58" t="n">
-        <v>78707</v>
+        <v>78799</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6775,21 +6775,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>421487</v>
+        <v>421354</v>
       </c>
       <c r="R58" t="n">
-        <v>6788638</v>
+        <v>6788463</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129124176</v>
+        <v>129124166</v>
       </c>
       <c r="B59" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,21 +6882,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>421338</v>
+        <v>421316</v>
       </c>
       <c r="R59" t="n">
-        <v>6788476</v>
+        <v>6788317</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6978,7 +6978,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129124151</v>
+        <v>129124149</v>
       </c>
       <c r="B60" t="n">
         <v>79041</v>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>421275</v>
+        <v>421376</v>
       </c>
       <c r="R60" t="n">
-        <v>6788430</v>
+        <v>6788380</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7085,10 +7085,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129124149</v>
+        <v>129124142</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7096,21 +7096,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>421376</v>
+        <v>421594</v>
       </c>
       <c r="R61" t="n">
-        <v>6788380</v>
+        <v>6787870</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7192,10 +7192,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129124061</v>
+        <v>129124151</v>
       </c>
       <c r="B62" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7203,21 +7203,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>421238</v>
+        <v>421275</v>
       </c>
       <c r="R62" t="n">
-        <v>6788555</v>
+        <v>6788430</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7299,10 +7299,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129124142</v>
+        <v>129124061</v>
       </c>
       <c r="B63" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7310,21 +7310,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>421594</v>
+        <v>421238</v>
       </c>
       <c r="R63" t="n">
-        <v>6787870</v>
+        <v>6788555</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7628,7 +7628,7 @@
         <v>129124173</v>
       </c>
       <c r="B66" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7732,50 +7732,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129124114</v>
+        <v>129124058</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>421399</v>
+        <v>421246</v>
       </c>
       <c r="R67" t="n">
-        <v>6788567</v>
+        <v>6788416</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7807,7 +7802,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7817,7 +7812,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7844,50 +7839,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129124115</v>
+        <v>129124059</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>421608</v>
+        <v>421354</v>
       </c>
       <c r="R68" t="n">
-        <v>6788661</v>
+        <v>6788463</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7919,7 +7909,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7929,7 +7919,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7956,10 +7946,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129124074</v>
+        <v>129124051</v>
       </c>
       <c r="B69" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7967,21 +7957,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7991,10 +7981,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>421236</v>
+        <v>421392</v>
       </c>
       <c r="R69" t="n">
-        <v>6788559</v>
+        <v>6788226</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8026,7 +8016,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8036,12 +8026,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På stubbe med 6 brandljud</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8068,10 +8053,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129124058</v>
+        <v>129124187</v>
       </c>
       <c r="B70" t="n">
-        <v>79660</v>
+        <v>78444</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8079,21 +8064,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8103,10 +8088,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>421246</v>
+        <v>421639</v>
       </c>
       <c r="R70" t="n">
-        <v>6788416</v>
+        <v>6788393</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8138,7 +8123,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8148,7 +8133,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8175,45 +8160,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124059</v>
+        <v>129124114</v>
       </c>
       <c r="B71" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>421354</v>
+        <v>421399</v>
       </c>
       <c r="R71" t="n">
-        <v>6788463</v>
+        <v>6788567</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8245,7 +8235,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8255,7 +8245,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8282,45 +8272,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124051</v>
+        <v>129124115</v>
       </c>
       <c r="B72" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>421392</v>
+        <v>421608</v>
       </c>
       <c r="R72" t="n">
-        <v>6788226</v>
+        <v>6788661</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8352,7 +8347,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8362,7 +8357,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8389,10 +8384,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129124187</v>
+        <v>129124074</v>
       </c>
       <c r="B73" t="n">
-        <v>78444</v>
+        <v>79631</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8400,21 +8395,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8424,10 +8419,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>421639</v>
+        <v>421236</v>
       </c>
       <c r="R73" t="n">
-        <v>6788393</v>
+        <v>6788559</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8459,7 +8454,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8469,7 +8464,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På stubbe med 6 brandljud</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8496,32 +8496,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129124146</v>
+        <v>129124145</v>
       </c>
       <c r="B74" t="n">
-        <v>91703</v>
+        <v>78798</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>421654</v>
+        <v>421591</v>
       </c>
       <c r="R74" t="n">
-        <v>6788448</v>
+        <v>6787819</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8603,10 +8603,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129124177</v>
+        <v>129124152</v>
       </c>
       <c r="B75" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8614,21 +8614,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>421318</v>
+        <v>421234</v>
       </c>
       <c r="R75" t="n">
-        <v>6788511</v>
+        <v>6788411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8710,10 +8710,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124145</v>
+        <v>129124177</v>
       </c>
       <c r="B76" t="n">
-        <v>78798</v>
+        <v>78707</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8721,21 +8721,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421591</v>
+        <v>421318</v>
       </c>
       <c r="R76" t="n">
-        <v>6787819</v>
+        <v>6788511</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8817,32 +8817,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124152</v>
+        <v>129124146</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>91712</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421234</v>
+        <v>421654</v>
       </c>
       <c r="R77" t="n">
-        <v>6788411</v>
+        <v>6788448</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9031,10 +9031,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129124143</v>
+        <v>129124090</v>
       </c>
       <c r="B79" t="n">
-        <v>78798</v>
+        <v>91560</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9042,21 +9042,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>421596</v>
+        <v>421576</v>
       </c>
       <c r="R79" t="n">
-        <v>6787835</v>
+        <v>6788373</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9111,7 +9111,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ej märkt med hänsyn</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9138,10 +9143,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129124090</v>
+        <v>129124143</v>
       </c>
       <c r="B80" t="n">
-        <v>91562</v>
+        <v>78798</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9149,21 +9154,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9173,10 +9178,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>421576</v>
+        <v>421596</v>
       </c>
       <c r="R80" t="n">
-        <v>6788373</v>
+        <v>6787835</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9208,7 +9213,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9218,12 +9223,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ej märkt med hänsyn</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9357,10 +9357,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129124157</v>
+        <v>129124134</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9368,21 +9368,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>421271</v>
+        <v>421616</v>
       </c>
       <c r="R82" t="n">
-        <v>6788641</v>
+        <v>6787882</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9464,10 +9464,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129124167</v>
+        <v>129124129</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9475,21 +9475,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9499,10 +9499,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>421342</v>
+        <v>421292</v>
       </c>
       <c r="R83" t="n">
-        <v>6788261</v>
+        <v>6788456</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9571,10 +9571,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129124148</v>
+        <v>129124083</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9582,21 +9582,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>421395</v>
+        <v>421598</v>
       </c>
       <c r="R84" t="n">
-        <v>6788374</v>
+        <v>6787829</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9678,10 +9678,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129124134</v>
+        <v>129124157</v>
       </c>
       <c r="B85" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9689,21 +9689,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9713,10 +9713,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>421616</v>
+        <v>421271</v>
       </c>
       <c r="R85" t="n">
-        <v>6787882</v>
+        <v>6788641</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9785,10 +9785,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129124129</v>
+        <v>129124167</v>
       </c>
       <c r="B86" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>421292</v>
+        <v>421342</v>
       </c>
       <c r="R86" t="n">
-        <v>6788456</v>
+        <v>6788261</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9892,10 +9892,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129124083</v>
+        <v>129124148</v>
       </c>
       <c r="B87" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9903,21 +9903,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>421598</v>
+        <v>421395</v>
       </c>
       <c r="R87" t="n">
-        <v>6787829</v>
+        <v>6788374</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9999,45 +9999,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129124150</v>
+        <v>129124123</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>421349</v>
+        <v>421446</v>
       </c>
       <c r="R88" t="n">
-        <v>6788397</v>
+        <v>6788421</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10069,7 +10074,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10079,7 +10084,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10106,50 +10111,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129124123</v>
+        <v>129124132</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>421446</v>
+        <v>421649</v>
       </c>
       <c r="R89" t="n">
-        <v>6788421</v>
+        <v>6787778</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10218,7 +10218,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129124132</v>
+        <v>129124136</v>
       </c>
       <c r="B90" t="n">
         <v>78799</v>
@@ -10253,10 +10253,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>421649</v>
+        <v>421598</v>
       </c>
       <c r="R90" t="n">
-        <v>6787778</v>
+        <v>6787834</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10325,10 +10325,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129124136</v>
+        <v>129124150</v>
       </c>
       <c r="B91" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10336,21 +10336,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10360,10 +10360,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>421598</v>
+        <v>421349</v>
       </c>
       <c r="R91" t="n">
-        <v>6787834</v>
+        <v>6788397</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10432,10 +10432,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129124096</v>
+        <v>129124102</v>
       </c>
       <c r="B92" t="n">
-        <v>57724</v>
+        <v>83002</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10443,39 +10443,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>310</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>421596</v>
+        <v>421694</v>
       </c>
       <c r="R92" t="n">
-        <v>6787836</v>
+        <v>6787682</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10507,7 +10502,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10517,7 +10512,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10544,10 +10539,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129124102</v>
+        <v>129124096</v>
       </c>
       <c r="B93" t="n">
-        <v>83002</v>
+        <v>57724</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10555,34 +10550,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>310</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>421694</v>
+        <v>421596</v>
       </c>
       <c r="R93" t="n">
-        <v>6787682</v>
+        <v>6787836</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11298,10 +11298,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129124104</v>
+        <v>129124154</v>
       </c>
       <c r="B100" t="n">
-        <v>92873</v>
+        <v>79041</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11309,43 +11309,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>421407</v>
+        <v>421303</v>
       </c>
       <c r="R100" t="n">
-        <v>6788349</v>
+        <v>6788456</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11377,7 +11368,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11387,7 +11378,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11414,7 +11405,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129124154</v>
+        <v>129124147</v>
       </c>
       <c r="B101" t="n">
         <v>79041</v>
@@ -11449,10 +11440,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>421303</v>
+        <v>421437</v>
       </c>
       <c r="R101" t="n">
-        <v>6788456</v>
+        <v>6788275</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11484,7 +11475,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11494,7 +11485,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11521,10 +11512,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129124147</v>
+        <v>129124104</v>
       </c>
       <c r="B102" t="n">
-        <v>79041</v>
+        <v>92859</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11532,34 +11523,43 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>421437</v>
+        <v>421407</v>
       </c>
       <c r="R102" t="n">
-        <v>6788275</v>
+        <v>6788349</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11591,7 +11591,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11847,10 +11847,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129124071</v>
+        <v>129124141</v>
       </c>
       <c r="B105" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11858,21 +11858,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>421598</v>
+        <v>421616</v>
       </c>
       <c r="R105" t="n">
-        <v>6787863</v>
+        <v>6787883</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11954,10 +11954,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124141</v>
+        <v>129124071</v>
       </c>
       <c r="B106" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11965,21 +11965,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11989,10 +11989,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421616</v>
+        <v>421598</v>
       </c>
       <c r="R106" t="n">
-        <v>6787883</v>
+        <v>6787863</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12280,50 +12280,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129124117</v>
+        <v>129124181</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>78707</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>421611</v>
+        <v>421537</v>
       </c>
       <c r="R109" t="n">
-        <v>6788482</v>
+        <v>6788706</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12355,7 +12350,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12365,7 +12360,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12392,50 +12387,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129124116</v>
+        <v>129124175</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>78707</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>421615</v>
+        <v>421343</v>
       </c>
       <c r="R110" t="n">
-        <v>6788580</v>
+        <v>6788400</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12467,7 +12457,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12477,7 +12467,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12504,50 +12494,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129124111</v>
+        <v>129124158</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>421315</v>
+        <v>421383</v>
       </c>
       <c r="R111" t="n">
-        <v>6788532</v>
+        <v>6788546</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12579,7 +12564,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12589,7 +12574,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12616,10 +12601,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124080</v>
+        <v>129124139</v>
       </c>
       <c r="B112" t="n">
-        <v>79631</v>
+        <v>78798</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12627,21 +12612,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12651,10 +12636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421633</v>
+        <v>421354</v>
       </c>
       <c r="R112" t="n">
-        <v>6787841</v>
+        <v>6788463</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12686,7 +12671,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12696,7 +12681,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12723,10 +12708,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129124181</v>
+        <v>129124159</v>
       </c>
       <c r="B113" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12734,21 +12719,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12758,10 +12743,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421537</v>
+        <v>421612</v>
       </c>
       <c r="R113" t="n">
-        <v>6788706</v>
+        <v>6788488</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12793,7 +12778,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12803,7 +12788,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12830,10 +12815,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129124175</v>
+        <v>129124053</v>
       </c>
       <c r="B114" t="n">
-        <v>78707</v>
+        <v>79660</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12841,21 +12826,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12865,10 +12850,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>421343</v>
+        <v>421421</v>
       </c>
       <c r="R114" t="n">
-        <v>6788400</v>
+        <v>6788216</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12900,7 +12885,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12910,7 +12895,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12937,10 +12922,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129124158</v>
+        <v>129124063</v>
       </c>
       <c r="B115" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,21 +12933,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12972,10 +12957,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>421383</v>
+        <v>421442</v>
       </c>
       <c r="R115" t="n">
-        <v>6788546</v>
+        <v>6788613</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13007,7 +12992,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13017,7 +13002,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13044,10 +13029,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129124159</v>
+        <v>129124052</v>
       </c>
       <c r="B116" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13055,21 +13040,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13079,10 +13064,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>421612</v>
+        <v>421391</v>
       </c>
       <c r="R116" t="n">
-        <v>6788488</v>
+        <v>6788209</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13114,7 +13099,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13124,7 +13109,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13151,10 +13136,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129124053</v>
+        <v>129124080</v>
       </c>
       <c r="B117" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13162,21 +13147,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13186,10 +13171,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>421421</v>
+        <v>421633</v>
       </c>
       <c r="R117" t="n">
-        <v>6788216</v>
+        <v>6787841</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13221,7 +13206,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13231,7 +13216,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13258,45 +13243,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129124063</v>
+        <v>129124117</v>
       </c>
       <c r="B118" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>421442</v>
+        <v>421611</v>
       </c>
       <c r="R118" t="n">
-        <v>6788613</v>
+        <v>6788482</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13328,7 +13318,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13338,7 +13328,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13365,45 +13355,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129124139</v>
+        <v>129124116</v>
       </c>
       <c r="B119" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>421354</v>
+        <v>421615</v>
       </c>
       <c r="R119" t="n">
-        <v>6788463</v>
+        <v>6788580</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13435,7 +13430,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13445,7 +13440,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13472,45 +13467,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129124052</v>
+        <v>129124111</v>
       </c>
       <c r="B120" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>421391</v>
+        <v>421315</v>
       </c>
       <c r="R120" t="n">
-        <v>6788209</v>
+        <v>6788532</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13579,10 +13579,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129124164</v>
+        <v>129124082</v>
       </c>
       <c r="B121" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13590,21 +13590,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13614,10 +13614,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>421345</v>
+        <v>421601</v>
       </c>
       <c r="R121" t="n">
-        <v>6788394</v>
+        <v>6787830</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13798,10 +13798,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129124082</v>
+        <v>129124054</v>
       </c>
       <c r="B123" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13809,21 +13809,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13833,10 +13833,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>421601</v>
+        <v>421423</v>
       </c>
       <c r="R123" t="n">
-        <v>6787830</v>
+        <v>6788261</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13868,7 +13868,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13905,10 +13905,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129124156</v>
+        <v>129124062</v>
       </c>
       <c r="B124" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13916,21 +13916,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>421351</v>
+        <v>421395</v>
       </c>
       <c r="R124" t="n">
-        <v>6788471</v>
+        <v>6788610</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14015,7 +14015,7 @@
         <v>129124105</v>
       </c>
       <c r="B125" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14128,10 +14128,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129124069</v>
+        <v>129124164</v>
       </c>
       <c r="B126" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14139,21 +14139,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14163,10 +14163,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>421626</v>
+        <v>421345</v>
       </c>
       <c r="R126" t="n">
-        <v>6787879</v>
+        <v>6788394</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14235,10 +14235,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129124054</v>
+        <v>129124156</v>
       </c>
       <c r="B127" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14246,21 +14246,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14270,10 +14270,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421423</v>
+        <v>421351</v>
       </c>
       <c r="R127" t="n">
-        <v>6788261</v>
+        <v>6788471</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14342,7 +14342,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129124062</v>
+        <v>129124069</v>
       </c>
       <c r="B128" t="n">
         <v>79660</v>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>421395</v>
+        <v>421626</v>
       </c>
       <c r="R128" t="n">
-        <v>6788610</v>
+        <v>6787879</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14449,45 +14449,50 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129124056</v>
+        <v>129124108</v>
       </c>
       <c r="B129" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>421343</v>
+        <v>421362</v>
       </c>
       <c r="R129" t="n">
-        <v>6788400</v>
+        <v>6788387</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14519,7 +14524,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14529,7 +14534,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14556,50 +14561,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129124108</v>
+        <v>129124056</v>
       </c>
       <c r="B130" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>421362</v>
+        <v>421343</v>
       </c>
       <c r="R130" t="n">
-        <v>6788387</v>
+        <v>6788400</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14668,10 +14668,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129124155</v>
+        <v>129124178</v>
       </c>
       <c r="B131" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14679,21 +14679,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14703,10 +14703,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>421354</v>
+        <v>421235</v>
       </c>
       <c r="R131" t="n">
-        <v>6788463</v>
+        <v>6788559</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14775,10 +14775,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129124073</v>
+        <v>129124180</v>
       </c>
       <c r="B132" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14786,21 +14786,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14810,10 +14810,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>421595</v>
+        <v>421501</v>
       </c>
       <c r="R132" t="n">
-        <v>6787823</v>
+        <v>6788671</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14882,10 +14882,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129124178</v>
+        <v>129124073</v>
       </c>
       <c r="B133" t="n">
-        <v>78707</v>
+        <v>79660</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>421235</v>
+        <v>421595</v>
       </c>
       <c r="R133" t="n">
-        <v>6788559</v>
+        <v>6787823</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14989,45 +14989,50 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129124180</v>
+        <v>129124112</v>
       </c>
       <c r="B134" t="n">
-        <v>78707</v>
+        <v>8450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>421501</v>
+        <v>421293</v>
       </c>
       <c r="R134" t="n">
-        <v>6788671</v>
+        <v>6788551</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15059,7 +15064,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15069,7 +15074,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15096,50 +15101,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129124112</v>
+        <v>129124155</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>421293</v>
+        <v>421354</v>
       </c>
       <c r="R135" t="n">
-        <v>6788551</v>
+        <v>6788463</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15208,45 +15208,50 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129124163</v>
+        <v>129124088</v>
       </c>
       <c r="B136" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>421454</v>
+        <v>421296</v>
       </c>
       <c r="R136" t="n">
-        <v>6788422</v>
+        <v>6788608</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15278,7 +15283,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15288,7 +15293,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15315,10 +15320,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129124057</v>
+        <v>129124163</v>
       </c>
       <c r="B137" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15326,21 +15331,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15350,10 +15355,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>421312</v>
+        <v>421454</v>
       </c>
       <c r="R137" t="n">
-        <v>6788393</v>
+        <v>6788422</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15385,7 +15390,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15395,7 +15400,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15422,50 +15427,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129124088</v>
+        <v>129124057</v>
       </c>
       <c r="B138" t="n">
-        <v>56917</v>
+        <v>79660</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>421296</v>
+        <v>421312</v>
       </c>
       <c r="R138" t="n">
-        <v>6788608</v>
+        <v>6788393</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15748,10 +15748,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129124068</v>
+        <v>129124169</v>
       </c>
       <c r="B141" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15759,21 +15759,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15783,10 +15783,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>421675</v>
+        <v>421618</v>
       </c>
       <c r="R141" t="n">
-        <v>6787696</v>
+        <v>6787872</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15855,7 +15855,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129124065</v>
+        <v>129124068</v>
       </c>
       <c r="B142" t="n">
         <v>79660</v>
@@ -15890,10 +15890,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>421530</v>
+        <v>421675</v>
       </c>
       <c r="R142" t="n">
-        <v>6788679</v>
+        <v>6787696</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15925,7 +15925,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15962,10 +15962,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129124169</v>
+        <v>129124065</v>
       </c>
       <c r="B143" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15973,21 +15973,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15997,10 +15997,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>421618</v>
+        <v>421530</v>
       </c>
       <c r="R143" t="n">
-        <v>6787872</v>
+        <v>6788679</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16181,45 +16181,50 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124170</v>
+        <v>129124106</v>
       </c>
       <c r="B145" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421604</v>
+        <v>421574</v>
       </c>
       <c r="R145" t="n">
-        <v>6787823</v>
+        <v>6788374</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16251,7 +16256,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16261,7 +16266,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16288,45 +16293,50 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124144</v>
+        <v>129124122</v>
       </c>
       <c r="B146" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421602</v>
+        <v>421477</v>
       </c>
       <c r="R146" t="n">
-        <v>6787829</v>
+        <v>6788422</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16358,7 +16368,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16368,7 +16378,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16395,45 +16405,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129124138</v>
+        <v>129124120</v>
       </c>
       <c r="B147" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>421292</v>
+        <v>421520</v>
       </c>
       <c r="R147" t="n">
-        <v>6788456</v>
+        <v>6788366</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16465,7 +16480,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16475,7 +16490,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16502,50 +16517,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129124106</v>
+        <v>129124133</v>
       </c>
       <c r="B148" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421574</v>
+        <v>421633</v>
       </c>
       <c r="R148" t="n">
-        <v>6788374</v>
+        <v>6787841</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16577,7 +16587,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16587,7 +16597,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16614,50 +16624,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124122</v>
+        <v>129124078</v>
       </c>
       <c r="B149" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421477</v>
+        <v>421640</v>
       </c>
       <c r="R149" t="n">
-        <v>6788422</v>
+        <v>6788394</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16689,7 +16694,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16699,7 +16704,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16726,50 +16731,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124120</v>
+        <v>129124144</v>
       </c>
       <c r="B150" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421520</v>
+        <v>421602</v>
       </c>
       <c r="R150" t="n">
-        <v>6788366</v>
+        <v>6787829</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16801,7 +16801,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16838,10 +16838,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124087</v>
+        <v>129124170</v>
       </c>
       <c r="B151" t="n">
-        <v>79136</v>
+        <v>79041</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16849,21 +16849,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16873,10 +16873,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421601</v>
+        <v>421604</v>
       </c>
       <c r="R151" t="n">
-        <v>6787830</v>
+        <v>6787823</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16945,10 +16945,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129124133</v>
+        <v>129124138</v>
       </c>
       <c r="B152" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16956,21 +16956,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16980,10 +16980,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>421633</v>
+        <v>421292</v>
       </c>
       <c r="R152" t="n">
-        <v>6787841</v>
+        <v>6788456</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17052,10 +17052,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129124078</v>
+        <v>129124087</v>
       </c>
       <c r="B153" t="n">
-        <v>79631</v>
+        <v>79136</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17063,21 +17063,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17087,10 +17087,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>421640</v>
+        <v>421601</v>
       </c>
       <c r="R153" t="n">
-        <v>6788394</v>
+        <v>6787830</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17159,10 +17159,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129124064</v>
+        <v>129124186</v>
       </c>
       <c r="B154" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17170,21 +17170,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17194,10 +17194,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>421501</v>
+        <v>421626</v>
       </c>
       <c r="R154" t="n">
-        <v>6788671</v>
+        <v>6787877</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17373,10 +17373,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129124186</v>
+        <v>129124064</v>
       </c>
       <c r="B156" t="n">
-        <v>78707</v>
+        <v>79660</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17384,21 +17384,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17408,10 +17408,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>421626</v>
+        <v>421501</v>
       </c>
       <c r="R156" t="n">
-        <v>6787877</v>
+        <v>6788671</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17443,7 +17443,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17453,7 +17453,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17480,45 +17480,50 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129124076</v>
+        <v>129124119</v>
       </c>
       <c r="B157" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>421240</v>
+        <v>421653</v>
       </c>
       <c r="R157" t="n">
-        <v>6788558</v>
+        <v>6788387</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17550,7 +17555,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17560,7 +17565,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17587,7 +17592,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129124084</v>
+        <v>129124076</v>
       </c>
       <c r="B158" t="n">
         <v>79631</v>
@@ -17622,10 +17627,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>421591</v>
+        <v>421240</v>
       </c>
       <c r="R158" t="n">
-        <v>6787819</v>
+        <v>6788558</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17657,7 +17662,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17667,7 +17672,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17694,50 +17699,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129124119</v>
+        <v>129124084</v>
       </c>
       <c r="B159" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>421653</v>
+        <v>421591</v>
       </c>
       <c r="R159" t="n">
-        <v>6788387</v>
+        <v>6787819</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129124171</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129124161</v>
+        <v>129124183</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421701</v>
+        <v>421744</v>
       </c>
       <c r="R9" t="n">
-        <v>6788470</v>
+        <v>6788480</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129124183</v>
+        <v>129124161</v>
       </c>
       <c r="B10" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421744</v>
+        <v>421701</v>
       </c>
       <c r="R10" t="n">
-        <v>6788480</v>
+        <v>6788470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129093027</v>
+        <v>129094012</v>
       </c>
       <c r="B14" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,21 +2042,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421341</v>
+        <v>421379</v>
       </c>
       <c r="R14" t="n">
-        <v>6788261</v>
+        <v>6788540</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129094012</v>
+        <v>129093983</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421379</v>
+        <v>421400</v>
       </c>
       <c r="R15" t="n">
-        <v>6788540</v>
+        <v>6788524</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2245,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129093983</v>
+        <v>129095317</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421400</v>
+        <v>421398</v>
       </c>
       <c r="R16" t="n">
-        <v>6788524</v>
+        <v>6788372</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129095317</v>
+        <v>129094871</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,34 +2363,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421398</v>
+        <v>421534</v>
       </c>
       <c r="R17" t="n">
-        <v>6788372</v>
+        <v>6788452</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2459,10 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129094871</v>
+        <v>129093027</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2470,39 +2475,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421534</v>
+        <v>421341</v>
       </c>
       <c r="R18" t="n">
-        <v>6788452</v>
+        <v>6788261</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129094072</v>
+        <v>129095256</v>
       </c>
       <c r="B34" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421379</v>
+        <v>421440</v>
       </c>
       <c r="R34" t="n">
-        <v>6788540</v>
+        <v>6788407</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129095256</v>
+        <v>129094072</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4294,21 +4294,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>421440</v>
+        <v>421379</v>
       </c>
       <c r="R35" t="n">
-        <v>6788407</v>
+        <v>6788540</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -6550,10 +6550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124160</v>
+        <v>129124070</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,21 +6561,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421611</v>
+        <v>421616</v>
       </c>
       <c r="R56" t="n">
-        <v>6788481</v>
+        <v>6787882</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6657,10 +6657,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129124070</v>
+        <v>129124160</v>
       </c>
       <c r="B57" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,21 +6668,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>421616</v>
+        <v>421611</v>
       </c>
       <c r="R57" t="n">
-        <v>6787882</v>
+        <v>6788481</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6764,10 +6764,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129124130</v>
+        <v>129124166</v>
       </c>
       <c r="B58" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6775,21 +6775,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>421354</v>
+        <v>421316</v>
       </c>
       <c r="R58" t="n">
-        <v>6788463</v>
+        <v>6788317</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129124166</v>
+        <v>129124130</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,21 +6882,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>421316</v>
+        <v>421354</v>
       </c>
       <c r="R59" t="n">
-        <v>6788317</v>
+        <v>6788463</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6978,10 +6978,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129124149</v>
+        <v>129124142</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,21 +6989,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>421376</v>
+        <v>421594</v>
       </c>
       <c r="R60" t="n">
-        <v>6788380</v>
+        <v>6787870</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7085,10 +7085,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129124142</v>
+        <v>129124061</v>
       </c>
       <c r="B61" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7096,21 +7096,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>421594</v>
+        <v>421238</v>
       </c>
       <c r="R61" t="n">
-        <v>6787870</v>
+        <v>6788555</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7192,7 +7192,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129124151</v>
+        <v>129124149</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>421275</v>
+        <v>421376</v>
       </c>
       <c r="R62" t="n">
-        <v>6788430</v>
+        <v>6788380</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7299,10 +7299,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129124061</v>
+        <v>129124151</v>
       </c>
       <c r="B63" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7310,21 +7310,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>421238</v>
+        <v>421275</v>
       </c>
       <c r="R63" t="n">
-        <v>6788555</v>
+        <v>6788430</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7628,7 +7628,7 @@
         <v>129124173</v>
       </c>
       <c r="B66" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7732,10 +7732,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129124058</v>
+        <v>129124187</v>
       </c>
       <c r="B67" t="n">
-        <v>79660</v>
+        <v>78444</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7743,21 +7743,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>421246</v>
+        <v>421639</v>
       </c>
       <c r="R67" t="n">
-        <v>6788416</v>
+        <v>6788393</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7839,45 +7839,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129124059</v>
+        <v>129124115</v>
       </c>
       <c r="B68" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>421354</v>
+        <v>421608</v>
       </c>
       <c r="R68" t="n">
-        <v>6788463</v>
+        <v>6788661</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7909,7 +7914,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7919,7 +7924,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7946,45 +7951,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129124051</v>
+        <v>129124114</v>
       </c>
       <c r="B69" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>421392</v>
+        <v>421399</v>
       </c>
       <c r="R69" t="n">
-        <v>6788226</v>
+        <v>6788567</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8016,7 +8026,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8026,7 +8036,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8053,10 +8063,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129124187</v>
+        <v>129124058</v>
       </c>
       <c r="B70" t="n">
-        <v>78444</v>
+        <v>79660</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8064,21 +8074,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8088,10 +8098,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>421639</v>
+        <v>421246</v>
       </c>
       <c r="R70" t="n">
-        <v>6788393</v>
+        <v>6788416</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8123,7 +8133,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8133,7 +8143,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8160,50 +8170,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124114</v>
+        <v>129124059</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>421399</v>
+        <v>421354</v>
       </c>
       <c r="R71" t="n">
-        <v>6788567</v>
+        <v>6788463</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8235,7 +8240,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8245,7 +8250,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8272,50 +8277,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124115</v>
+        <v>129124051</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>421608</v>
+        <v>421392</v>
       </c>
       <c r="R72" t="n">
-        <v>6788661</v>
+        <v>6788226</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8603,10 +8603,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129124152</v>
+        <v>129124103</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8614,21 +8614,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>421234</v>
+        <v>421618</v>
       </c>
       <c r="R75" t="n">
-        <v>6788411</v>
+        <v>6787832</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8710,32 +8710,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124177</v>
+        <v>129124146</v>
       </c>
       <c r="B76" t="n">
-        <v>78707</v>
+        <v>91713</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421318</v>
+        <v>421654</v>
       </c>
       <c r="R76" t="n">
-        <v>6788511</v>
+        <v>6788448</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8817,32 +8817,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124146</v>
+        <v>129124177</v>
       </c>
       <c r="B77" t="n">
-        <v>91712</v>
+        <v>78707</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421654</v>
+        <v>421318</v>
       </c>
       <c r="R77" t="n">
-        <v>6788448</v>
+        <v>6788511</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8924,10 +8924,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129124103</v>
+        <v>129124152</v>
       </c>
       <c r="B78" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8935,21 +8935,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>421618</v>
+        <v>421234</v>
       </c>
       <c r="R78" t="n">
-        <v>6787832</v>
+        <v>6788411</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9031,10 +9031,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129124090</v>
+        <v>129124143</v>
       </c>
       <c r="B79" t="n">
-        <v>91560</v>
+        <v>78798</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9042,21 +9042,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>421576</v>
+        <v>421596</v>
       </c>
       <c r="R79" t="n">
-        <v>6788373</v>
+        <v>6787835</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9111,12 +9111,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ej märkt med hänsyn</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9143,10 +9138,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129124143</v>
+        <v>129124090</v>
       </c>
       <c r="B80" t="n">
-        <v>78798</v>
+        <v>91561</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9154,21 +9149,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9178,10 +9173,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>421596</v>
+        <v>421576</v>
       </c>
       <c r="R80" t="n">
-        <v>6787835</v>
+        <v>6788373</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9213,7 +9208,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9223,7 +9218,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ej märkt med hänsyn</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9357,10 +9357,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129124134</v>
+        <v>129124157</v>
       </c>
       <c r="B82" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9368,21 +9368,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>421616</v>
+        <v>421271</v>
       </c>
       <c r="R82" t="n">
-        <v>6787882</v>
+        <v>6788641</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9464,10 +9464,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129124129</v>
+        <v>129124167</v>
       </c>
       <c r="B83" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9475,21 +9475,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9499,10 +9499,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>421292</v>
+        <v>421342</v>
       </c>
       <c r="R83" t="n">
-        <v>6788456</v>
+        <v>6788261</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9571,10 +9571,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129124083</v>
+        <v>129124148</v>
       </c>
       <c r="B84" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9582,21 +9582,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>421598</v>
+        <v>421395</v>
       </c>
       <c r="R84" t="n">
-        <v>6787829</v>
+        <v>6788374</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9678,10 +9678,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129124157</v>
+        <v>129124134</v>
       </c>
       <c r="B85" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9689,21 +9689,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9713,10 +9713,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>421271</v>
+        <v>421616</v>
       </c>
       <c r="R85" t="n">
-        <v>6788641</v>
+        <v>6787882</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9785,10 +9785,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129124167</v>
+        <v>129124129</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>421342</v>
+        <v>421292</v>
       </c>
       <c r="R86" t="n">
-        <v>6788261</v>
+        <v>6788456</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9892,10 +9892,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129124148</v>
+        <v>129124083</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9903,21 +9903,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>421395</v>
+        <v>421598</v>
       </c>
       <c r="R87" t="n">
-        <v>6788374</v>
+        <v>6787829</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10111,10 +10111,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129124132</v>
+        <v>129124150</v>
       </c>
       <c r="B89" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10122,21 +10122,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>421649</v>
+        <v>421349</v>
       </c>
       <c r="R89" t="n">
-        <v>6787778</v>
+        <v>6788397</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10218,7 +10218,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129124136</v>
+        <v>129124132</v>
       </c>
       <c r="B90" t="n">
         <v>78799</v>
@@ -10253,10 +10253,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>421598</v>
+        <v>421649</v>
       </c>
       <c r="R90" t="n">
-        <v>6787834</v>
+        <v>6787778</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10325,10 +10325,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129124150</v>
+        <v>129124136</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10336,21 +10336,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10360,10 +10360,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>421349</v>
+        <v>421598</v>
       </c>
       <c r="R91" t="n">
-        <v>6788397</v>
+        <v>6787834</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10432,10 +10432,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129124102</v>
+        <v>129124096</v>
       </c>
       <c r="B92" t="n">
-        <v>83002</v>
+        <v>57724</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10443,34 +10443,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>310</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>421694</v>
+        <v>421596</v>
       </c>
       <c r="R92" t="n">
-        <v>6787682</v>
+        <v>6787836</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10502,7 +10507,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10512,7 +10517,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10539,10 +10544,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129124096</v>
+        <v>129124102</v>
       </c>
       <c r="B93" t="n">
-        <v>57724</v>
+        <v>83002</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10550,39 +10555,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>310</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>421596</v>
+        <v>421694</v>
       </c>
       <c r="R93" t="n">
-        <v>6787836</v>
+        <v>6787682</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10865,10 +10865,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129124153</v>
+        <v>129124060</v>
       </c>
       <c r="B96" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10876,21 +10876,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10900,10 +10900,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>421305</v>
+        <v>421338</v>
       </c>
       <c r="R96" t="n">
-        <v>6788474</v>
+        <v>6788476</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10972,7 +10972,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129124060</v>
+        <v>129124072</v>
       </c>
       <c r="B97" t="n">
         <v>79660</v>
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>421338</v>
+        <v>421591</v>
       </c>
       <c r="R97" t="n">
-        <v>6788476</v>
+        <v>6787819</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11079,10 +11079,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129124072</v>
+        <v>129124153</v>
       </c>
       <c r="B98" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11090,21 +11090,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11114,10 +11114,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>421591</v>
+        <v>421305</v>
       </c>
       <c r="R98" t="n">
-        <v>6787819</v>
+        <v>6788474</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11149,7 +11149,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11298,10 +11298,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129124154</v>
+        <v>129124104</v>
       </c>
       <c r="B100" t="n">
-        <v>79041</v>
+        <v>92860</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11309,34 +11309,43 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>421303</v>
+        <v>421407</v>
       </c>
       <c r="R100" t="n">
-        <v>6788456</v>
+        <v>6788349</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11368,7 +11377,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11378,7 +11387,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11405,7 +11414,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129124147</v>
+        <v>129124154</v>
       </c>
       <c r="B101" t="n">
         <v>79041</v>
@@ -11440,10 +11449,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>421437</v>
+        <v>421303</v>
       </c>
       <c r="R101" t="n">
-        <v>6788275</v>
+        <v>6788456</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11475,7 +11484,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11485,7 +11494,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11512,10 +11521,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129124104</v>
+        <v>129124147</v>
       </c>
       <c r="B102" t="n">
-        <v>92859</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11523,43 +11532,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>421407</v>
+        <v>421437</v>
       </c>
       <c r="R102" t="n">
-        <v>6788349</v>
+        <v>6788275</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11591,7 +11591,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11740,10 +11740,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129124165</v>
+        <v>129124141</v>
       </c>
       <c r="B104" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11751,21 +11751,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11775,10 +11775,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>421340</v>
+        <v>421616</v>
       </c>
       <c r="R104" t="n">
-        <v>6788389</v>
+        <v>6787883</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11847,10 +11847,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129124141</v>
+        <v>129124071</v>
       </c>
       <c r="B105" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11858,21 +11858,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>421616</v>
+        <v>421598</v>
       </c>
       <c r="R105" t="n">
-        <v>6787883</v>
+        <v>6787863</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11954,10 +11954,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124071</v>
+        <v>129124165</v>
       </c>
       <c r="B106" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11965,21 +11965,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11989,10 +11989,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421598</v>
+        <v>421340</v>
       </c>
       <c r="R106" t="n">
-        <v>6787863</v>
+        <v>6788389</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12280,10 +12280,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129124181</v>
+        <v>129124139</v>
       </c>
       <c r="B109" t="n">
-        <v>78707</v>
+        <v>78798</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12291,21 +12291,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>421537</v>
+        <v>421354</v>
       </c>
       <c r="R109" t="n">
-        <v>6788706</v>
+        <v>6788463</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12387,10 +12387,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129124175</v>
+        <v>129124053</v>
       </c>
       <c r="B110" t="n">
-        <v>78707</v>
+        <v>79660</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12398,21 +12398,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12422,10 +12422,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>421343</v>
+        <v>421421</v>
       </c>
       <c r="R110" t="n">
-        <v>6788400</v>
+        <v>6788216</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12494,10 +12494,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129124158</v>
+        <v>129124063</v>
       </c>
       <c r="B111" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>421383</v>
+        <v>421442</v>
       </c>
       <c r="R111" t="n">
-        <v>6788546</v>
+        <v>6788613</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12601,10 +12601,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124139</v>
+        <v>129124052</v>
       </c>
       <c r="B112" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12612,21 +12612,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421354</v>
+        <v>421391</v>
       </c>
       <c r="R112" t="n">
-        <v>6788463</v>
+        <v>6788209</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12708,7 +12708,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129124159</v>
+        <v>129124158</v>
       </c>
       <c r="B113" t="n">
         <v>79041</v>
@@ -12743,10 +12743,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421612</v>
+        <v>421383</v>
       </c>
       <c r="R113" t="n">
-        <v>6788488</v>
+        <v>6788546</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12815,10 +12815,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129124053</v>
+        <v>129124159</v>
       </c>
       <c r="B114" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12826,21 +12826,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>421421</v>
+        <v>421612</v>
       </c>
       <c r="R114" t="n">
-        <v>6788216</v>
+        <v>6788488</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12922,45 +12922,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129124063</v>
+        <v>129124111</v>
       </c>
       <c r="B115" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>421442</v>
+        <v>421315</v>
       </c>
       <c r="R115" t="n">
-        <v>6788613</v>
+        <v>6788532</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12992,7 +12997,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13002,7 +13007,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13029,45 +13034,50 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129124052</v>
+        <v>129124116</v>
       </c>
       <c r="B116" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>421391</v>
+        <v>421615</v>
       </c>
       <c r="R116" t="n">
-        <v>6788209</v>
+        <v>6788580</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13099,7 +13109,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13109,7 +13119,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13136,45 +13146,50 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129124080</v>
+        <v>129124117</v>
       </c>
       <c r="B117" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>421633</v>
+        <v>421611</v>
       </c>
       <c r="R117" t="n">
-        <v>6787841</v>
+        <v>6788482</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13206,7 +13221,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13216,7 +13231,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13243,50 +13258,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129124117</v>
+        <v>129124080</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>421611</v>
+        <v>421633</v>
       </c>
       <c r="R118" t="n">
-        <v>6788482</v>
+        <v>6787841</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13318,7 +13328,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13328,7 +13338,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13355,50 +13365,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129124116</v>
+        <v>129124181</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>78707</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>421615</v>
+        <v>421537</v>
       </c>
       <c r="R119" t="n">
-        <v>6788580</v>
+        <v>6788706</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13430,7 +13435,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13440,7 +13445,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13467,50 +13472,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129124111</v>
+        <v>129124175</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>78707</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>421315</v>
+        <v>421343</v>
       </c>
       <c r="R120" t="n">
-        <v>6788532</v>
+        <v>6788400</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13579,10 +13579,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129124082</v>
+        <v>129124105</v>
       </c>
       <c r="B121" t="n">
-        <v>79631</v>
+        <v>92860</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13590,34 +13590,43 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>421601</v>
+        <v>421613</v>
       </c>
       <c r="R121" t="n">
-        <v>6787830</v>
+        <v>6788634</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13649,7 +13658,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13659,7 +13668,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13686,50 +13695,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129124121</v>
+        <v>129124069</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>421524</v>
+        <v>421626</v>
       </c>
       <c r="R122" t="n">
-        <v>6788399</v>
+        <v>6787879</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13761,7 +13765,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13771,7 +13775,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13905,10 +13909,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129124062</v>
+        <v>129124164</v>
       </c>
       <c r="B124" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13916,21 +13920,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13940,10 +13944,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>421395</v>
+        <v>421345</v>
       </c>
       <c r="R124" t="n">
-        <v>6788610</v>
+        <v>6788394</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13975,7 +13979,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13985,7 +13989,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14012,10 +14016,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129124105</v>
+        <v>129124156</v>
       </c>
       <c r="B125" t="n">
-        <v>92859</v>
+        <v>79041</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14023,43 +14027,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>421613</v>
+        <v>421351</v>
       </c>
       <c r="R125" t="n">
-        <v>6788634</v>
+        <v>6788471</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14091,7 +14086,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14101,7 +14096,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14128,45 +14123,50 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129124164</v>
+        <v>129124121</v>
       </c>
       <c r="B126" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>421345</v>
+        <v>421524</v>
       </c>
       <c r="R126" t="n">
-        <v>6788394</v>
+        <v>6788399</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14235,10 +14235,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129124156</v>
+        <v>129124062</v>
       </c>
       <c r="B127" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14246,21 +14246,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14270,10 +14270,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421351</v>
+        <v>421395</v>
       </c>
       <c r="R127" t="n">
-        <v>6788471</v>
+        <v>6788610</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14342,10 +14342,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129124069</v>
+        <v>129124082</v>
       </c>
       <c r="B128" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14353,21 +14353,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>421626</v>
+        <v>421601</v>
       </c>
       <c r="R128" t="n">
-        <v>6787879</v>
+        <v>6787830</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14668,10 +14668,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129124178</v>
+        <v>129124155</v>
       </c>
       <c r="B131" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14679,21 +14679,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14703,10 +14703,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>421235</v>
+        <v>421354</v>
       </c>
       <c r="R131" t="n">
-        <v>6788559</v>
+        <v>6788463</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14775,7 +14775,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129124180</v>
+        <v>129124178</v>
       </c>
       <c r="B132" t="n">
         <v>78707</v>
@@ -14810,10 +14810,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>421501</v>
+        <v>421235</v>
       </c>
       <c r="R132" t="n">
-        <v>6788671</v>
+        <v>6788559</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14882,10 +14882,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129124073</v>
+        <v>129124180</v>
       </c>
       <c r="B133" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>421595</v>
+        <v>421501</v>
       </c>
       <c r="R133" t="n">
-        <v>6787823</v>
+        <v>6788671</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14989,50 +14989,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129124112</v>
+        <v>129124073</v>
       </c>
       <c r="B134" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>421293</v>
+        <v>421595</v>
       </c>
       <c r="R134" t="n">
-        <v>6788551</v>
+        <v>6787823</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15064,7 +15059,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15074,7 +15069,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15101,45 +15096,50 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129124155</v>
+        <v>129124112</v>
       </c>
       <c r="B135" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>421354</v>
+        <v>421293</v>
       </c>
       <c r="R135" t="n">
-        <v>6788463</v>
+        <v>6788551</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15208,50 +15208,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129124088</v>
+        <v>129124057</v>
       </c>
       <c r="B136" t="n">
-        <v>56917</v>
+        <v>79660</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>421296</v>
+        <v>421312</v>
       </c>
       <c r="R136" t="n">
-        <v>6788608</v>
+        <v>6788393</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15283,7 +15278,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15293,7 +15288,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15320,45 +15315,50 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129124163</v>
+        <v>129124088</v>
       </c>
       <c r="B137" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>421454</v>
+        <v>421296</v>
       </c>
       <c r="R137" t="n">
-        <v>6788422</v>
+        <v>6788608</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15390,7 +15390,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15427,10 +15427,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129124057</v>
+        <v>129124163</v>
       </c>
       <c r="B138" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15438,21 +15438,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15462,10 +15462,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>421312</v>
+        <v>421454</v>
       </c>
       <c r="R138" t="n">
-        <v>6788393</v>
+        <v>6788422</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15748,10 +15748,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129124169</v>
+        <v>129124068</v>
       </c>
       <c r="B141" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15759,21 +15759,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15783,10 +15783,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>421618</v>
+        <v>421675</v>
       </c>
       <c r="R141" t="n">
-        <v>6787872</v>
+        <v>6787696</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15855,7 +15855,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129124068</v>
+        <v>129124065</v>
       </c>
       <c r="B142" t="n">
         <v>79660</v>
@@ -15890,10 +15890,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>421675</v>
+        <v>421530</v>
       </c>
       <c r="R142" t="n">
-        <v>6787696</v>
+        <v>6788679</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15925,7 +15925,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15962,10 +15962,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129124065</v>
+        <v>129124169</v>
       </c>
       <c r="B143" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15973,21 +15973,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15997,10 +15997,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>421530</v>
+        <v>421618</v>
       </c>
       <c r="R143" t="n">
-        <v>6788679</v>
+        <v>6787872</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16181,7 +16181,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124106</v>
+        <v>129124120</v>
       </c>
       <c r="B145" t="n">
         <v>8450</v>
@@ -16212,7 +16212,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16221,10 +16221,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421574</v>
+        <v>421520</v>
       </c>
       <c r="R145" t="n">
-        <v>6788374</v>
+        <v>6788366</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16293,7 +16293,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124122</v>
+        <v>129124106</v>
       </c>
       <c r="B146" t="n">
         <v>8450</v>
@@ -16324,7 +16324,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -16333,10 +16333,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421477</v>
+        <v>421574</v>
       </c>
       <c r="R146" t="n">
-        <v>6788422</v>
+        <v>6788374</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16368,7 +16368,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16378,7 +16378,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16405,50 +16405,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129124120</v>
+        <v>129124133</v>
       </c>
       <c r="B147" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>421520</v>
+        <v>421633</v>
       </c>
       <c r="R147" t="n">
-        <v>6788366</v>
+        <v>6787841</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16480,7 +16475,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16490,7 +16485,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16517,10 +16512,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129124133</v>
+        <v>129124078</v>
       </c>
       <c r="B148" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16528,21 +16523,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16552,10 +16547,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421633</v>
+        <v>421640</v>
       </c>
       <c r="R148" t="n">
-        <v>6787841</v>
+        <v>6788394</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16587,7 +16582,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16597,7 +16592,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16624,45 +16619,50 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124078</v>
+        <v>129124122</v>
       </c>
       <c r="B149" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421640</v>
+        <v>421477</v>
       </c>
       <c r="R149" t="n">
-        <v>6788394</v>
+        <v>6788422</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16731,10 +16731,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124144</v>
+        <v>129124087</v>
       </c>
       <c r="B150" t="n">
-        <v>78798</v>
+        <v>79136</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16742,21 +16742,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16766,10 +16766,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421602</v>
+        <v>421601</v>
       </c>
       <c r="R150" t="n">
-        <v>6787829</v>
+        <v>6787830</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16838,10 +16838,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124170</v>
+        <v>129124144</v>
       </c>
       <c r="B151" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16849,21 +16849,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16873,10 +16873,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421604</v>
+        <v>421602</v>
       </c>
       <c r="R151" t="n">
-        <v>6787823</v>
+        <v>6787829</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17052,10 +17052,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129124087</v>
+        <v>129124170</v>
       </c>
       <c r="B153" t="n">
-        <v>79136</v>
+        <v>79041</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17063,21 +17063,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17087,10 +17087,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>421601</v>
+        <v>421604</v>
       </c>
       <c r="R153" t="n">
-        <v>6787830</v>
+        <v>6787823</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17159,10 +17159,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129124186</v>
+        <v>129124064</v>
       </c>
       <c r="B154" t="n">
-        <v>78707</v>
+        <v>79660</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17170,21 +17170,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17194,10 +17194,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>421626</v>
+        <v>421501</v>
       </c>
       <c r="R154" t="n">
-        <v>6787877</v>
+        <v>6788671</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17266,45 +17266,50 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129124137</v>
+        <v>129124119</v>
       </c>
       <c r="B155" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>421312</v>
+        <v>421653</v>
       </c>
       <c r="R155" t="n">
-        <v>6788393</v>
+        <v>6788387</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17336,7 +17341,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17346,7 +17351,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17373,10 +17378,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129124064</v>
+        <v>129124186</v>
       </c>
       <c r="B156" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17384,21 +17389,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17408,10 +17413,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>421501</v>
+        <v>421626</v>
       </c>
       <c r="R156" t="n">
-        <v>6788671</v>
+        <v>6787877</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17443,7 +17448,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17453,7 +17458,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17480,50 +17485,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129124119</v>
+        <v>129124137</v>
       </c>
       <c r="B157" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>421653</v>
+        <v>421312</v>
       </c>
       <c r="R157" t="n">
-        <v>6788387</v>
+        <v>6788393</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17555,7 +17555,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17565,7 +17565,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD157" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129094012</v>
+        <v>129094871</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,34 +2042,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421379</v>
+        <v>421534</v>
       </c>
       <c r="R14" t="n">
-        <v>6788540</v>
+        <v>6788452</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,10 +2143,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129093983</v>
+        <v>129093027</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2149,21 +2154,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2173,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421400</v>
+        <v>421341</v>
       </c>
       <c r="R15" t="n">
-        <v>6788524</v>
+        <v>6788261</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2250,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129095317</v>
+        <v>129093983</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2280,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421398</v>
+        <v>421400</v>
       </c>
       <c r="R16" t="n">
-        <v>6788372</v>
+        <v>6788524</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,10 +2357,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129094871</v>
+        <v>129095317</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,39 +2368,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421534</v>
+        <v>421398</v>
       </c>
       <c r="R17" t="n">
-        <v>6788452</v>
+        <v>6788372</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,10 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129093027</v>
+        <v>129094012</v>
       </c>
       <c r="B18" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,21 +2475,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421341</v>
+        <v>421379</v>
       </c>
       <c r="R18" t="n">
-        <v>6788261</v>
+        <v>6788540</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129093188</v>
+        <v>129093202</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129093167</v>
+        <v>129094076</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421391</v>
+        <v>421379</v>
       </c>
       <c r="R24" t="n">
-        <v>6788314</v>
+        <v>6788540</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129094076</v>
+        <v>129093167</v>
       </c>
       <c r="B25" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,21 +3224,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421379</v>
+        <v>421391</v>
       </c>
       <c r="R25" t="n">
-        <v>6788540</v>
+        <v>6788314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3534,32 +3534,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129094800</v>
+        <v>129094249</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421501</v>
+        <v>421564</v>
       </c>
       <c r="R28" t="n">
-        <v>6788477</v>
+        <v>6788544</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,32 +3641,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129094249</v>
+        <v>129094800</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421564</v>
+        <v>421501</v>
       </c>
       <c r="R29" t="n">
-        <v>6788544</v>
+        <v>6788477</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3855,7 +3855,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129093018</v>
+        <v>129094179</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421341</v>
+        <v>421509</v>
       </c>
       <c r="R31" t="n">
-        <v>6788261</v>
+        <v>6788597</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3962,7 +3962,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129094179</v>
+        <v>129093018</v>
       </c>
       <c r="B32" t="n">
         <v>79041</v>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>421509</v>
+        <v>421341</v>
       </c>
       <c r="R32" t="n">
-        <v>6788597</v>
+        <v>6788261</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129095256</v>
+        <v>129094072</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421440</v>
+        <v>421379</v>
       </c>
       <c r="R34" t="n">
-        <v>6788407</v>
+        <v>6788540</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129094072</v>
+        <v>129095256</v>
       </c>
       <c r="B35" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4294,21 +4294,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>421379</v>
+        <v>421440</v>
       </c>
       <c r="R35" t="n">
-        <v>6788540</v>
+        <v>6788407</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4925,10 +4925,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129093226</v>
+        <v>129094242</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4936,34 +4936,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>421395</v>
+        <v>421564</v>
       </c>
       <c r="R41" t="n">
-        <v>6788438</v>
+        <v>6788544</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5032,45 +5037,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129093117</v>
+        <v>129095090</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>421391</v>
+        <v>421500</v>
       </c>
       <c r="R42" t="n">
-        <v>6788314</v>
+        <v>6788425</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5139,7 +5149,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129094242</v>
+        <v>129094162</v>
       </c>
       <c r="B43" t="n">
         <v>57724</v>
@@ -5179,10 +5189,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>421564</v>
+        <v>421499</v>
       </c>
       <c r="R43" t="n">
-        <v>6788544</v>
+        <v>6788592</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5251,50 +5261,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129094162</v>
+        <v>129093117</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>421499</v>
+        <v>421391</v>
       </c>
       <c r="R44" t="n">
-        <v>6788592</v>
+        <v>6788314</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,10 +5368,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129095090</v>
+        <v>129093226</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5374,39 +5379,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>421500</v>
+        <v>421395</v>
       </c>
       <c r="R45" t="n">
-        <v>6788425</v>
+        <v>6788438</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5903,45 +5903,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129094103</v>
+        <v>129095582</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>421421</v>
+        <v>421342</v>
       </c>
       <c r="R50" t="n">
-        <v>6788547</v>
+        <v>6788310</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6010,50 +6015,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129095582</v>
+        <v>129094103</v>
       </c>
       <c r="B51" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>421342</v>
+        <v>421421</v>
       </c>
       <c r="R51" t="n">
-        <v>6788310</v>
+        <v>6788547</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6229,10 +6229,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129124182</v>
+        <v>129124160</v>
       </c>
       <c r="B53" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6240,21 +6240,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>421622</v>
+        <v>421611</v>
       </c>
       <c r="R53" t="n">
-        <v>6788520</v>
+        <v>6788481</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6336,10 +6336,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129124179</v>
+        <v>129124070</v>
       </c>
       <c r="B54" t="n">
-        <v>78707</v>
+        <v>79660</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>421487</v>
+        <v>421616</v>
       </c>
       <c r="R54" t="n">
-        <v>6788638</v>
+        <v>6787882</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6443,10 +6443,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129124176</v>
+        <v>129124130</v>
       </c>
       <c r="B55" t="n">
-        <v>78707</v>
+        <v>78799</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6454,21 +6454,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>421338</v>
+        <v>421354</v>
       </c>
       <c r="R55" t="n">
-        <v>6788476</v>
+        <v>6788463</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124070</v>
+        <v>129124166</v>
       </c>
       <c r="B56" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,21 +6561,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421616</v>
+        <v>421316</v>
       </c>
       <c r="R56" t="n">
-        <v>6787882</v>
+        <v>6788317</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6657,10 +6657,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129124160</v>
+        <v>129124182</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,21 +6668,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>421611</v>
+        <v>421622</v>
       </c>
       <c r="R57" t="n">
-        <v>6788481</v>
+        <v>6788520</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6764,10 +6764,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129124166</v>
+        <v>129124179</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6775,21 +6775,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>421316</v>
+        <v>421487</v>
       </c>
       <c r="R58" t="n">
-        <v>6788317</v>
+        <v>6788638</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129124130</v>
+        <v>129124176</v>
       </c>
       <c r="B59" t="n">
-        <v>78799</v>
+        <v>78707</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,21 +6882,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>421354</v>
+        <v>421338</v>
       </c>
       <c r="R59" t="n">
-        <v>6788463</v>
+        <v>6788476</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6978,10 +6978,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129124142</v>
+        <v>129124061</v>
       </c>
       <c r="B60" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,21 +6989,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>421594</v>
+        <v>421238</v>
       </c>
       <c r="R60" t="n">
-        <v>6787870</v>
+        <v>6788555</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7085,10 +7085,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129124061</v>
+        <v>129124142</v>
       </c>
       <c r="B61" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7096,21 +7096,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>421238</v>
+        <v>421594</v>
       </c>
       <c r="R61" t="n">
-        <v>6788555</v>
+        <v>6787870</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7192,7 +7192,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129124149</v>
+        <v>129124151</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>421376</v>
+        <v>421275</v>
       </c>
       <c r="R62" t="n">
-        <v>6788380</v>
+        <v>6788430</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7299,10 +7299,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129124151</v>
+        <v>129124131</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7310,21 +7310,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>421275</v>
+        <v>421659</v>
       </c>
       <c r="R63" t="n">
-        <v>6788430</v>
+        <v>6787750</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7406,50 +7406,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129124124</v>
+        <v>129124149</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>421440</v>
+        <v>421376</v>
       </c>
       <c r="R64" t="n">
-        <v>6788409</v>
+        <v>6788380</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7481,7 +7476,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7491,7 +7486,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7518,45 +7513,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129124131</v>
+        <v>129124124</v>
       </c>
       <c r="B65" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>421659</v>
+        <v>421440</v>
       </c>
       <c r="R65" t="n">
-        <v>6787750</v>
+        <v>6788409</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7732,10 +7732,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129124187</v>
+        <v>129124058</v>
       </c>
       <c r="B67" t="n">
-        <v>78444</v>
+        <v>79660</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7743,21 +7743,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>421639</v>
+        <v>421246</v>
       </c>
       <c r="R67" t="n">
-        <v>6788393</v>
+        <v>6788416</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7839,50 +7839,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129124115</v>
+        <v>129124059</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>421608</v>
+        <v>421354</v>
       </c>
       <c r="R68" t="n">
-        <v>6788661</v>
+        <v>6788463</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7914,7 +7909,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7924,7 +7919,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7951,50 +7946,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129124114</v>
+        <v>129124051</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>421399</v>
+        <v>421392</v>
       </c>
       <c r="R69" t="n">
-        <v>6788567</v>
+        <v>6788226</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8026,7 +8016,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8036,7 +8026,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8063,10 +8053,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129124058</v>
+        <v>129124187</v>
       </c>
       <c r="B70" t="n">
-        <v>79660</v>
+        <v>78444</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8074,21 +8064,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8098,10 +8088,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>421246</v>
+        <v>421639</v>
       </c>
       <c r="R70" t="n">
-        <v>6788416</v>
+        <v>6788393</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8133,7 +8123,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8143,7 +8133,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8170,45 +8160,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124059</v>
+        <v>129124114</v>
       </c>
       <c r="B71" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>421354</v>
+        <v>421399</v>
       </c>
       <c r="R71" t="n">
-        <v>6788463</v>
+        <v>6788567</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8240,7 +8235,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8250,7 +8245,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8277,45 +8272,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124051</v>
+        <v>129124115</v>
       </c>
       <c r="B72" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>421392</v>
+        <v>421608</v>
       </c>
       <c r="R72" t="n">
-        <v>6788226</v>
+        <v>6788661</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8496,32 +8496,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129124145</v>
+        <v>129124146</v>
       </c>
       <c r="B74" t="n">
-        <v>78798</v>
+        <v>91713</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>421591</v>
+        <v>421654</v>
       </c>
       <c r="R74" t="n">
-        <v>6787819</v>
+        <v>6788448</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8603,10 +8603,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129124103</v>
+        <v>129124177</v>
       </c>
       <c r="B75" t="n">
-        <v>78799</v>
+        <v>78707</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8614,21 +8614,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>421618</v>
+        <v>421318</v>
       </c>
       <c r="R75" t="n">
-        <v>6787832</v>
+        <v>6788511</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8710,32 +8710,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124146</v>
+        <v>129124145</v>
       </c>
       <c r="B76" t="n">
-        <v>91713</v>
+        <v>78798</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421654</v>
+        <v>421591</v>
       </c>
       <c r="R76" t="n">
-        <v>6788448</v>
+        <v>6787819</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8817,10 +8817,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124177</v>
+        <v>129124152</v>
       </c>
       <c r="B77" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421318</v>
+        <v>421234</v>
       </c>
       <c r="R77" t="n">
-        <v>6788511</v>
+        <v>6788411</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8924,10 +8924,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129124152</v>
+        <v>129124103</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8935,21 +8935,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>421234</v>
+        <v>421618</v>
       </c>
       <c r="R78" t="n">
-        <v>6788411</v>
+        <v>6787832</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9031,10 +9031,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129124143</v>
+        <v>129124090</v>
       </c>
       <c r="B79" t="n">
-        <v>78798</v>
+        <v>91561</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9042,21 +9042,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>421596</v>
+        <v>421576</v>
       </c>
       <c r="R79" t="n">
-        <v>6787835</v>
+        <v>6788373</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9111,7 +9111,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ej märkt med hänsyn</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9138,10 +9143,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129124090</v>
+        <v>129124143</v>
       </c>
       <c r="B80" t="n">
-        <v>91561</v>
+        <v>78798</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9149,21 +9154,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9173,10 +9178,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>421576</v>
+        <v>421596</v>
       </c>
       <c r="R80" t="n">
-        <v>6788373</v>
+        <v>6787835</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9208,7 +9213,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9218,12 +9223,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ej märkt med hänsyn</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9250,7 +9250,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129124168</v>
+        <v>129124167</v>
       </c>
       <c r="B81" t="n">
         <v>79041</v>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>421329</v>
+        <v>421342</v>
       </c>
       <c r="R81" t="n">
-        <v>6788222</v>
+        <v>6788261</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9357,7 +9357,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129124157</v>
+        <v>129124148</v>
       </c>
       <c r="B82" t="n">
         <v>79041</v>
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>421271</v>
+        <v>421395</v>
       </c>
       <c r="R82" t="n">
-        <v>6788641</v>
+        <v>6788374</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9464,7 +9464,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129124167</v>
+        <v>129124168</v>
       </c>
       <c r="B83" t="n">
         <v>79041</v>
@@ -9499,10 +9499,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>421342</v>
+        <v>421329</v>
       </c>
       <c r="R83" t="n">
-        <v>6788261</v>
+        <v>6788222</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9571,7 +9571,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129124148</v>
+        <v>129124157</v>
       </c>
       <c r="B84" t="n">
         <v>79041</v>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>421395</v>
+        <v>421271</v>
       </c>
       <c r="R84" t="n">
-        <v>6788374</v>
+        <v>6788641</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9999,50 +9999,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129124123</v>
+        <v>129124150</v>
       </c>
       <c r="B88" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>421446</v>
+        <v>421349</v>
       </c>
       <c r="R88" t="n">
-        <v>6788421</v>
+        <v>6788397</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10074,7 +10069,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10084,7 +10079,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10111,45 +10106,50 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129124150</v>
+        <v>129124123</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>421349</v>
+        <v>421446</v>
       </c>
       <c r="R89" t="n">
-        <v>6788397</v>
+        <v>6788421</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10432,10 +10432,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129124096</v>
+        <v>129124102</v>
       </c>
       <c r="B92" t="n">
-        <v>57724</v>
+        <v>83002</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10443,39 +10443,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>310</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>421596</v>
+        <v>421694</v>
       </c>
       <c r="R92" t="n">
-        <v>6787836</v>
+        <v>6787682</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10507,7 +10502,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10517,7 +10512,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10544,10 +10539,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129124102</v>
+        <v>129124096</v>
       </c>
       <c r="B93" t="n">
-        <v>83002</v>
+        <v>57724</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10555,34 +10550,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>310</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>421694</v>
+        <v>421596</v>
       </c>
       <c r="R93" t="n">
-        <v>6787682</v>
+        <v>6787836</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11079,45 +11079,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129124153</v>
+        <v>129124125</v>
       </c>
       <c r="B98" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>421305</v>
+        <v>421369</v>
       </c>
       <c r="R98" t="n">
-        <v>6788474</v>
+        <v>6788395</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11149,7 +11154,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11159,7 +11164,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11186,50 +11191,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129124125</v>
+        <v>129124153</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>421369</v>
+        <v>421305</v>
       </c>
       <c r="R99" t="n">
-        <v>6788395</v>
+        <v>6788474</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11261,7 +11261,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11298,42 +11298,38 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129124104</v>
+        <v>129124110</v>
       </c>
       <c r="B100" t="n">
-        <v>92860</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11342,10 +11338,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>421407</v>
+        <v>421271</v>
       </c>
       <c r="R100" t="n">
-        <v>6788349</v>
+        <v>6788430</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11377,7 +11373,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11387,7 +11383,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11414,10 +11410,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129124154</v>
+        <v>129124104</v>
       </c>
       <c r="B101" t="n">
-        <v>79041</v>
+        <v>92860</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11425,34 +11421,43 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>421303</v>
+        <v>421407</v>
       </c>
       <c r="R101" t="n">
-        <v>6788456</v>
+        <v>6788349</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11484,7 +11489,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11494,7 +11499,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11521,7 +11526,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129124147</v>
+        <v>129124154</v>
       </c>
       <c r="B102" t="n">
         <v>79041</v>
@@ -11556,10 +11561,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>421437</v>
+        <v>421303</v>
       </c>
       <c r="R102" t="n">
-        <v>6788275</v>
+        <v>6788456</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11591,7 +11596,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11601,7 +11606,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11628,50 +11633,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129124110</v>
+        <v>129124147</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>421271</v>
+        <v>421437</v>
       </c>
       <c r="R103" t="n">
-        <v>6788430</v>
+        <v>6788275</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11740,10 +11740,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129124141</v>
+        <v>129124071</v>
       </c>
       <c r="B104" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11751,21 +11751,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11775,10 +11775,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>421616</v>
+        <v>421598</v>
       </c>
       <c r="R104" t="n">
-        <v>6787883</v>
+        <v>6787863</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11847,10 +11847,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129124071</v>
+        <v>129124141</v>
       </c>
       <c r="B105" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11858,21 +11858,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>421598</v>
+        <v>421616</v>
       </c>
       <c r="R105" t="n">
-        <v>6787863</v>
+        <v>6787883</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11954,45 +11954,50 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124165</v>
+        <v>129124127</v>
       </c>
       <c r="B106" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421340</v>
+        <v>421630</v>
       </c>
       <c r="R106" t="n">
-        <v>6788389</v>
+        <v>6787815</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12024,7 +12029,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12034,7 +12039,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12061,50 +12066,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129124127</v>
+        <v>129124081</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>421630</v>
+        <v>421592</v>
       </c>
       <c r="R107" t="n">
-        <v>6787815</v>
+        <v>6787842</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12173,10 +12173,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129124081</v>
+        <v>129124165</v>
       </c>
       <c r="B108" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12184,21 +12184,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12208,10 +12208,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>421592</v>
+        <v>421340</v>
       </c>
       <c r="R108" t="n">
-        <v>6787842</v>
+        <v>6788389</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12280,45 +12280,50 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129124139</v>
+        <v>129124117</v>
       </c>
       <c r="B109" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>421354</v>
+        <v>421611</v>
       </c>
       <c r="R109" t="n">
-        <v>6788463</v>
+        <v>6788482</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12350,7 +12355,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12360,7 +12365,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12387,45 +12392,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129124053</v>
+        <v>129124116</v>
       </c>
       <c r="B110" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>421421</v>
+        <v>421615</v>
       </c>
       <c r="R110" t="n">
-        <v>6788216</v>
+        <v>6788580</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12457,7 +12467,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12467,7 +12477,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12494,45 +12504,50 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129124063</v>
+        <v>129124111</v>
       </c>
       <c r="B111" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>421442</v>
+        <v>421315</v>
       </c>
       <c r="R111" t="n">
-        <v>6788613</v>
+        <v>6788532</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12564,7 +12579,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12574,7 +12589,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12601,7 +12616,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124052</v>
+        <v>129124053</v>
       </c>
       <c r="B112" t="n">
         <v>79660</v>
@@ -12636,10 +12651,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421391</v>
+        <v>421421</v>
       </c>
       <c r="R112" t="n">
-        <v>6788209</v>
+        <v>6788216</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12671,7 +12686,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12681,7 +12696,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12708,10 +12723,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129124158</v>
+        <v>129124063</v>
       </c>
       <c r="B113" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12719,21 +12734,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12743,10 +12758,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421383</v>
+        <v>421442</v>
       </c>
       <c r="R113" t="n">
-        <v>6788546</v>
+        <v>6788613</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12778,7 +12793,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12788,7 +12803,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12815,10 +12830,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129124159</v>
+        <v>129124139</v>
       </c>
       <c r="B114" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12826,21 +12841,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12850,10 +12865,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>421612</v>
+        <v>421354</v>
       </c>
       <c r="R114" t="n">
-        <v>6788488</v>
+        <v>6788463</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12885,7 +12900,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12895,7 +12910,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12922,50 +12937,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129124111</v>
+        <v>129124052</v>
       </c>
       <c r="B115" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>421315</v>
+        <v>421391</v>
       </c>
       <c r="R115" t="n">
-        <v>6788532</v>
+        <v>6788209</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12997,7 +13007,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13007,7 +13017,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13034,50 +13044,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129124116</v>
+        <v>129124080</v>
       </c>
       <c r="B116" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>421615</v>
+        <v>421633</v>
       </c>
       <c r="R116" t="n">
-        <v>6788580</v>
+        <v>6787841</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13109,7 +13114,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13119,7 +13124,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13146,50 +13151,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129124117</v>
+        <v>129124158</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>421611</v>
+        <v>421383</v>
       </c>
       <c r="R117" t="n">
-        <v>6788482</v>
+        <v>6788546</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13221,7 +13221,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13258,10 +13258,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129124080</v>
+        <v>129124159</v>
       </c>
       <c r="B118" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13269,21 +13269,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>421633</v>
+        <v>421612</v>
       </c>
       <c r="R118" t="n">
-        <v>6787841</v>
+        <v>6788488</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13579,10 +13579,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129124105</v>
+        <v>129124164</v>
       </c>
       <c r="B121" t="n">
-        <v>92860</v>
+        <v>79041</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13590,43 +13590,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>421613</v>
+        <v>421345</v>
       </c>
       <c r="R121" t="n">
-        <v>6788634</v>
+        <v>6788394</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13658,7 +13649,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13668,7 +13659,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13695,10 +13686,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129124069</v>
+        <v>129124156</v>
       </c>
       <c r="B122" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13706,21 +13697,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13730,10 +13721,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>421626</v>
+        <v>421351</v>
       </c>
       <c r="R122" t="n">
-        <v>6787879</v>
+        <v>6788471</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13765,7 +13756,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13775,7 +13766,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13802,10 +13793,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129124054</v>
+        <v>129124105</v>
       </c>
       <c r="B123" t="n">
-        <v>79660</v>
+        <v>92860</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13813,34 +13804,43 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>421423</v>
+        <v>421613</v>
       </c>
       <c r="R123" t="n">
-        <v>6788261</v>
+        <v>6788634</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13872,7 +13872,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13909,10 +13909,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129124164</v>
+        <v>129124069</v>
       </c>
       <c r="B124" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13920,21 +13920,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13944,10 +13944,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>421345</v>
+        <v>421626</v>
       </c>
       <c r="R124" t="n">
-        <v>6788394</v>
+        <v>6787879</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14016,10 +14016,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129124156</v>
+        <v>129124054</v>
       </c>
       <c r="B125" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14027,21 +14027,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14051,10 +14051,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>421351</v>
+        <v>421423</v>
       </c>
       <c r="R125" t="n">
-        <v>6788471</v>
+        <v>6788261</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14086,7 +14086,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14123,50 +14123,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129124121</v>
+        <v>129124062</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>421524</v>
+        <v>421395</v>
       </c>
       <c r="R126" t="n">
-        <v>6788399</v>
+        <v>6788610</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14198,7 +14193,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14208,7 +14203,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14235,45 +14230,50 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129124062</v>
+        <v>129124121</v>
       </c>
       <c r="B127" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421395</v>
+        <v>421524</v>
       </c>
       <c r="R127" t="n">
-        <v>6788610</v>
+        <v>6788399</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14668,10 +14668,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129124155</v>
+        <v>129124178</v>
       </c>
       <c r="B131" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14679,21 +14679,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14703,10 +14703,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>421354</v>
+        <v>421235</v>
       </c>
       <c r="R131" t="n">
-        <v>6788463</v>
+        <v>6788559</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14775,7 +14775,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129124178</v>
+        <v>129124180</v>
       </c>
       <c r="B132" t="n">
         <v>78707</v>
@@ -14810,10 +14810,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>421235</v>
+        <v>421501</v>
       </c>
       <c r="R132" t="n">
-        <v>6788559</v>
+        <v>6788671</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14882,45 +14882,50 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129124180</v>
+        <v>129124112</v>
       </c>
       <c r="B133" t="n">
-        <v>78707</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>421501</v>
+        <v>421293</v>
       </c>
       <c r="R133" t="n">
-        <v>6788671</v>
+        <v>6788551</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14952,7 +14957,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14962,7 +14967,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14989,10 +14994,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129124073</v>
+        <v>129124155</v>
       </c>
       <c r="B134" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15000,21 +15005,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15024,10 +15029,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>421595</v>
+        <v>421354</v>
       </c>
       <c r="R134" t="n">
-        <v>6787823</v>
+        <v>6788463</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15059,7 +15064,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15069,7 +15074,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15096,50 +15101,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129124112</v>
+        <v>129124073</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>421293</v>
+        <v>421595</v>
       </c>
       <c r="R135" t="n">
-        <v>6788551</v>
+        <v>6787823</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15208,45 +15208,50 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129124057</v>
+        <v>129124088</v>
       </c>
       <c r="B136" t="n">
-        <v>79660</v>
+        <v>56917</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>421312</v>
+        <v>421296</v>
       </c>
       <c r="R136" t="n">
-        <v>6788393</v>
+        <v>6788608</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15278,7 +15283,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15288,7 +15293,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15315,50 +15320,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129124088</v>
+        <v>129124057</v>
       </c>
       <c r="B137" t="n">
-        <v>56917</v>
+        <v>79660</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>421296</v>
+        <v>421312</v>
       </c>
       <c r="R137" t="n">
-        <v>6788608</v>
+        <v>6788393</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15390,7 +15390,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15641,10 +15641,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129124140</v>
+        <v>129124169</v>
       </c>
       <c r="B140" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15652,21 +15652,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15676,10 +15676,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>421656</v>
+        <v>421618</v>
       </c>
       <c r="R140" t="n">
-        <v>6787791</v>
+        <v>6787872</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15748,10 +15748,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129124068</v>
+        <v>129124140</v>
       </c>
       <c r="B141" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15759,21 +15759,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15783,10 +15783,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>421675</v>
+        <v>421656</v>
       </c>
       <c r="R141" t="n">
-        <v>6787696</v>
+        <v>6787791</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15855,7 +15855,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129124065</v>
+        <v>129124068</v>
       </c>
       <c r="B142" t="n">
         <v>79660</v>
@@ -15890,10 +15890,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>421530</v>
+        <v>421675</v>
       </c>
       <c r="R142" t="n">
-        <v>6788679</v>
+        <v>6787696</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15925,7 +15925,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15962,10 +15962,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129124169</v>
+        <v>129124065</v>
       </c>
       <c r="B143" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15973,21 +15973,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15997,10 +15997,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>421618</v>
+        <v>421530</v>
       </c>
       <c r="R143" t="n">
-        <v>6787872</v>
+        <v>6788679</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16181,50 +16181,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124120</v>
+        <v>129124087</v>
       </c>
       <c r="B145" t="n">
-        <v>8450</v>
+        <v>79136</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>967</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421520</v>
+        <v>421601</v>
       </c>
       <c r="R145" t="n">
-        <v>6788366</v>
+        <v>6787830</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16256,7 +16251,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16266,7 +16261,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16293,50 +16288,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124106</v>
+        <v>129124144</v>
       </c>
       <c r="B146" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421574</v>
+        <v>421602</v>
       </c>
       <c r="R146" t="n">
-        <v>6788374</v>
+        <v>6787829</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16368,7 +16358,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16378,7 +16368,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16405,10 +16395,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129124133</v>
+        <v>129124138</v>
       </c>
       <c r="B147" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16416,21 +16406,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16440,10 +16430,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>421633</v>
+        <v>421292</v>
       </c>
       <c r="R147" t="n">
-        <v>6787841</v>
+        <v>6788456</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16475,7 +16465,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16485,7 +16475,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16512,45 +16502,50 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129124078</v>
+        <v>129124106</v>
       </c>
       <c r="B148" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421640</v>
+        <v>421574</v>
       </c>
       <c r="R148" t="n">
-        <v>6788394</v>
+        <v>6788374</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16582,7 +16577,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16592,7 +16587,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16731,45 +16726,50 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124087</v>
+        <v>129124120</v>
       </c>
       <c r="B150" t="n">
-        <v>79136</v>
+        <v>8450</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>967</v>
+        <v>106545</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421601</v>
+        <v>421520</v>
       </c>
       <c r="R150" t="n">
-        <v>6787830</v>
+        <v>6788366</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16801,7 +16801,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16838,10 +16838,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124144</v>
+        <v>129124133</v>
       </c>
       <c r="B151" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16849,21 +16849,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16873,10 +16873,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421602</v>
+        <v>421633</v>
       </c>
       <c r="R151" t="n">
-        <v>6787829</v>
+        <v>6787841</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16945,10 +16945,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129124138</v>
+        <v>129124078</v>
       </c>
       <c r="B152" t="n">
-        <v>78798</v>
+        <v>79631</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16956,21 +16956,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16980,10 +16980,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>421292</v>
+        <v>421640</v>
       </c>
       <c r="R152" t="n">
-        <v>6788456</v>
+        <v>6788394</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17159,10 +17159,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129124064</v>
+        <v>129124186</v>
       </c>
       <c r="B154" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17170,21 +17170,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17194,10 +17194,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>421501</v>
+        <v>421626</v>
       </c>
       <c r="R154" t="n">
-        <v>6788671</v>
+        <v>6787877</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17266,50 +17266,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129124119</v>
+        <v>129124064</v>
       </c>
       <c r="B155" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>421653</v>
+        <v>421501</v>
       </c>
       <c r="R155" t="n">
-        <v>6788387</v>
+        <v>6788671</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17341,7 +17336,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17351,7 +17346,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17378,10 +17373,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129124186</v>
+        <v>129124137</v>
       </c>
       <c r="B156" t="n">
-        <v>78707</v>
+        <v>78798</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17389,21 +17384,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17413,10 +17408,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>421626</v>
+        <v>421312</v>
       </c>
       <c r="R156" t="n">
-        <v>6787877</v>
+        <v>6788393</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17448,7 +17443,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17458,7 +17453,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17485,45 +17480,50 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129124137</v>
+        <v>129124119</v>
       </c>
       <c r="B157" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>421312</v>
+        <v>421653</v>
       </c>
       <c r="R157" t="n">
-        <v>6788393</v>
+        <v>6788387</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17555,7 +17555,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17565,7 +17565,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD157" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129124066</v>
+        <v>129124162</v>
       </c>
       <c r="B2" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421685</v>
+        <v>421720</v>
       </c>
       <c r="R2" t="n">
-        <v>6788462</v>
+        <v>6788450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129124162</v>
+        <v>129124066</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421720</v>
+        <v>421685</v>
       </c>
       <c r="R3" t="n">
-        <v>6788450</v>
+        <v>6788462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>129124171</v>
       </c>
       <c r="B4" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129124185</v>
       </c>
       <c r="B5" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129124184</v>
       </c>
       <c r="B6" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>129124067</v>
       </c>
       <c r="B8" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>129124183</v>
       </c>
       <c r="B9" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>129124161</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129093027</v>
       </c>
       <c r="B15" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129093983</v>
+        <v>129094012</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421400</v>
+        <v>421379</v>
       </c>
       <c r="R16" t="n">
-        <v>6788524</v>
+        <v>6788540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129095317</v>
+        <v>129093983</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421398</v>
+        <v>421400</v>
       </c>
       <c r="R17" t="n">
-        <v>6788372</v>
+        <v>6788524</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,10 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129094012</v>
+        <v>129095317</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421379</v>
+        <v>421398</v>
       </c>
       <c r="R18" t="n">
-        <v>6788540</v>
+        <v>6788372</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
         <v>129093952</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>129093598</v>
       </c>
       <c r="B20" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129093202</v>
+        <v>129093188</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>129093043</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>129094076</v>
       </c>
       <c r="B24" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129093167</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>129093766</v>
       </c>
       <c r="B26" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>129094170</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3534,32 +3534,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129094249</v>
+        <v>129094800</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421564</v>
+        <v>421501</v>
       </c>
       <c r="R28" t="n">
-        <v>6788544</v>
+        <v>6788477</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,32 +3641,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129094800</v>
+        <v>129094249</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421501</v>
+        <v>421564</v>
       </c>
       <c r="R29" t="n">
-        <v>6788477</v>
+        <v>6788544</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3751,7 +3751,7 @@
         <v>129093086</v>
       </c>
       <c r="B30" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129094179</v>
+        <v>129093018</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421509</v>
+        <v>421341</v>
       </c>
       <c r="R31" t="n">
-        <v>6788597</v>
+        <v>6788261</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3962,10 +3962,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129093018</v>
+        <v>129094179</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>421341</v>
+        <v>421509</v>
       </c>
       <c r="R32" t="n">
-        <v>6788261</v>
+        <v>6788597</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4179,7 +4179,7 @@
         <v>129094072</v>
       </c>
       <c r="B34" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>129095256</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>129094091</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>129096050</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>129095002</v>
       </c>
       <c r="B38" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>129093008</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>129094542</v>
       </c>
       <c r="B40" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4925,50 +4925,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129094242</v>
+        <v>129093117</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>421564</v>
+        <v>421391</v>
       </c>
       <c r="R41" t="n">
-        <v>6788544</v>
+        <v>6788314</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5037,10 +5032,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129095090</v>
+        <v>129093226</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5048,39 +5043,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>421500</v>
+        <v>421395</v>
       </c>
       <c r="R42" t="n">
-        <v>6788425</v>
+        <v>6788438</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5149,10 +5139,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129094162</v>
+        <v>129095090</v>
       </c>
       <c r="B43" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5160,16 +5150,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5180,7 +5170,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5189,10 +5179,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>421499</v>
+        <v>421500</v>
       </c>
       <c r="R43" t="n">
-        <v>6788592</v>
+        <v>6788425</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,45 +5251,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129093117</v>
+        <v>129094242</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>421391</v>
+        <v>421564</v>
       </c>
       <c r="R44" t="n">
-        <v>6788314</v>
+        <v>6788544</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5368,10 +5363,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129093226</v>
+        <v>129094162</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5379,34 +5374,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>421395</v>
+        <v>421499</v>
       </c>
       <c r="R45" t="n">
-        <v>6788438</v>
+        <v>6788592</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
         <v>129094551</v>
       </c>
       <c r="B46" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>129093174</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>129093173</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>129095392</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5903,50 +5903,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129095582</v>
+        <v>129094943</v>
       </c>
       <c r="B50" t="n">
-        <v>58097</v>
+        <v>79633</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>421342</v>
+        <v>421534</v>
       </c>
       <c r="R50" t="n">
-        <v>6788310</v>
+        <v>6788452</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6018,7 +6013,7 @@
         <v>129094103</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6122,45 +6117,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129094943</v>
+        <v>129095582</v>
       </c>
       <c r="B52" t="n">
-        <v>79631</v>
+        <v>58097</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>421534</v>
+        <v>421342</v>
       </c>
       <c r="R52" t="n">
-        <v>6788452</v>
+        <v>6788310</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6229,10 +6229,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129124160</v>
+        <v>129124182</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>78709</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6240,21 +6240,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>421611</v>
+        <v>421622</v>
       </c>
       <c r="R53" t="n">
-        <v>6788481</v>
+        <v>6788520</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6336,10 +6336,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129124070</v>
+        <v>129124179</v>
       </c>
       <c r="B54" t="n">
-        <v>79660</v>
+        <v>78709</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>421616</v>
+        <v>421487</v>
       </c>
       <c r="R54" t="n">
-        <v>6787882</v>
+        <v>6788638</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6443,10 +6443,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129124130</v>
+        <v>129124176</v>
       </c>
       <c r="B55" t="n">
-        <v>78799</v>
+        <v>78709</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6454,21 +6454,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>421354</v>
+        <v>421338</v>
       </c>
       <c r="R55" t="n">
-        <v>6788463</v>
+        <v>6788476</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124166</v>
+        <v>129124160</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421316</v>
+        <v>421611</v>
       </c>
       <c r="R56" t="n">
-        <v>6788317</v>
+        <v>6788481</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6657,10 +6657,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129124182</v>
+        <v>129124166</v>
       </c>
       <c r="B57" t="n">
-        <v>78707</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,21 +6668,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>421622</v>
+        <v>421316</v>
       </c>
       <c r="R57" t="n">
-        <v>6788520</v>
+        <v>6788317</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6764,10 +6764,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129124179</v>
+        <v>129124130</v>
       </c>
       <c r="B58" t="n">
-        <v>78707</v>
+        <v>78801</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6775,21 +6775,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>421487</v>
+        <v>421354</v>
       </c>
       <c r="R58" t="n">
-        <v>6788638</v>
+        <v>6788463</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129124176</v>
+        <v>129124070</v>
       </c>
       <c r="B59" t="n">
-        <v>78707</v>
+        <v>79662</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,21 +6882,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>421338</v>
+        <v>421616</v>
       </c>
       <c r="R59" t="n">
-        <v>6788476</v>
+        <v>6787882</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6978,10 +6978,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129124061</v>
+        <v>129124149</v>
       </c>
       <c r="B60" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,21 +6989,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>421238</v>
+        <v>421376</v>
       </c>
       <c r="R60" t="n">
-        <v>6788555</v>
+        <v>6788380</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7085,10 +7085,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129124142</v>
+        <v>129124151</v>
       </c>
       <c r="B61" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7096,21 +7096,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>421594</v>
+        <v>421275</v>
       </c>
       <c r="R61" t="n">
-        <v>6787870</v>
+        <v>6788430</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7192,10 +7192,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129124151</v>
+        <v>129124061</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7203,21 +7203,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>421275</v>
+        <v>421238</v>
       </c>
       <c r="R62" t="n">
-        <v>6788430</v>
+        <v>6788555</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7299,10 +7299,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129124131</v>
+        <v>129124142</v>
       </c>
       <c r="B63" t="n">
-        <v>78799</v>
+        <v>78800</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7310,21 +7310,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>421659</v>
+        <v>421594</v>
       </c>
       <c r="R63" t="n">
-        <v>6787750</v>
+        <v>6787870</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7406,45 +7406,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129124149</v>
+        <v>129124124</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>421376</v>
+        <v>421440</v>
       </c>
       <c r="R64" t="n">
-        <v>6788380</v>
+        <v>6788409</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7476,7 +7481,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7486,7 +7491,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7513,50 +7518,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129124124</v>
+        <v>129124131</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>78801</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>421440</v>
+        <v>421659</v>
       </c>
       <c r="R65" t="n">
-        <v>6788409</v>
+        <v>6787750</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7625,32 +7625,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129124173</v>
+        <v>129124187</v>
       </c>
       <c r="B66" t="n">
-        <v>92822</v>
+        <v>78446</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>421621</v>
+        <v>421639</v>
       </c>
       <c r="R66" t="n">
-        <v>6787838</v>
+        <v>6788393</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7735,7 +7735,7 @@
         <v>129124058</v>
       </c>
       <c r="B67" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>129124059</v>
       </c>
       <c r="B68" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>129124051</v>
       </c>
       <c r="B69" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8053,45 +8053,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129124187</v>
+        <v>129124114</v>
       </c>
       <c r="B70" t="n">
-        <v>78444</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6437</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>421639</v>
+        <v>421399</v>
       </c>
       <c r="R70" t="n">
-        <v>6788393</v>
+        <v>6788567</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8123,7 +8128,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8133,7 +8138,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8160,7 +8165,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124114</v>
+        <v>129124115</v>
       </c>
       <c r="B71" t="n">
         <v>8450</v>
@@ -8200,10 +8205,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>421399</v>
+        <v>421608</v>
       </c>
       <c r="R71" t="n">
-        <v>6788567</v>
+        <v>6788661</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8235,7 +8240,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8245,7 +8250,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8272,50 +8277,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124115</v>
+        <v>129124074</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>79633</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>421608</v>
+        <v>421236</v>
       </c>
       <c r="R72" t="n">
-        <v>6788661</v>
+        <v>6788559</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8357,7 +8357,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På stubbe med 6 brandljud</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8384,32 +8389,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129124074</v>
+        <v>129124173</v>
       </c>
       <c r="B73" t="n">
-        <v>79631</v>
+        <v>92825</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8419,10 +8424,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>421236</v>
+        <v>421621</v>
       </c>
       <c r="R73" t="n">
-        <v>6788559</v>
+        <v>6787838</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8454,7 +8459,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8464,12 +8469,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På stubbe med 6 brandljud</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8499,7 +8499,7 @@
         <v>129124146</v>
       </c>
       <c r="B74" t="n">
-        <v>91713</v>
+        <v>91716</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>129124177</v>
       </c>
       <c r="B75" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8710,10 +8710,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124145</v>
+        <v>129124152</v>
       </c>
       <c r="B76" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8721,21 +8721,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421591</v>
+        <v>421234</v>
       </c>
       <c r="R76" t="n">
-        <v>6787819</v>
+        <v>6788411</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8817,10 +8817,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124152</v>
+        <v>129124145</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421234</v>
+        <v>421591</v>
       </c>
       <c r="R77" t="n">
-        <v>6788411</v>
+        <v>6787819</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8927,7 +8927,7 @@
         <v>129124103</v>
       </c>
       <c r="B78" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>129124090</v>
       </c>
       <c r="B79" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>129124143</v>
       </c>
       <c r="B80" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129124167</v>
+        <v>129124134</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>78801</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9261,21 +9261,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>421342</v>
+        <v>421616</v>
       </c>
       <c r="R81" t="n">
-        <v>6788261</v>
+        <v>6787882</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9357,10 +9357,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129124148</v>
+        <v>129124129</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>78801</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9368,21 +9368,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>421395</v>
+        <v>421292</v>
       </c>
       <c r="R82" t="n">
-        <v>6788374</v>
+        <v>6788456</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9464,10 +9464,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129124168</v>
+        <v>129124083</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>79633</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9475,21 +9475,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9499,10 +9499,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>421329</v>
+        <v>421598</v>
       </c>
       <c r="R83" t="n">
-        <v>6788222</v>
+        <v>6787829</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9571,10 +9571,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129124157</v>
+        <v>129124168</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>421271</v>
+        <v>421329</v>
       </c>
       <c r="R84" t="n">
-        <v>6788641</v>
+        <v>6788222</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9678,10 +9678,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129124134</v>
+        <v>129124157</v>
       </c>
       <c r="B85" t="n">
-        <v>78799</v>
+        <v>79043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9689,21 +9689,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9713,10 +9713,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>421616</v>
+        <v>421271</v>
       </c>
       <c r="R85" t="n">
-        <v>6787882</v>
+        <v>6788641</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9785,10 +9785,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129124129</v>
+        <v>129124167</v>
       </c>
       <c r="B86" t="n">
-        <v>78799</v>
+        <v>79043</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>421292</v>
+        <v>421342</v>
       </c>
       <c r="R86" t="n">
-        <v>6788456</v>
+        <v>6788261</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9892,10 +9892,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129124083</v>
+        <v>129124148</v>
       </c>
       <c r="B87" t="n">
-        <v>79631</v>
+        <v>79043</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9903,21 +9903,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>421598</v>
+        <v>421395</v>
       </c>
       <c r="R87" t="n">
-        <v>6787829</v>
+        <v>6788374</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10002,7 +10002,7 @@
         <v>129124150</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>129124132</v>
       </c>
       <c r="B90" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>129124136</v>
       </c>
       <c r="B91" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10432,10 +10432,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129124102</v>
+        <v>129124096</v>
       </c>
       <c r="B92" t="n">
-        <v>83002</v>
+        <v>57724</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10443,34 +10443,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>310</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>421694</v>
+        <v>421596</v>
       </c>
       <c r="R92" t="n">
-        <v>6787682</v>
+        <v>6787836</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10502,7 +10507,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10512,7 +10517,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10539,10 +10544,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129124096</v>
+        <v>129124102</v>
       </c>
       <c r="B93" t="n">
-        <v>57724</v>
+        <v>83006</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10550,39 +10555,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>310</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>421596</v>
+        <v>421694</v>
       </c>
       <c r="R93" t="n">
-        <v>6787836</v>
+        <v>6787682</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10654,7 +10654,7 @@
         <v>129124135</v>
       </c>
       <c r="B94" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>129124128</v>
       </c>
       <c r="B95" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10865,10 +10865,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129124060</v>
+        <v>129124153</v>
       </c>
       <c r="B96" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10876,21 +10876,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10900,10 +10900,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>421338</v>
+        <v>421305</v>
       </c>
       <c r="R96" t="n">
-        <v>6788476</v>
+        <v>6788474</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10972,10 +10972,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129124072</v>
+        <v>129124060</v>
       </c>
       <c r="B97" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>421591</v>
+        <v>421338</v>
       </c>
       <c r="R97" t="n">
-        <v>6787819</v>
+        <v>6788476</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11079,50 +11079,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129124125</v>
+        <v>129124072</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>79662</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>421369</v>
+        <v>421591</v>
       </c>
       <c r="R98" t="n">
-        <v>6788395</v>
+        <v>6787819</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11154,7 +11149,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11164,7 +11159,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11191,45 +11186,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129124153</v>
+        <v>129124125</v>
       </c>
       <c r="B99" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>421305</v>
+        <v>421369</v>
       </c>
       <c r="R99" t="n">
-        <v>6788474</v>
+        <v>6788395</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11261,7 +11261,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11413,7 +11413,7 @@
         <v>129124104</v>
       </c>
       <c r="B101" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>129124154</v>
       </c>
       <c r="B102" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>129124147</v>
       </c>
       <c r="B103" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11740,45 +11740,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129124071</v>
+        <v>129124127</v>
       </c>
       <c r="B104" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>421598</v>
+        <v>421630</v>
       </c>
       <c r="R104" t="n">
-        <v>6787863</v>
+        <v>6787815</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11810,7 +11815,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11820,7 +11825,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11847,10 +11852,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129124141</v>
+        <v>129124081</v>
       </c>
       <c r="B105" t="n">
-        <v>78798</v>
+        <v>79633</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11858,21 +11863,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11882,10 +11887,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>421616</v>
+        <v>421592</v>
       </c>
       <c r="R105" t="n">
-        <v>6787883</v>
+        <v>6787842</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11917,7 +11922,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11927,7 +11932,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11954,50 +11959,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124127</v>
+        <v>129124165</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421630</v>
+        <v>421340</v>
       </c>
       <c r="R106" t="n">
-        <v>6787815</v>
+        <v>6788389</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12066,10 +12066,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129124081</v>
+        <v>129124071</v>
       </c>
       <c r="B107" t="n">
-        <v>79631</v>
+        <v>79662</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12077,21 +12077,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12101,10 +12101,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>421592</v>
+        <v>421598</v>
       </c>
       <c r="R107" t="n">
-        <v>6787842</v>
+        <v>6787863</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12173,10 +12173,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129124165</v>
+        <v>129124141</v>
       </c>
       <c r="B108" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12184,21 +12184,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12208,10 +12208,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>421340</v>
+        <v>421616</v>
       </c>
       <c r="R108" t="n">
-        <v>6788389</v>
+        <v>6787883</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12280,50 +12280,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129124117</v>
+        <v>129124181</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>78709</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>421611</v>
+        <v>421537</v>
       </c>
       <c r="R109" t="n">
-        <v>6788482</v>
+        <v>6788706</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12355,7 +12350,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12365,7 +12360,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12392,50 +12387,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129124116</v>
+        <v>129124175</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>78709</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>421615</v>
+        <v>421343</v>
       </c>
       <c r="R110" t="n">
-        <v>6788580</v>
+        <v>6788400</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12467,7 +12457,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12477,7 +12467,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12504,50 +12494,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129124111</v>
+        <v>129124158</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>421315</v>
+        <v>421383</v>
       </c>
       <c r="R111" t="n">
-        <v>6788532</v>
+        <v>6788546</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12579,7 +12564,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12589,7 +12574,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12616,10 +12601,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124053</v>
+        <v>129124159</v>
       </c>
       <c r="B112" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12627,21 +12612,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12651,10 +12636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421421</v>
+        <v>421612</v>
       </c>
       <c r="R112" t="n">
-        <v>6788216</v>
+        <v>6788488</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12686,7 +12671,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12696,7 +12681,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12723,10 +12708,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129124063</v>
+        <v>129124080</v>
       </c>
       <c r="B113" t="n">
-        <v>79660</v>
+        <v>79633</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12734,21 +12719,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12758,10 +12743,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421442</v>
+        <v>421633</v>
       </c>
       <c r="R113" t="n">
-        <v>6788613</v>
+        <v>6787841</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12793,7 +12778,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12803,7 +12788,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12830,10 +12815,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129124139</v>
+        <v>129124053</v>
       </c>
       <c r="B114" t="n">
-        <v>78798</v>
+        <v>79662</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12841,21 +12826,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12865,10 +12850,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>421354</v>
+        <v>421421</v>
       </c>
       <c r="R114" t="n">
-        <v>6788463</v>
+        <v>6788216</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12900,7 +12885,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12910,7 +12895,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12937,10 +12922,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129124052</v>
+        <v>129124063</v>
       </c>
       <c r="B115" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12972,10 +12957,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>421391</v>
+        <v>421442</v>
       </c>
       <c r="R115" t="n">
-        <v>6788209</v>
+        <v>6788613</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13007,7 +12992,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13017,7 +13002,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13044,10 +13029,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129124080</v>
+        <v>129124139</v>
       </c>
       <c r="B116" t="n">
-        <v>79631</v>
+        <v>78800</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13055,21 +13040,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13079,10 +13064,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>421633</v>
+        <v>421354</v>
       </c>
       <c r="R116" t="n">
-        <v>6787841</v>
+        <v>6788463</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13114,7 +13099,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13124,7 +13109,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13151,10 +13136,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129124158</v>
+        <v>129124052</v>
       </c>
       <c r="B117" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13162,21 +13147,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13186,10 +13171,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>421383</v>
+        <v>421391</v>
       </c>
       <c r="R117" t="n">
-        <v>6788546</v>
+        <v>6788209</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13221,7 +13206,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13231,7 +13216,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13258,45 +13243,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129124159</v>
+        <v>129124117</v>
       </c>
       <c r="B118" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>421612</v>
+        <v>421611</v>
       </c>
       <c r="R118" t="n">
-        <v>6788488</v>
+        <v>6788482</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13365,45 +13355,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129124181</v>
+        <v>129124116</v>
       </c>
       <c r="B119" t="n">
-        <v>78707</v>
+        <v>8450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>421537</v>
+        <v>421615</v>
       </c>
       <c r="R119" t="n">
-        <v>6788706</v>
+        <v>6788580</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13435,7 +13430,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13445,7 +13440,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13472,45 +13467,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129124175</v>
+        <v>129124111</v>
       </c>
       <c r="B120" t="n">
-        <v>78707</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>421343</v>
+        <v>421315</v>
       </c>
       <c r="R120" t="n">
-        <v>6788400</v>
+        <v>6788532</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13579,10 +13579,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129124164</v>
+        <v>129124105</v>
       </c>
       <c r="B121" t="n">
-        <v>79041</v>
+        <v>92863</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13590,34 +13590,43 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>421345</v>
+        <v>421613</v>
       </c>
       <c r="R121" t="n">
-        <v>6788394</v>
+        <v>6788634</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13649,7 +13658,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13659,7 +13668,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13686,10 +13695,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129124156</v>
+        <v>129124069</v>
       </c>
       <c r="B122" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13697,21 +13706,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13721,10 +13730,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>421351</v>
+        <v>421626</v>
       </c>
       <c r="R122" t="n">
-        <v>6788471</v>
+        <v>6787879</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13756,7 +13765,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13766,7 +13775,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13793,10 +13802,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129124105</v>
+        <v>129124054</v>
       </c>
       <c r="B123" t="n">
-        <v>92860</v>
+        <v>79662</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13804,43 +13813,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>421613</v>
+        <v>421423</v>
       </c>
       <c r="R123" t="n">
-        <v>6788634</v>
+        <v>6788261</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13872,7 +13872,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13909,10 +13909,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129124069</v>
+        <v>129124062</v>
       </c>
       <c r="B124" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13944,10 +13944,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>421626</v>
+        <v>421395</v>
       </c>
       <c r="R124" t="n">
-        <v>6787879</v>
+        <v>6788610</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14016,10 +14016,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129124054</v>
+        <v>129124082</v>
       </c>
       <c r="B125" t="n">
-        <v>79660</v>
+        <v>79633</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14027,21 +14027,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14051,10 +14051,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>421423</v>
+        <v>421601</v>
       </c>
       <c r="R125" t="n">
-        <v>6788261</v>
+        <v>6787830</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14086,7 +14086,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14123,10 +14123,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129124062</v>
+        <v>129124164</v>
       </c>
       <c r="B126" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14134,21 +14134,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14158,10 +14158,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>421395</v>
+        <v>421345</v>
       </c>
       <c r="R126" t="n">
-        <v>6788610</v>
+        <v>6788394</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14193,7 +14193,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14203,7 +14203,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14230,50 +14230,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129124121</v>
+        <v>129124156</v>
       </c>
       <c r="B127" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421524</v>
+        <v>421351</v>
       </c>
       <c r="R127" t="n">
-        <v>6788399</v>
+        <v>6788471</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14305,7 +14300,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14315,7 +14310,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14342,45 +14337,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129124082</v>
+        <v>129124121</v>
       </c>
       <c r="B128" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>421601</v>
+        <v>421524</v>
       </c>
       <c r="R128" t="n">
-        <v>6787830</v>
+        <v>6788399</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14449,50 +14449,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129124108</v>
+        <v>129124056</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79662</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>421362</v>
+        <v>421343</v>
       </c>
       <c r="R129" t="n">
-        <v>6788387</v>
+        <v>6788400</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14524,7 +14519,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14534,7 +14529,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14561,45 +14556,50 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129124056</v>
+        <v>129124108</v>
       </c>
       <c r="B130" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>421343</v>
+        <v>421362</v>
       </c>
       <c r="R130" t="n">
-        <v>6788400</v>
+        <v>6788387</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14671,7 +14671,7 @@
         <v>129124178</v>
       </c>
       <c r="B131" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>129124180</v>
       </c>
       <c r="B132" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14882,50 +14882,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129124112</v>
+        <v>129124155</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>421293</v>
+        <v>421354</v>
       </c>
       <c r="R133" t="n">
-        <v>6788551</v>
+        <v>6788463</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14957,7 +14952,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14967,7 +14962,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14994,10 +14989,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129124155</v>
+        <v>129124073</v>
       </c>
       <c r="B134" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15005,21 +15000,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15029,10 +15024,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>421354</v>
+        <v>421595</v>
       </c>
       <c r="R134" t="n">
-        <v>6788463</v>
+        <v>6787823</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15064,7 +15059,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15074,7 +15069,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15101,45 +15096,50 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129124073</v>
+        <v>129124112</v>
       </c>
       <c r="B135" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>421595</v>
+        <v>421293</v>
       </c>
       <c r="R135" t="n">
-        <v>6787823</v>
+        <v>6788551</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15208,50 +15208,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129124088</v>
+        <v>129124057</v>
       </c>
       <c r="B136" t="n">
-        <v>56917</v>
+        <v>79662</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>421296</v>
+        <v>421312</v>
       </c>
       <c r="R136" t="n">
-        <v>6788608</v>
+        <v>6788393</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15283,7 +15278,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15293,7 +15288,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15320,45 +15315,50 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129124057</v>
+        <v>129124088</v>
       </c>
       <c r="B137" t="n">
-        <v>79660</v>
+        <v>56917</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>421312</v>
+        <v>421296</v>
       </c>
       <c r="R137" t="n">
-        <v>6788393</v>
+        <v>6788608</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15390,7 +15390,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15427,10 +15427,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129124163</v>
+        <v>129124077</v>
       </c>
       <c r="B138" t="n">
-        <v>79041</v>
+        <v>79633</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15438,21 +15438,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15462,10 +15462,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>421454</v>
+        <v>421633</v>
       </c>
       <c r="R138" t="n">
-        <v>6788422</v>
+        <v>6788617</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15534,10 +15534,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129124077</v>
+        <v>129124163</v>
       </c>
       <c r="B139" t="n">
-        <v>79631</v>
+        <v>79043</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15545,21 +15545,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15569,10 +15569,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>421633</v>
+        <v>421454</v>
       </c>
       <c r="R139" t="n">
-        <v>6788617</v>
+        <v>6788422</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15641,10 +15641,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129124169</v>
+        <v>129124140</v>
       </c>
       <c r="B140" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15652,21 +15652,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15676,10 +15676,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>421618</v>
+        <v>421656</v>
       </c>
       <c r="R140" t="n">
-        <v>6787872</v>
+        <v>6787791</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15748,10 +15748,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129124140</v>
+        <v>129124068</v>
       </c>
       <c r="B141" t="n">
-        <v>78798</v>
+        <v>79662</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15759,21 +15759,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15783,10 +15783,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>421656</v>
+        <v>421675</v>
       </c>
       <c r="R141" t="n">
-        <v>6787791</v>
+        <v>6787696</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15855,10 +15855,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129124068</v>
+        <v>129124065</v>
       </c>
       <c r="B142" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15890,10 +15890,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>421675</v>
+        <v>421530</v>
       </c>
       <c r="R142" t="n">
-        <v>6787696</v>
+        <v>6788679</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15925,7 +15925,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15962,10 +15962,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129124065</v>
+        <v>129124169</v>
       </c>
       <c r="B143" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15973,21 +15973,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15997,10 +15997,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>421530</v>
+        <v>421618</v>
       </c>
       <c r="R143" t="n">
-        <v>6788679</v>
+        <v>6787872</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16181,10 +16181,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124087</v>
+        <v>129124170</v>
       </c>
       <c r="B145" t="n">
-        <v>79136</v>
+        <v>79043</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16192,21 +16192,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421601</v>
+        <v>421604</v>
       </c>
       <c r="R145" t="n">
-        <v>6787830</v>
+        <v>6787823</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16251,7 +16251,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16288,10 +16288,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124144</v>
+        <v>129124138</v>
       </c>
       <c r="B146" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16323,10 +16323,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421602</v>
+        <v>421292</v>
       </c>
       <c r="R146" t="n">
-        <v>6787829</v>
+        <v>6788456</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16395,45 +16395,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129124138</v>
+        <v>129124106</v>
       </c>
       <c r="B147" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>421292</v>
+        <v>421574</v>
       </c>
       <c r="R147" t="n">
-        <v>6788456</v>
+        <v>6788374</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16465,7 +16470,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16475,7 +16480,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16502,7 +16507,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129124106</v>
+        <v>129124122</v>
       </c>
       <c r="B148" t="n">
         <v>8450</v>
@@ -16533,7 +16538,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -16542,10 +16547,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421574</v>
+        <v>421477</v>
       </c>
       <c r="R148" t="n">
-        <v>6788374</v>
+        <v>6788422</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16577,7 +16582,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16587,7 +16592,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16614,7 +16619,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124122</v>
+        <v>129124120</v>
       </c>
       <c r="B149" t="n">
         <v>8450</v>
@@ -16654,10 +16659,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421477</v>
+        <v>421520</v>
       </c>
       <c r="R149" t="n">
-        <v>6788422</v>
+        <v>6788366</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16689,7 +16694,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16699,7 +16704,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16726,50 +16731,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124120</v>
+        <v>129124087</v>
       </c>
       <c r="B150" t="n">
-        <v>8450</v>
+        <v>79138</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>106545</v>
+        <v>967</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421520</v>
+        <v>421601</v>
       </c>
       <c r="R150" t="n">
-        <v>6788366</v>
+        <v>6787830</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16801,7 +16801,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16838,10 +16838,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124133</v>
+        <v>129124144</v>
       </c>
       <c r="B151" t="n">
-        <v>78799</v>
+        <v>78800</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16849,21 +16849,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16873,10 +16873,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421633</v>
+        <v>421602</v>
       </c>
       <c r="R151" t="n">
-        <v>6787841</v>
+        <v>6787829</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16945,10 +16945,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129124078</v>
+        <v>129124133</v>
       </c>
       <c r="B152" t="n">
-        <v>79631</v>
+        <v>78801</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16956,21 +16956,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16980,10 +16980,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>421640</v>
+        <v>421633</v>
       </c>
       <c r="R152" t="n">
-        <v>6788394</v>
+        <v>6787841</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17052,10 +17052,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129124170</v>
+        <v>129124078</v>
       </c>
       <c r="B153" t="n">
-        <v>79041</v>
+        <v>79633</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17063,21 +17063,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17087,10 +17087,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>421604</v>
+        <v>421640</v>
       </c>
       <c r="R153" t="n">
-        <v>6787823</v>
+        <v>6788394</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17162,7 +17162,7 @@
         <v>129124186</v>
       </c>
       <c r="B154" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17266,45 +17266,50 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129124064</v>
+        <v>129124119</v>
       </c>
       <c r="B155" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>421501</v>
+        <v>421653</v>
       </c>
       <c r="R155" t="n">
-        <v>6788671</v>
+        <v>6788387</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17336,7 +17341,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17346,7 +17351,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17373,10 +17378,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129124137</v>
+        <v>129124076</v>
       </c>
       <c r="B156" t="n">
-        <v>78798</v>
+        <v>79633</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17384,21 +17389,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17408,10 +17413,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>421312</v>
+        <v>421240</v>
       </c>
       <c r="R156" t="n">
-        <v>6788393</v>
+        <v>6788558</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17443,7 +17448,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17453,7 +17458,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17480,50 +17485,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129124119</v>
+        <v>129124084</v>
       </c>
       <c r="B157" t="n">
-        <v>8450</v>
+        <v>79633</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>421653</v>
+        <v>421591</v>
       </c>
       <c r="R157" t="n">
-        <v>6788387</v>
+        <v>6787819</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17555,7 +17555,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17565,7 +17565,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17592,10 +17592,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129124076</v>
+        <v>129124064</v>
       </c>
       <c r="B158" t="n">
-        <v>79631</v>
+        <v>79662</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17603,21 +17603,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17627,10 +17627,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>421240</v>
+        <v>421501</v>
       </c>
       <c r="R158" t="n">
-        <v>6788558</v>
+        <v>6788671</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17672,7 +17672,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17699,10 +17699,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129124084</v>
+        <v>129124137</v>
       </c>
       <c r="B159" t="n">
-        <v>79631</v>
+        <v>78800</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17710,21 +17710,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17734,10 +17734,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>421591</v>
+        <v>421312</v>
       </c>
       <c r="R159" t="n">
-        <v>6787819</v>
+        <v>6788393</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY177"/>
+  <dimension ref="A1:AZ177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124183</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124184</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124185</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124171</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124161</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124162</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124066</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124067</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124118</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124092</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124102</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124174</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124175</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124176</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124177</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2389,6 +2469,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124178</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2496,6 +2581,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124179</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2603,6 +2693,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124180</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2710,6 +2805,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124181</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2817,6 +2917,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124182</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2924,6 +3029,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124186</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3031,6 +3141,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124087</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3138,6 +3253,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124146</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3245,6 +3365,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124172</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3352,6 +3477,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124173</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3464,6 +3594,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124090</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3580,6 +3715,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124104</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3696,6 +3836,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124105</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3803,6 +3948,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093008</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3910,6 +4060,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093018</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4017,6 +4172,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093043</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4124,6 +4284,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093167</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4231,6 +4396,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093173</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4338,6 +4508,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093174</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4445,6 +4620,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093188</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4552,6 +4732,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093226</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4659,6 +4844,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093929</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4766,6 +4956,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093983</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4873,6 +5068,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094012</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4980,6 +5180,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094091</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5087,6 +5292,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094103</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5194,6 +5404,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094170</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5301,6 +5516,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094179</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5408,6 +5628,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094800</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5515,6 +5740,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129095256</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5622,6 +5852,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129095317</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5729,6 +5964,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129095392</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5836,6 +6076,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096050</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5943,6 +6188,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124147</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6050,6 +6300,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124148</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6157,6 +6412,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124149</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6264,6 +6524,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124150</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6371,6 +6636,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124151</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6478,6 +6748,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124152</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6585,6 +6860,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124153</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6692,6 +6972,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124154</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6799,6 +7084,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124155</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6906,6 +7196,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124156</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7013,6 +7308,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124157</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7120,6 +7420,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124158</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7227,6 +7532,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124159</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7334,6 +7644,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124160</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7441,6 +7756,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124163</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7548,6 +7868,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124164</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7655,6 +7980,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124165</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7762,6 +8092,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124166</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7869,6 +8204,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124167</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7976,6 +8316,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124168</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8083,6 +8428,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124169</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8190,6 +8540,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124170</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8297,6 +8652,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124187</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8404,6 +8764,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129095733</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8511,6 +8876,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124137</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8618,6 +8988,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124138</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8725,6 +9100,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124139</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8832,6 +9212,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124140</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8939,6 +9324,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124141</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9046,6 +9436,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124142</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9153,6 +9548,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124143</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9260,6 +9660,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124144</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9367,6 +9772,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124145</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9474,6 +9884,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093027</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9581,6 +9996,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093086</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9688,6 +10108,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093766</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9795,6 +10220,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094072</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9902,6 +10332,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094551</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10009,6 +10444,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129095002</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10116,6 +10556,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129095786</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10223,6 +10668,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129095862</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10330,6 +10780,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129095947</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10437,6 +10892,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124051</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10544,6 +11004,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124052</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10651,6 +11116,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124053</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10758,6 +11228,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124054</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10865,6 +11340,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124055</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10972,6 +11452,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124056</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11079,6 +11564,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124057</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11186,6 +11676,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124058</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11293,6 +11788,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124059</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11400,6 +11900,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124060</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11507,6 +12012,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124061</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11614,6 +12124,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124062</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11721,6 +12236,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124063</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11828,6 +12348,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124064</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11935,6 +12460,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124065</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12042,6 +12572,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124068</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12149,6 +12684,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124069</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12256,6 +12796,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124070</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12363,6 +12908,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124071</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12470,6 +13020,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124072</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12577,6 +13132,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124073</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12689,6 +13249,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094162</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12801,6 +13366,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094242</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12913,6 +13483,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094871</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13025,6 +13600,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124096</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13137,6 +13717,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129095090</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13249,6 +13834,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124088</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13361,6 +13951,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129095582</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13491,6 +14086,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88280081</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13612,6 +14212,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88280082</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13719,6 +14324,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093117</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13826,6 +14436,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093853</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13933,6 +14548,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093945</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14040,6 +14660,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094196</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14147,6 +14772,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094249</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14259,6 +14889,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124106</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14371,6 +15006,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124107</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14483,6 +15123,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124108</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14595,6 +15240,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124109</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14707,6 +15357,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124110</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14819,6 +15474,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124111</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14931,6 +15591,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124112</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15043,6 +15708,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124114</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15155,6 +15825,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124115</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15267,6 +15942,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124116</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15379,6 +16059,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124117</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15491,6 +16176,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124119</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15603,6 +16293,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124120</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15715,6 +16410,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124121</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15827,6 +16527,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124122</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15939,6 +16644,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124123</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16051,6 +16761,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124124</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16163,6 +16878,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124125</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16275,6 +16995,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124126</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16387,6 +17112,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124127</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16494,6 +17224,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129095730</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16601,6 +17336,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124103</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16708,6 +17448,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124128</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16815,6 +17560,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124129</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16922,6 +17672,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124130</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17029,6 +17784,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124131</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17136,6 +17896,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124132</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17243,6 +18008,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124133</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17350,6 +18120,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124134</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17457,6 +18232,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124135</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17564,6 +18344,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124136</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17671,6 +18456,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093598</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17778,6 +18568,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094076</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17885,6 +18680,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094542</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17992,6 +18792,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094943</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18099,6 +18904,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129095743</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18206,6 +19016,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129095886</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18313,6 +19128,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129095952</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18425,6 +19245,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124074</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18532,6 +19357,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124075</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18639,6 +19469,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124076</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18746,6 +19581,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124077</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18853,6 +19693,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124078</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18960,6 +19805,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124079</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19067,6 +19917,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124080</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19174,6 +20029,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124081</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19281,6 +20141,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124082</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19388,6 +20253,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124083</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19495,6 +20365,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124084</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19602,6 +20477,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124085</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19709,8 +20589,191 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124091</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationsh